--- a/RWF_Entourage.xlsx
+++ b/RWF_Entourage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise-Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="237" documentId="8_{A60C4C07-97B7-C84A-9A2B-5740B6758233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0548CC4B-A655-CE4C-96EE-75028DF21013}"/>
+  <xr:revisionPtr revIDLastSave="243" documentId="8_{A60C4C07-97B7-C84A-9A2B-5740B6758233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72BF127E-70D8-9845-871E-25D11DF84456}"/>
   <bookViews>
-    <workbookView xWindow="5920" yWindow="8240" windowWidth="33100" windowHeight="15420" xr2:uid="{3F2EE892-A619-2747-9F28-51C106355EDF}"/>
+    <workbookView xWindow="16000" yWindow="6820" windowWidth="33100" windowHeight="15420" xr2:uid="{3F2EE892-A619-2747-9F28-51C106355EDF}"/>
   </bookViews>
   <sheets>
     <sheet name="Entourage" sheetId="1" r:id="rId1"/>
@@ -406,9 +406,6 @@
     <t>+ Le Soldat américain  (1970)itz et Reinhold !</t>
   </si>
   <si>
-    <t>Fig essentielle de la der période, à la fois techniquement indispenLe Soldat américain  (1970)ble et historiquement décisive pour la conservation de l’héritage Fassbinder</t>
-  </si>
-  <si>
     <t>Proche du milieu théâtral des débuts, Le Soldat américain  (1970)ns précision biographique intime forte dans la source de départ</t>
   </si>
   <si>
@@ -589,9 +586,6 @@
     <t>Jeu, théâtre Le Monde sur le fil  (1973)mé, relation de pouvoir</t>
   </si>
   <si>
-    <t>Identité visuelle des Le Monde sur le fil  (1973)ms de RWF</t>
-  </si>
-  <si>
     <t>La Troisième génération  (1979)</t>
   </si>
   <si>
@@ -691,22 +685,13 @@
     <t>L’Allemagne en automne  (1978)</t>
   </si>
   <si>
-    <t>FormTous les autres s’appellent Ali  (1974)Le Soldat américain  (1970)tion du grand style visuel tardif</t>
-  </si>
-  <si>
     <t>Tous les autres s’appellent Ali  (1974)</t>
   </si>
   <si>
-    <t>Figure de l’altérité raciTous les autres s’appellent Ali  (1974)sée et du désir</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tous les autres s’appellent Ali  (1974) </t>
   </si>
   <si>
     <t>Corps de la frustration sociale, de l’Tous les autres s’appellent Ali  (1974)énation et du domestique</t>
-  </si>
-  <si>
-    <t>Fascination du méchant, +journTous les autres s’appellent Ali  (1974)ste</t>
   </si>
   <si>
     <t>Maman Küsters s’en va au ciel  (1975)</t>
@@ -996,6 +981,21 @@
   </si>
   <si>
     <t xml:space="preserve">Despair (1978) </t>
+  </si>
+  <si>
+    <t>Formation du grand style visuel tardif</t>
+  </si>
+  <si>
+    <t>Figure de l’altérité racisée et du désir</t>
+  </si>
+  <si>
+    <t>Fascination du méchant, +journaliste</t>
+  </si>
+  <si>
+    <t>Fig essentielle de la dernière période, à la fois techniquement indispensable et historiquement décisive pour la conservation de l’héritage Fassbinder</t>
+  </si>
+  <si>
+    <t>Identité visuelle des films de RWF</t>
   </si>
 </sst>
 </file>
@@ -2406,18 +2406,18 @@
       <c r="C1" s="53"/>
       <c r="D1" s="53"/>
       <c r="L1" s="63" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="M1" s="63" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="L2" s="63" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="M2" s="63" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -2427,16 +2427,16 @@
     </row>
     <row r="4" spans="1:13" ht="40" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="61" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>156</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>2</v>
@@ -2460,21 +2460,21 @@
         <v>8</v>
       </c>
       <c r="L4" s="69" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="M4" s="70" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="84" t="s">
+        <v>116</v>
+      </c>
+      <c r="B5" s="93" t="s">
+        <v>238</v>
+      </c>
+      <c r="C5" s="108" t="s">
         <v>117</v>
-      </c>
-      <c r="B5" s="93" t="s">
-        <v>243</v>
-      </c>
-      <c r="C5" s="108" t="s">
-        <v>118</v>
       </c>
       <c r="D5" s="55"/>
       <c r="E5" s="105" t="s">
@@ -2490,19 +2490,19 @@
         <v>12</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="J5" s="105" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="K5" s="99" t="s">
         <v>93</v>
       </c>
       <c r="L5" s="78" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="M5" s="81" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
@@ -2515,7 +2515,7 @@
       <c r="G6" s="106"/>
       <c r="H6" s="106"/>
       <c r="I6" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J6" s="106"/>
       <c r="K6" s="100"/>
@@ -2549,7 +2549,7 @@
       <c r="G8" s="106"/>
       <c r="H8" s="106"/>
       <c r="I8" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J8" s="106"/>
       <c r="K8" s="100"/>
@@ -2566,7 +2566,7 @@
       <c r="G9" s="106"/>
       <c r="H9" s="106"/>
       <c r="I9" s="7" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="J9" s="106"/>
       <c r="K9" s="100"/>
@@ -2583,7 +2583,7 @@
       <c r="G10" s="106"/>
       <c r="H10" s="106"/>
       <c r="I10" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J10" s="106"/>
       <c r="K10" s="100"/>
@@ -2600,7 +2600,7 @@
       <c r="G11" s="106"/>
       <c r="H11" s="106"/>
       <c r="I11" s="8" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="J11" s="106"/>
       <c r="K11" s="100"/>
@@ -2617,7 +2617,7 @@
       <c r="G12" s="106"/>
       <c r="H12" s="106"/>
       <c r="I12" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J12" s="106"/>
       <c r="K12" s="100"/>
@@ -2634,7 +2634,7 @@
       <c r="G13" s="106"/>
       <c r="H13" s="106"/>
       <c r="I13" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J13" s="106"/>
       <c r="K13" s="100"/>
@@ -2651,7 +2651,7 @@
       <c r="G14" s="106"/>
       <c r="H14" s="106"/>
       <c r="I14" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J14" s="106"/>
       <c r="K14" s="100"/>
@@ -2668,7 +2668,7 @@
       <c r="G15" s="107"/>
       <c r="H15" s="107"/>
       <c r="I15" s="9" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="J15" s="107"/>
       <c r="K15" s="101"/>
@@ -2677,13 +2677,13 @@
     </row>
     <row r="16" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="84" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B16" s="93" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" s="108" t="s">
         <v>119</v>
-      </c>
-      <c r="C16" s="108" t="s">
-        <v>120</v>
       </c>
       <c r="D16" s="55"/>
       <c r="E16" s="105" t="s">
@@ -2699,19 +2699,19 @@
         <v>16</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J16" s="105" t="s">
-        <v>199</v>
+        <v>296</v>
       </c>
       <c r="K16" s="99" t="s">
         <v>94</v>
       </c>
       <c r="L16" s="66" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="M16" s="67" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -2724,15 +2724,15 @@
       <c r="G17" s="106"/>
       <c r="H17" s="106"/>
       <c r="I17" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J17" s="106"/>
       <c r="K17" s="100"/>
       <c r="L17" s="66" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="M17" s="67" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -2745,15 +2745,15 @@
       <c r="G18" s="106"/>
       <c r="H18" s="106"/>
       <c r="I18" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J18" s="106"/>
       <c r="K18" s="100"/>
       <c r="L18" s="66" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="M18" s="67" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -2766,15 +2766,15 @@
       <c r="G19" s="106"/>
       <c r="H19" s="106"/>
       <c r="I19" s="13" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="J19" s="106"/>
       <c r="K19" s="100"/>
       <c r="L19" s="66" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="M19" s="67" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -2787,15 +2787,15 @@
       <c r="G20" s="106"/>
       <c r="H20" s="106"/>
       <c r="I20" s="13" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J20" s="106"/>
       <c r="K20" s="100"/>
       <c r="L20" s="66" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="M20" s="67" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -2808,15 +2808,15 @@
       <c r="G21" s="106"/>
       <c r="H21" s="106"/>
       <c r="I21" s="13" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="J21" s="106"/>
       <c r="K21" s="100"/>
       <c r="L21" s="66" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="M21" s="67" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -2829,15 +2829,15 @@
       <c r="G22" s="106"/>
       <c r="H22" s="106"/>
       <c r="I22" s="13" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J22" s="106"/>
       <c r="K22" s="100"/>
       <c r="L22" s="66" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="M22" s="67" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -2850,15 +2850,15 @@
       <c r="G23" s="106"/>
       <c r="H23" s="106"/>
       <c r="I23" s="13" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J23" s="106"/>
       <c r="K23" s="100"/>
       <c r="L23" s="66" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="M23" s="67" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -2871,15 +2871,15 @@
       <c r="G24" s="106"/>
       <c r="H24" s="106"/>
       <c r="I24" s="13" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J24" s="106"/>
       <c r="K24" s="100"/>
       <c r="L24" s="66" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="M24" s="67" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -2892,15 +2892,15 @@
       <c r="G25" s="106"/>
       <c r="H25" s="106"/>
       <c r="I25" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J25" s="106"/>
       <c r="K25" s="100"/>
       <c r="L25" s="66" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="M25" s="67" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -2913,15 +2913,15 @@
       <c r="G26" s="106"/>
       <c r="H26" s="106"/>
       <c r="I26" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J26" s="106"/>
       <c r="K26" s="100"/>
       <c r="L26" s="66" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="M26" s="67" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -2934,15 +2934,15 @@
       <c r="G27" s="106"/>
       <c r="H27" s="106"/>
       <c r="I27" s="14" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="J27" s="106"/>
       <c r="K27" s="100"/>
       <c r="L27" s="66" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="M27" s="67" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -2955,26 +2955,26 @@
       <c r="G28" s="107"/>
       <c r="H28" s="107"/>
       <c r="I28" s="15" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J28" s="107"/>
       <c r="K28" s="101"/>
       <c r="L28" s="66" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="M28" s="67" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="84" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B29" s="93" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C29" s="108" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D29" s="55"/>
       <c r="E29" s="105" t="s">
@@ -2990,19 +2990,19 @@
         <v>20</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J29" s="105" t="s">
-        <v>201</v>
+        <v>297</v>
       </c>
       <c r="K29" s="99" t="s">
         <v>101</v>
       </c>
       <c r="L29" s="71" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="M29" s="72" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3015,15 +3015,15 @@
       <c r="G30" s="106"/>
       <c r="H30" s="106"/>
       <c r="I30" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J30" s="106"/>
       <c r="K30" s="100"/>
       <c r="L30" s="74" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="M30" s="67" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3036,15 +3036,15 @@
       <c r="G31" s="106"/>
       <c r="H31" s="106"/>
       <c r="I31" s="16" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="J31" s="106"/>
       <c r="K31" s="100"/>
       <c r="L31" s="75" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="M31" s="67" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3057,15 +3057,15 @@
       <c r="G32" s="106"/>
       <c r="H32" s="106"/>
       <c r="I32" s="12" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="J32" s="106"/>
       <c r="K32" s="100"/>
       <c r="L32" s="75" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="M32" s="67" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -3078,26 +3078,26 @@
       <c r="G33" s="107"/>
       <c r="H33" s="107"/>
       <c r="I33" s="17" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J33" s="107"/>
       <c r="K33" s="101"/>
       <c r="L33" s="76" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="M33" s="73" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A34" s="93" t="s">
+        <v>121</v>
+      </c>
+      <c r="B34" s="93" t="s">
+        <v>121</v>
+      </c>
+      <c r="C34" s="108" t="s">
         <v>122</v>
-      </c>
-      <c r="B34" s="93" t="s">
-        <v>122</v>
-      </c>
-      <c r="C34" s="108" t="s">
-        <v>123</v>
       </c>
       <c r="D34" s="55"/>
       <c r="E34" s="105" t="s">
@@ -3113,7 +3113,7 @@
         <v>24</v>
       </c>
       <c r="I34" s="21" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="J34" s="105" t="s">
         <v>25</v>
@@ -3122,10 +3122,10 @@
         <v>95</v>
       </c>
       <c r="L34" s="74" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="M34" s="72" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="24" x14ac:dyDescent="0.2">
@@ -3140,15 +3140,15 @@
       </c>
       <c r="H35" s="106"/>
       <c r="I35" s="13" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="J35" s="106"/>
       <c r="K35" s="132"/>
       <c r="L35" s="75" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="M35" s="67" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3161,15 +3161,15 @@
       <c r="G36" s="19"/>
       <c r="H36" s="106"/>
       <c r="I36" s="13" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J36" s="106"/>
       <c r="K36" s="132"/>
       <c r="L36" s="75" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="M36" s="67" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3182,15 +3182,15 @@
       <c r="G37" s="19"/>
       <c r="H37" s="106"/>
       <c r="I37" s="13" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="J37" s="106"/>
       <c r="K37" s="132"/>
       <c r="L37" s="75" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="M37" s="67" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -3206,21 +3206,21 @@
       <c r="J38" s="107"/>
       <c r="K38" s="133"/>
       <c r="L38" s="76" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="M38" s="73" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A39" s="93" t="s">
+        <v>114</v>
+      </c>
+      <c r="B39" s="93" t="s">
+        <v>114</v>
+      </c>
+      <c r="C39" s="108" t="s">
         <v>115</v>
-      </c>
-      <c r="B39" s="93" t="s">
-        <v>115</v>
-      </c>
-      <c r="C39" s="108" t="s">
-        <v>116</v>
       </c>
       <c r="D39" s="55"/>
       <c r="E39" s="105" t="s">
@@ -3236,7 +3236,7 @@
         <v>29</v>
       </c>
       <c r="I39" s="23" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>30</v>
@@ -3245,10 +3245,10 @@
         <v>97</v>
       </c>
       <c r="L39" s="81" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="M39" s="67" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.2">
@@ -3261,7 +3261,7 @@
       <c r="G40" s="106"/>
       <c r="H40" s="106"/>
       <c r="I40" s="24" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="J40" s="26" t="s">
         <v>31</v>
@@ -3280,7 +3280,7 @@
       <c r="G41" s="106"/>
       <c r="H41" s="106"/>
       <c r="I41" s="13" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="J41" s="19"/>
       <c r="K41" s="100"/>
@@ -3297,7 +3297,7 @@
       <c r="G42" s="106"/>
       <c r="H42" s="106"/>
       <c r="I42" s="25" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="J42" s="19"/>
       <c r="K42" s="100"/>
@@ -3314,7 +3314,7 @@
       <c r="G43" s="106"/>
       <c r="H43" s="106"/>
       <c r="I43" s="13" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J43" s="19"/>
       <c r="K43" s="100"/>
@@ -3331,7 +3331,7 @@
       <c r="G44" s="106"/>
       <c r="H44" s="106"/>
       <c r="I44" s="13" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J44" s="19"/>
       <c r="K44" s="100"/>
@@ -3348,7 +3348,7 @@
       <c r="G45" s="107"/>
       <c r="H45" s="107"/>
       <c r="I45" s="17" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J45" s="20"/>
       <c r="K45" s="101"/>
@@ -3357,13 +3357,13 @@
     </row>
     <row r="46" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A46" s="93" t="s">
+        <v>123</v>
+      </c>
+      <c r="B46" s="93" t="s">
+        <v>123</v>
+      </c>
+      <c r="C46" s="108" t="s">
         <v>124</v>
-      </c>
-      <c r="B46" s="93" t="s">
-        <v>124</v>
-      </c>
-      <c r="C46" s="108" t="s">
-        <v>125</v>
       </c>
       <c r="D46" s="55"/>
       <c r="E46" s="105" t="s">
@@ -3373,13 +3373,13 @@
         <v>21</v>
       </c>
       <c r="G46" s="105" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H46" s="105" t="s">
         <v>102</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J46" s="105" t="s">
         <v>33</v>
@@ -3388,10 +3388,10 @@
         <v>96</v>
       </c>
       <c r="L46" s="75" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="M46" s="67" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3404,15 +3404,15 @@
       <c r="G47" s="106"/>
       <c r="H47" s="106"/>
       <c r="I47" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J47" s="106"/>
       <c r="K47" s="100"/>
       <c r="L47" s="75" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="M47" s="67" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3425,15 +3425,15 @@
       <c r="G48" s="106"/>
       <c r="H48" s="106"/>
       <c r="I48" s="27" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="J48" s="106"/>
       <c r="K48" s="100"/>
       <c r="L48" s="75" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="M48" s="67" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3446,15 +3446,15 @@
       <c r="G49" s="106"/>
       <c r="H49" s="106"/>
       <c r="I49" s="16" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J49" s="106"/>
       <c r="K49" s="100"/>
       <c r="L49" s="75" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="M49" s="67" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3467,15 +3467,15 @@
       <c r="G50" s="106"/>
       <c r="H50" s="106"/>
       <c r="I50" s="13" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="J50" s="106"/>
       <c r="K50" s="100"/>
       <c r="L50" s="75" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="M50" s="67" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3488,15 +3488,15 @@
       <c r="G51" s="106"/>
       <c r="H51" s="106"/>
       <c r="I51" s="13" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J51" s="106"/>
       <c r="K51" s="100"/>
       <c r="L51" s="75" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="M51" s="67" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3509,15 +3509,15 @@
       <c r="G52" s="106"/>
       <c r="H52" s="106"/>
       <c r="I52" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J52" s="106"/>
       <c r="K52" s="100"/>
       <c r="L52" s="75" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="M52" s="67" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -3533,21 +3533,21 @@
       <c r="J53" s="107"/>
       <c r="K53" s="101"/>
       <c r="L53" s="75" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="M53" s="67" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A54" s="93" t="s">
+        <v>125</v>
+      </c>
+      <c r="B54" s="93" t="s">
+        <v>125</v>
+      </c>
+      <c r="C54" s="108" t="s">
         <v>126</v>
-      </c>
-      <c r="B54" s="93" t="s">
-        <v>126</v>
-      </c>
-      <c r="C54" s="108" t="s">
-        <v>127</v>
       </c>
       <c r="D54" s="55"/>
       <c r="E54" s="105" t="s">
@@ -3563,7 +3563,7 @@
         <v>36</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="J54" s="105" t="s">
         <v>37</v>
@@ -3572,10 +3572,10 @@
         <v>98</v>
       </c>
       <c r="L54" s="75" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="M54" s="67" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3588,15 +3588,15 @@
       <c r="G55" s="106"/>
       <c r="H55" s="106"/>
       <c r="I55" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J55" s="106"/>
       <c r="K55" s="100"/>
       <c r="L55" s="75" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="M55" s="67" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
     </row>
     <row r="56" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3609,15 +3609,15 @@
       <c r="G56" s="106"/>
       <c r="H56" s="106"/>
       <c r="I56" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J56" s="106"/>
       <c r="K56" s="100"/>
       <c r="L56" s="75" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="M56" s="67" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3630,15 +3630,15 @@
       <c r="G57" s="106"/>
       <c r="H57" s="106"/>
       <c r="I57" s="13" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="J57" s="106"/>
       <c r="K57" s="100"/>
       <c r="L57" s="75" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="M57" s="67" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3651,15 +3651,15 @@
       <c r="G58" s="106"/>
       <c r="H58" s="106"/>
       <c r="I58" s="16" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J58" s="106"/>
       <c r="K58" s="100"/>
       <c r="L58" s="75" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="M58" s="67" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3672,15 +3672,15 @@
       <c r="G59" s="106"/>
       <c r="H59" s="106"/>
       <c r="I59" s="13" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="J59" s="106"/>
       <c r="K59" s="100"/>
       <c r="L59" s="75" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="M59" s="67" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3693,15 +3693,15 @@
       <c r="G60" s="106"/>
       <c r="H60" s="106"/>
       <c r="I60" s="13" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J60" s="106"/>
       <c r="K60" s="100"/>
       <c r="L60" s="75" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="M60" s="67" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3714,15 +3714,15 @@
       <c r="G61" s="106"/>
       <c r="H61" s="106"/>
       <c r="I61" s="13" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J61" s="106"/>
       <c r="K61" s="100"/>
       <c r="L61" s="75" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="M61" s="67" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -3735,26 +3735,26 @@
       <c r="G62" s="107"/>
       <c r="H62" s="107"/>
       <c r="I62" s="28" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J62" s="107"/>
       <c r="K62" s="101"/>
       <c r="L62" s="75" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="M62" s="67" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A63" s="93" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B63" s="93" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C63" s="108" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D63" s="55"/>
       <c r="E63" s="137"/>
@@ -3775,10 +3775,10 @@
         <v>99</v>
       </c>
       <c r="L63" s="75" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="M63" s="67" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="26" x14ac:dyDescent="0.2">
@@ -3793,15 +3793,15 @@
       <c r="G64" s="138"/>
       <c r="H64" s="106"/>
       <c r="I64" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J64" s="106"/>
       <c r="K64" s="100"/>
       <c r="L64" s="75" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="M64" s="67" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3814,15 +3814,15 @@
       <c r="G65" s="138"/>
       <c r="H65" s="106"/>
       <c r="I65" s="25" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="J65" s="106"/>
       <c r="K65" s="100"/>
       <c r="L65" s="75" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="M65" s="67" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3835,15 +3835,15 @@
       <c r="G66" s="138"/>
       <c r="H66" s="106"/>
       <c r="I66" s="13" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="J66" s="106"/>
       <c r="K66" s="100"/>
       <c r="L66" s="75" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="M66" s="67" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3856,15 +3856,15 @@
       <c r="G67" s="138"/>
       <c r="H67" s="106"/>
       <c r="I67" s="13" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="J67" s="106"/>
       <c r="K67" s="100"/>
       <c r="L67" s="75" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="M67" s="67" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3877,15 +3877,15 @@
       <c r="G68" s="138"/>
       <c r="H68" s="106"/>
       <c r="I68" s="11" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="J68" s="106"/>
       <c r="K68" s="100"/>
       <c r="L68" s="75" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="M68" s="67" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3898,15 +3898,15 @@
       <c r="G69" s="138"/>
       <c r="H69" s="106"/>
       <c r="I69" s="25" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="J69" s="106"/>
       <c r="K69" s="100"/>
       <c r="L69" s="75" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="M69" s="67" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3919,15 +3919,15 @@
       <c r="G70" s="138"/>
       <c r="H70" s="106"/>
       <c r="I70" s="16" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="J70" s="106"/>
       <c r="K70" s="100"/>
       <c r="L70" s="75" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="M70" s="67" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3940,15 +3940,15 @@
       <c r="G71" s="138"/>
       <c r="H71" s="106"/>
       <c r="I71" s="13" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J71" s="106"/>
       <c r="K71" s="100"/>
       <c r="L71" s="75" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="M71" s="67" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3961,15 +3961,15 @@
       <c r="G72" s="138"/>
       <c r="H72" s="106"/>
       <c r="I72" s="16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J72" s="106"/>
       <c r="K72" s="100"/>
       <c r="L72" s="75" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="M72" s="67" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3982,15 +3982,15 @@
       <c r="G73" s="138"/>
       <c r="H73" s="106"/>
       <c r="I73" s="13" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J73" s="106"/>
       <c r="K73" s="100"/>
       <c r="L73" s="75" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="M73" s="67" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4003,15 +4003,15 @@
       <c r="G74" s="138"/>
       <c r="H74" s="106"/>
       <c r="I74" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J74" s="106"/>
       <c r="K74" s="100"/>
       <c r="L74" s="75" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="M74" s="67" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="75" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -4024,15 +4024,15 @@
       <c r="G75" s="139"/>
       <c r="H75" s="107"/>
       <c r="I75" s="30" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="J75" s="107"/>
       <c r="K75" s="101"/>
       <c r="L75" s="75" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="M75" s="67" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4055,19 +4055,19 @@
         <v>44</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="J76" s="105" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="K76" s="134" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="L76" s="75" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="M76" s="67" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="77" spans="1:13" ht="39" x14ac:dyDescent="0.2">
@@ -4082,15 +4082,15 @@
       <c r="G77" s="106"/>
       <c r="H77" s="106"/>
       <c r="I77" s="11" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="J77" s="106"/>
       <c r="K77" s="135"/>
       <c r="L77" s="75" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="M77" s="67" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="78" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4103,15 +4103,15 @@
       <c r="G78" s="106"/>
       <c r="H78" s="106"/>
       <c r="I78" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J78" s="106"/>
       <c r="K78" s="135"/>
       <c r="L78" s="75" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="M78" s="67" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="79" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4124,15 +4124,15 @@
       <c r="G79" s="106"/>
       <c r="H79" s="106"/>
       <c r="I79" s="31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J79" s="106"/>
       <c r="K79" s="135"/>
       <c r="L79" s="75" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="M79" s="67" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="80" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4145,15 +4145,15 @@
       <c r="G80" s="106"/>
       <c r="H80" s="106"/>
       <c r="I80" s="31" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J80" s="106"/>
       <c r="K80" s="135"/>
       <c r="L80" s="75" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="M80" s="67" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="81" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4166,15 +4166,15 @@
       <c r="G81" s="106"/>
       <c r="H81" s="106"/>
       <c r="I81" s="13" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="J81" s="106"/>
       <c r="K81" s="135"/>
       <c r="L81" s="75" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="M81" s="67" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="82" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4187,15 +4187,15 @@
       <c r="G82" s="106"/>
       <c r="H82" s="106"/>
       <c r="I82" s="13" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="J82" s="106"/>
       <c r="K82" s="135"/>
       <c r="L82" s="75" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="M82" s="67" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4208,15 +4208,15 @@
       <c r="G83" s="106"/>
       <c r="H83" s="106"/>
       <c r="I83" s="13" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J83" s="106"/>
       <c r="K83" s="135"/>
       <c r="L83" s="75" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="M83" s="67" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="84" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4229,15 +4229,15 @@
       <c r="G84" s="106"/>
       <c r="H84" s="106"/>
       <c r="I84" s="25" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J84" s="106"/>
       <c r="K84" s="135"/>
       <c r="L84" s="75" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="M84" s="67" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4250,15 +4250,15 @@
       <c r="G85" s="106"/>
       <c r="H85" s="106"/>
       <c r="I85" s="31" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="J85" s="106"/>
       <c r="K85" s="135"/>
       <c r="L85" s="75" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="M85" s="67" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -4271,26 +4271,26 @@
       <c r="G86" s="107"/>
       <c r="H86" s="107"/>
       <c r="I86" s="30" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J86" s="107"/>
       <c r="K86" s="136"/>
       <c r="L86" s="75" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="M86" s="67" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="87" spans="1:13" ht="52" x14ac:dyDescent="0.2">
       <c r="A87" s="93" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B87" s="93" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C87" s="108" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D87" s="55"/>
       <c r="E87" s="105"/>
@@ -4302,19 +4302,19 @@
       </c>
       <c r="H87" s="105"/>
       <c r="I87" s="32" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>204</v>
+        <v>298</v>
       </c>
       <c r="K87" s="131" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="L87" s="75" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="M87" s="67" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="26" x14ac:dyDescent="0.2">
@@ -4329,17 +4329,17 @@
       </c>
       <c r="H88" s="106"/>
       <c r="I88" s="13" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="J88" s="26" t="s">
         <v>103</v>
       </c>
       <c r="K88" s="132"/>
       <c r="L88" s="75" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="M88" s="67" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="89" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4352,15 +4352,15 @@
       <c r="G89" s="19"/>
       <c r="H89" s="106"/>
       <c r="I89" s="13" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J89" s="19"/>
       <c r="K89" s="132"/>
       <c r="L89" s="75" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="M89" s="67" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="90" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4373,15 +4373,15 @@
       <c r="G90" s="19"/>
       <c r="H90" s="106"/>
       <c r="I90" s="16" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="J90" s="19"/>
       <c r="K90" s="132"/>
       <c r="L90" s="75" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="M90" s="67" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="91" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4394,15 +4394,15 @@
       <c r="G91" s="19"/>
       <c r="H91" s="106"/>
       <c r="I91" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J91" s="19"/>
       <c r="K91" s="132"/>
       <c r="L91" s="75" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="M91" s="67" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="92" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4415,15 +4415,15 @@
       <c r="G92" s="19"/>
       <c r="H92" s="106"/>
       <c r="I92" s="24" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J92" s="19"/>
       <c r="K92" s="132"/>
       <c r="L92" s="75" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="M92" s="67" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="93" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4436,15 +4436,15 @@
       <c r="G93" s="19"/>
       <c r="H93" s="106"/>
       <c r="I93" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J93" s="19"/>
       <c r="K93" s="132"/>
       <c r="L93" s="75" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="M93" s="67" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4457,15 +4457,15 @@
       <c r="G94" s="19"/>
       <c r="H94" s="106"/>
       <c r="I94" s="11" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="J94" s="19"/>
       <c r="K94" s="132"/>
       <c r="L94" s="75" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="M94" s="67" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4478,15 +4478,15 @@
       <c r="G95" s="19"/>
       <c r="H95" s="106"/>
       <c r="I95" s="11" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="J95" s="19"/>
       <c r="K95" s="132"/>
       <c r="L95" s="75" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="M95" s="67" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="96" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4502,10 +4502,10 @@
       <c r="J96" s="19"/>
       <c r="K96" s="132"/>
       <c r="L96" s="75" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="M96" s="67" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="97" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4521,10 +4521,10 @@
       <c r="J97" s="19"/>
       <c r="K97" s="132"/>
       <c r="L97" s="75" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="M97" s="67" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="98" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4540,10 +4540,10 @@
       <c r="J98" s="19"/>
       <c r="K98" s="132"/>
       <c r="L98" s="75" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="M98" s="67" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="99" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -4559,21 +4559,21 @@
       <c r="J99" s="20"/>
       <c r="K99" s="133"/>
       <c r="L99" s="75" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="M99" s="67" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="100" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A100" s="93" t="s">
+        <v>127</v>
+      </c>
+      <c r="B100" s="93" t="s">
+        <v>127</v>
+      </c>
+      <c r="C100" s="108" t="s">
         <v>128</v>
-      </c>
-      <c r="B100" s="93" t="s">
-        <v>128</v>
-      </c>
-      <c r="C100" s="108" t="s">
-        <v>129</v>
       </c>
       <c r="D100" s="55"/>
       <c r="E100" s="105" t="s">
@@ -4589,19 +4589,19 @@
         <v>48</v>
       </c>
       <c r="I100" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="J100" s="105" t="s">
         <v>49</v>
       </c>
       <c r="K100" s="99" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="L100" s="75" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="M100" s="67" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="101" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4614,15 +4614,15 @@
       <c r="G101" s="106"/>
       <c r="H101" s="106"/>
       <c r="I101" s="8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="J101" s="106"/>
       <c r="K101" s="100"/>
       <c r="L101" s="75" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="M101" s="67" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="102" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4635,15 +4635,15 @@
       <c r="G102" s="106"/>
       <c r="H102" s="106"/>
       <c r="I102" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J102" s="106"/>
       <c r="K102" s="100"/>
       <c r="L102" s="75" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="M102" s="67" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="103" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4656,15 +4656,15 @@
       <c r="G103" s="106"/>
       <c r="H103" s="106"/>
       <c r="I103" s="33" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J103" s="106"/>
       <c r="K103" s="100"/>
       <c r="L103" s="75" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="M103" s="67" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="104" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4677,15 +4677,15 @@
       <c r="G104" s="106"/>
       <c r="H104" s="106"/>
       <c r="I104" s="34" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J104" s="106"/>
       <c r="K104" s="100"/>
       <c r="L104" s="75" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="M104" s="67" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="105" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4698,15 +4698,15 @@
       <c r="G105" s="106"/>
       <c r="H105" s="106"/>
       <c r="I105" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="J105" s="106"/>
       <c r="K105" s="100"/>
       <c r="L105" s="75" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="M105" s="67" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="106" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -4719,23 +4719,23 @@
       <c r="G106" s="107"/>
       <c r="H106" s="107"/>
       <c r="I106" s="35" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="J106" s="107"/>
       <c r="K106" s="101"/>
       <c r="L106" s="75" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="M106" s="67" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="107" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A107" s="96" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B107" s="96" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C107" s="108" t="s">
         <v>50</v>
@@ -4748,17 +4748,17 @@
       <c r="G107" s="105"/>
       <c r="H107" s="105"/>
       <c r="I107" s="10" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="J107" s="105"/>
       <c r="K107" s="99" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L107" s="75" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="M107" s="67" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
     </row>
     <row r="108" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4773,15 +4773,15 @@
       <c r="G108" s="106"/>
       <c r="H108" s="106"/>
       <c r="I108" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J108" s="106"/>
       <c r="K108" s="100"/>
       <c r="L108" s="75" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="M108" s="67" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
     </row>
     <row r="109" spans="1:13" ht="26" x14ac:dyDescent="0.2">
@@ -4796,15 +4796,15 @@
       <c r="G109" s="106"/>
       <c r="H109" s="106"/>
       <c r="I109" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="J109" s="106"/>
       <c r="K109" s="100"/>
       <c r="L109" s="75" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="M109" s="67" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
     </row>
     <row r="110" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4817,15 +4817,15 @@
       <c r="G110" s="106"/>
       <c r="H110" s="106"/>
       <c r="I110" s="13" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J110" s="106"/>
       <c r="K110" s="100"/>
       <c r="L110" s="75" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="M110" s="67" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
     </row>
     <row r="111" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4838,15 +4838,15 @@
       <c r="G111" s="106"/>
       <c r="H111" s="106"/>
       <c r="I111" s="13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="J111" s="106"/>
       <c r="K111" s="100"/>
       <c r="L111" s="75" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="M111" s="67" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
     </row>
     <row r="112" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -4859,26 +4859,26 @@
       <c r="G112" s="107"/>
       <c r="H112" s="107"/>
       <c r="I112" s="17" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J112" s="107"/>
       <c r="K112" s="101"/>
       <c r="L112" s="75" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="M112" s="67" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
     </row>
     <row r="113" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A113" s="93" t="s">
+        <v>130</v>
+      </c>
+      <c r="B113" s="93" t="s">
+        <v>130</v>
+      </c>
+      <c r="C113" s="108" t="s">
         <v>131</v>
-      </c>
-      <c r="B113" s="93" t="s">
-        <v>131</v>
-      </c>
-      <c r="C113" s="108" t="s">
-        <v>132</v>
       </c>
       <c r="D113" s="58"/>
       <c r="E113" s="4"/>
@@ -4892,19 +4892,19 @@
         <v>56</v>
       </c>
       <c r="I113" s="36" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J113" s="105" t="s">
-        <v>104</v>
+        <v>299</v>
       </c>
       <c r="K113" s="128" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="L113" s="75" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="M113" s="67" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="114" spans="1:13" ht="26" x14ac:dyDescent="0.2">
@@ -4919,15 +4919,15 @@
       <c r="G114" s="106"/>
       <c r="H114" s="106"/>
       <c r="I114" s="25" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J114" s="106"/>
       <c r="K114" s="129"/>
       <c r="L114" s="75" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="M114" s="67" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="115" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4940,15 +4940,15 @@
       <c r="G115" s="106"/>
       <c r="H115" s="106"/>
       <c r="I115" s="13" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J115" s="106"/>
       <c r="K115" s="129"/>
       <c r="L115" s="75" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="M115" s="67" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="116" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4961,15 +4961,15 @@
       <c r="G116" s="106"/>
       <c r="H116" s="106"/>
       <c r="I116" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J116" s="106"/>
       <c r="K116" s="129"/>
       <c r="L116" s="75" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="M116" s="67" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="117" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4982,15 +4982,15 @@
       <c r="G117" s="106"/>
       <c r="H117" s="106"/>
       <c r="I117" s="11" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J117" s="106"/>
       <c r="K117" s="129"/>
       <c r="L117" s="75" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="M117" s="67" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="118" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5003,15 +5003,15 @@
       <c r="G118" s="106"/>
       <c r="H118" s="106"/>
       <c r="I118" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J118" s="106"/>
       <c r="K118" s="129"/>
       <c r="L118" s="75" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="M118" s="67" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="119" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5027,10 +5027,10 @@
       <c r="J119" s="106"/>
       <c r="K119" s="129"/>
       <c r="L119" s="75" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="M119" s="67" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="120" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -5048,21 +5048,21 @@
       <c r="J120" s="107"/>
       <c r="K120" s="130"/>
       <c r="L120" s="75" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="M120" s="67" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="121" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A121" s="93" t="s">
+        <v>132</v>
+      </c>
+      <c r="B121" s="93" t="s">
+        <v>132</v>
+      </c>
+      <c r="C121" s="108" t="s">
         <v>133</v>
-      </c>
-      <c r="B121" s="93" t="s">
-        <v>133</v>
-      </c>
-      <c r="C121" s="108" t="s">
-        <v>134</v>
       </c>
       <c r="D121" s="55"/>
       <c r="E121" s="105" t="s">
@@ -5078,19 +5078,19 @@
         <v>59</v>
       </c>
       <c r="I121" s="10" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="J121" s="105" t="s">
         <v>60</v>
       </c>
       <c r="K121" s="99" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="L121" s="75" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="M121" s="67" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="122" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5103,15 +5103,15 @@
       <c r="G122" s="106"/>
       <c r="H122" s="106"/>
       <c r="I122" s="13" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="J122" s="106"/>
       <c r="K122" s="100"/>
       <c r="L122" s="75" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="M122" s="67" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="123" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5124,15 +5124,15 @@
       <c r="G123" s="106"/>
       <c r="H123" s="106"/>
       <c r="I123" s="13" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J123" s="106"/>
       <c r="K123" s="100"/>
       <c r="L123" s="75" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="M123" s="67" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="124" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5145,15 +5145,15 @@
       <c r="G124" s="106"/>
       <c r="H124" s="106"/>
       <c r="I124" s="12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J124" s="106"/>
       <c r="K124" s="100"/>
       <c r="L124" s="75" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="M124" s="67" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="125" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5166,15 +5166,15 @@
       <c r="G125" s="106"/>
       <c r="H125" s="106"/>
       <c r="I125" s="25" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="J125" s="106"/>
       <c r="K125" s="100"/>
       <c r="L125" s="75" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="M125" s="67" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="126" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -5187,26 +5187,26 @@
       <c r="G126" s="107"/>
       <c r="H126" s="107"/>
       <c r="I126" s="30" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="J126" s="107"/>
       <c r="K126" s="101"/>
       <c r="L126" s="75" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="M126" s="67" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="127" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="93" t="s">
+        <v>134</v>
+      </c>
+      <c r="B127" s="93" t="s">
+        <v>134</v>
+      </c>
+      <c r="C127" s="108" t="s">
         <v>135</v>
-      </c>
-      <c r="B127" s="93" t="s">
-        <v>135</v>
-      </c>
-      <c r="C127" s="108" t="s">
-        <v>136</v>
       </c>
       <c r="D127" s="55"/>
       <c r="E127" s="105" t="s">
@@ -5222,19 +5222,19 @@
         <v>63</v>
       </c>
       <c r="I127" s="37" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="J127" s="105" t="s">
         <v>64</v>
       </c>
       <c r="K127" s="99" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="L127" s="75" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="M127" s="67" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="128" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5247,15 +5247,15 @@
       <c r="G128" s="106"/>
       <c r="H128" s="106"/>
       <c r="I128" s="16" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="J128" s="106"/>
       <c r="K128" s="100"/>
       <c r="L128" s="75" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="M128" s="67" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="129" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5268,15 +5268,15 @@
       <c r="G129" s="106"/>
       <c r="H129" s="106"/>
       <c r="I129" s="13" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="J129" s="106"/>
       <c r="K129" s="100"/>
       <c r="L129" s="75" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="M129" s="67" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="130" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5289,15 +5289,15 @@
       <c r="G130" s="106"/>
       <c r="H130" s="106"/>
       <c r="I130" s="13" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J130" s="106"/>
       <c r="K130" s="100"/>
       <c r="L130" s="75" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="M130" s="67" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="131" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5310,15 +5310,15 @@
       <c r="G131" s="106"/>
       <c r="H131" s="106"/>
       <c r="I131" s="13" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J131" s="106"/>
       <c r="K131" s="100"/>
       <c r="L131" s="75" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="M131" s="67" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="132" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -5331,26 +5331,26 @@
       <c r="G132" s="107"/>
       <c r="H132" s="107"/>
       <c r="I132" s="12" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J132" s="107"/>
       <c r="K132" s="101"/>
       <c r="L132" s="75" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="M132" s="67" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="133" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A133" s="93" t="s">
+        <v>136</v>
+      </c>
+      <c r="B133" s="93" t="s">
+        <v>136</v>
+      </c>
+      <c r="C133" s="108" t="s">
         <v>137</v>
-      </c>
-      <c r="B133" s="93" t="s">
-        <v>137</v>
-      </c>
-      <c r="C133" s="108" t="s">
-        <v>138</v>
       </c>
       <c r="D133" s="108"/>
       <c r="E133" s="105" t="s">
@@ -5366,19 +5366,19 @@
         <v>67</v>
       </c>
       <c r="I133" s="10" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="J133" s="38" t="s">
         <v>68</v>
       </c>
       <c r="K133" s="99" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="L133" s="75" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="M133" s="67" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="134" spans="1:13" ht="26" x14ac:dyDescent="0.2">
@@ -5391,20 +5391,20 @@
       <c r="G134" s="106"/>
       <c r="H134" s="106"/>
       <c r="I134" s="11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J134" s="39" t="s">
         <v>69</v>
       </c>
       <c r="K134" s="100"/>
       <c r="L134" s="75" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="M134" s="67" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="135" spans="1:13" ht="24" x14ac:dyDescent="0.2">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A135" s="94"/>
       <c r="B135" s="94"/>
       <c r="C135" s="109"/>
@@ -5414,17 +5414,17 @@
       <c r="G135" s="106"/>
       <c r="H135" s="106"/>
       <c r="I135" s="12" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="J135" s="14" t="s">
-        <v>165</v>
+        <v>300</v>
       </c>
       <c r="K135" s="100"/>
       <c r="L135" s="75" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="M135" s="67" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="136" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5437,15 +5437,15 @@
       <c r="G136" s="106"/>
       <c r="H136" s="106"/>
       <c r="I136" s="12" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="J136" s="19"/>
       <c r="K136" s="100"/>
       <c r="L136" s="75" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="M136" s="67" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="137" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5458,15 +5458,15 @@
       <c r="G137" s="106"/>
       <c r="H137" s="106"/>
       <c r="I137" s="25" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="J137" s="19"/>
       <c r="K137" s="100"/>
       <c r="L137" s="75" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="M137" s="67" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="138" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5479,15 +5479,15 @@
       <c r="G138" s="106"/>
       <c r="H138" s="106"/>
       <c r="I138" s="13" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J138" s="19"/>
       <c r="K138" s="100"/>
       <c r="L138" s="75" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="M138" s="67" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="139" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5500,15 +5500,15 @@
       <c r="G139" s="106"/>
       <c r="H139" s="106"/>
       <c r="I139" s="13" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="J139" s="19"/>
       <c r="K139" s="100"/>
       <c r="L139" s="75" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="M139" s="67" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="140" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5521,15 +5521,15 @@
       <c r="G140" s="106"/>
       <c r="H140" s="106"/>
       <c r="I140" s="16" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J140" s="19"/>
       <c r="K140" s="100"/>
       <c r="L140" s="75" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="M140" s="67" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="141" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5542,15 +5542,15 @@
       <c r="G141" s="106"/>
       <c r="H141" s="106"/>
       <c r="I141" s="13" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J141" s="19"/>
       <c r="K141" s="100"/>
       <c r="L141" s="75" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="M141" s="67" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="142" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5563,15 +5563,15 @@
       <c r="G142" s="106"/>
       <c r="H142" s="106"/>
       <c r="I142" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J142" s="19"/>
       <c r="K142" s="100"/>
       <c r="L142" s="75" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="M142" s="67" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="143" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -5584,26 +5584,26 @@
       <c r="G143" s="107"/>
       <c r="H143" s="107"/>
       <c r="I143" s="30" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="J143" s="20"/>
       <c r="K143" s="101"/>
       <c r="L143" s="75" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="M143" s="67" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="144" spans="1:13" ht="59" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="93" t="s">
+        <v>138</v>
+      </c>
+      <c r="B144" s="93" t="s">
+        <v>138</v>
+      </c>
+      <c r="C144" s="108" t="s">
         <v>139</v>
-      </c>
-      <c r="B144" s="93" t="s">
-        <v>139</v>
-      </c>
-      <c r="C144" s="108" t="s">
-        <v>140</v>
       </c>
       <c r="D144" s="108"/>
       <c r="E144" s="105" t="s">
@@ -5623,13 +5623,13 @@
         <v>73</v>
       </c>
       <c r="K144" s="99" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="L144" s="75" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="M144" s="67" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
     </row>
     <row r="145" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5645,10 +5645,10 @@
       <c r="J145" s="106"/>
       <c r="K145" s="100"/>
       <c r="L145" s="75" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="M145" s="67" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
     </row>
     <row r="146" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -5664,21 +5664,21 @@
       <c r="J146" s="107"/>
       <c r="K146" s="101"/>
       <c r="L146" s="75" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="M146" s="67" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
     </row>
     <row r="147" spans="1:13" ht="79" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A147" s="62" t="s">
+        <v>140</v>
+      </c>
+      <c r="B147" s="54" t="s">
+        <v>140</v>
+      </c>
+      <c r="C147" s="54" t="s">
         <v>141</v>
-      </c>
-      <c r="B147" s="54" t="s">
-        <v>141</v>
-      </c>
-      <c r="C147" s="54" t="s">
-        <v>142</v>
       </c>
       <c r="D147" s="54"/>
       <c r="E147" s="41" t="s">
@@ -5694,30 +5694,30 @@
         <v>77</v>
       </c>
       <c r="I147" s="42" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="J147" s="41" t="s">
         <v>78</v>
       </c>
       <c r="K147" s="65" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="L147" s="75" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="M147" s="67" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
     </row>
     <row r="148" spans="1:13" ht="24" x14ac:dyDescent="0.2">
       <c r="A148" s="89" t="s">
+        <v>142</v>
+      </c>
+      <c r="B148" s="93" t="s">
+        <v>142</v>
+      </c>
+      <c r="C148" s="108" t="s">
         <v>143</v>
-      </c>
-      <c r="B148" s="93" t="s">
-        <v>143</v>
-      </c>
-      <c r="C148" s="108" t="s">
-        <v>144</v>
       </c>
       <c r="D148" s="108"/>
       <c r="E148" s="105" t="s">
@@ -5733,19 +5733,19 @@
         <v>81</v>
       </c>
       <c r="I148" s="43" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="J148" s="105" t="s">
         <v>82</v>
       </c>
       <c r="K148" s="99" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="L148" s="75" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="M148" s="67" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="149" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5758,15 +5758,15 @@
       <c r="G149" s="106"/>
       <c r="H149" s="106"/>
       <c r="I149" s="44" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="J149" s="106"/>
       <c r="K149" s="100"/>
       <c r="L149" s="75" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="M149" s="67" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="150" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5779,15 +5779,15 @@
       <c r="G150" s="106"/>
       <c r="H150" s="106"/>
       <c r="I150" s="45" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="J150" s="106"/>
       <c r="K150" s="100"/>
       <c r="L150" s="75" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="M150" s="67" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="151" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5800,15 +5800,15 @@
       <c r="G151" s="106"/>
       <c r="H151" s="106"/>
       <c r="I151" s="44" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J151" s="106"/>
       <c r="K151" s="100"/>
       <c r="L151" s="75" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="M151" s="67" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="152" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5821,15 +5821,15 @@
       <c r="G152" s="106"/>
       <c r="H152" s="106"/>
       <c r="I152" s="46" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J152" s="106"/>
       <c r="K152" s="100"/>
       <c r="L152" s="75" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="M152" s="67" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="153" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5842,15 +5842,15 @@
       <c r="G153" s="106"/>
       <c r="H153" s="106"/>
       <c r="I153" s="45" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J153" s="106"/>
       <c r="K153" s="100"/>
       <c r="L153" s="75" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="M153" s="67" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="154" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5863,15 +5863,15 @@
       <c r="G154" s="106"/>
       <c r="H154" s="106"/>
       <c r="I154" s="18" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="J154" s="106"/>
       <c r="K154" s="100"/>
       <c r="L154" s="75" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="M154" s="67" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="155" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5887,10 +5887,10 @@
       <c r="J155" s="106"/>
       <c r="K155" s="100"/>
       <c r="L155" s="75" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="M155" s="67" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="156" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -5906,21 +5906,21 @@
       <c r="J156" s="107"/>
       <c r="K156" s="101"/>
       <c r="L156" s="75" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="M156" s="67" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="157" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A157" s="86" t="s">
+        <v>144</v>
+      </c>
+      <c r="B157" s="102" t="s">
+        <v>144</v>
+      </c>
+      <c r="C157" s="111" t="s">
         <v>145</v>
-      </c>
-      <c r="B157" s="102" t="s">
-        <v>145</v>
-      </c>
-      <c r="C157" s="111" t="s">
-        <v>146</v>
       </c>
       <c r="D157" s="111"/>
       <c r="E157" s="105"/>
@@ -5930,19 +5930,19 @@
       <c r="G157" s="105"/>
       <c r="H157" s="105"/>
       <c r="I157" s="47" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="J157" s="105" t="s">
         <v>84</v>
       </c>
       <c r="K157" s="99" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="L157" s="75" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="M157" s="67" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
     </row>
     <row r="158" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5955,15 +5955,15 @@
       <c r="G158" s="106"/>
       <c r="H158" s="106"/>
       <c r="I158" s="44" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J158" s="106"/>
       <c r="K158" s="100"/>
       <c r="L158" s="75" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="M158" s="67" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
     </row>
     <row r="159" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5976,15 +5976,15 @@
       <c r="G159" s="106"/>
       <c r="H159" s="106"/>
       <c r="I159" s="46" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J159" s="106"/>
       <c r="K159" s="100"/>
       <c r="L159" s="75" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="M159" s="67" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
     </row>
     <row r="160" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5997,15 +5997,15 @@
       <c r="G160" s="106"/>
       <c r="H160" s="106"/>
       <c r="I160" s="44" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J160" s="106"/>
       <c r="K160" s="100"/>
       <c r="L160" s="75" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="M160" s="67" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
     </row>
     <row r="161" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -6018,15 +6018,15 @@
       <c r="G161" s="106"/>
       <c r="H161" s="106"/>
       <c r="I161" s="44" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="J161" s="106"/>
       <c r="K161" s="100"/>
       <c r="L161" s="75" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="M161" s="67" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
     </row>
     <row r="162" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -6039,15 +6039,15 @@
       <c r="G162" s="106"/>
       <c r="H162" s="106"/>
       <c r="I162" s="46" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J162" s="106"/>
       <c r="K162" s="100"/>
       <c r="L162" s="75" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="M162" s="67" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
     </row>
     <row r="163" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -6060,15 +6060,15 @@
       <c r="G163" s="106"/>
       <c r="H163" s="106"/>
       <c r="I163" s="46" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J163" s="106"/>
       <c r="K163" s="100"/>
       <c r="L163" s="75" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="M163" s="67" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
     </row>
     <row r="164" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -6081,15 +6081,15 @@
       <c r="G164" s="106"/>
       <c r="H164" s="106"/>
       <c r="I164" s="48" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J164" s="106"/>
       <c r="K164" s="100"/>
       <c r="L164" s="75" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="M164" s="67" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
     </row>
     <row r="165" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -6107,21 +6107,21 @@
       <c r="J165" s="119"/>
       <c r="K165" s="114"/>
       <c r="L165" s="75" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="M165" s="67" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
     </row>
     <row r="166" spans="1:13" ht="53" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="92" t="s">
+        <v>146</v>
+      </c>
+      <c r="B166" s="115" t="s">
+        <v>146</v>
+      </c>
+      <c r="C166" s="124" t="s">
         <v>147</v>
-      </c>
-      <c r="B166" s="115" t="s">
-        <v>147</v>
-      </c>
-      <c r="C166" s="124" t="s">
-        <v>148</v>
       </c>
       <c r="D166" s="124"/>
       <c r="E166" s="116" t="s">
@@ -6134,22 +6134,22 @@
         <v>86</v>
       </c>
       <c r="H166" s="116" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I166" s="50" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="J166" s="116" t="s">
         <v>87</v>
       </c>
       <c r="K166" s="117" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="L166" s="75" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="M166" s="67" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="167" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -6162,15 +6162,15 @@
       <c r="G167" s="106"/>
       <c r="H167" s="106"/>
       <c r="I167" s="11" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="J167" s="106"/>
       <c r="K167" s="100"/>
       <c r="L167" s="75" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="M167" s="67" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="168" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -6183,26 +6183,26 @@
       <c r="G168" s="107"/>
       <c r="H168" s="107"/>
       <c r="I168" s="51" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="J168" s="107"/>
       <c r="K168" s="101"/>
       <c r="L168" s="75" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="M168" s="67" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="169" spans="1:13" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="89" t="s">
+        <v>148</v>
+      </c>
+      <c r="B169" s="93" t="s">
+        <v>148</v>
+      </c>
+      <c r="C169" s="108" t="s">
         <v>149</v>
-      </c>
-      <c r="B169" s="93" t="s">
-        <v>149</v>
-      </c>
-      <c r="C169" s="108" t="s">
-        <v>150</v>
       </c>
       <c r="D169" s="108"/>
       <c r="E169" s="105" t="s">
@@ -6215,22 +6215,22 @@
         <v>88</v>
       </c>
       <c r="H169" s="105" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I169" s="10" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="J169" s="105" t="s">
         <v>89</v>
       </c>
       <c r="K169" s="99" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="L169" s="75" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="M169" s="67" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="170" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -6243,15 +6243,15 @@
       <c r="G170" s="106"/>
       <c r="H170" s="106"/>
       <c r="I170" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J170" s="106"/>
       <c r="K170" s="100"/>
       <c r="L170" s="75" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="M170" s="67" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="171" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -6267,10 +6267,10 @@
       <c r="J171" s="106"/>
       <c r="K171" s="100"/>
       <c r="L171" s="75" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="M171" s="67" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="172" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -6286,21 +6286,21 @@
       <c r="J172" s="107"/>
       <c r="K172" s="101"/>
       <c r="L172" s="75" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="M172" s="67" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="173" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A173" s="86" t="s">
+        <v>150</v>
+      </c>
+      <c r="B173" s="102" t="s">
+        <v>150</v>
+      </c>
+      <c r="C173" s="111" t="s">
         <v>151</v>
-      </c>
-      <c r="B173" s="102" t="s">
-        <v>151</v>
-      </c>
-      <c r="C173" s="111" t="s">
-        <v>152</v>
       </c>
       <c r="D173" s="111"/>
       <c r="E173" s="105"/>
@@ -6308,19 +6308,19 @@
       <c r="G173" s="40"/>
       <c r="H173" s="4"/>
       <c r="I173" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J173" s="105" t="s">
         <v>92</v>
       </c>
       <c r="K173" s="99" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="L173" s="75" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="M173" s="67" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="174" spans="1:13" ht="39" x14ac:dyDescent="0.2">
@@ -6339,15 +6339,15 @@
         <v>91</v>
       </c>
       <c r="I174" s="24" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J174" s="106"/>
       <c r="K174" s="100"/>
       <c r="L174" s="75" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="M174" s="67" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="175" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -6360,15 +6360,15 @@
       <c r="G175" s="19"/>
       <c r="H175" s="29"/>
       <c r="I175" s="16" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="J175" s="106"/>
       <c r="K175" s="100"/>
       <c r="L175" s="75" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="M175" s="67" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="176" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -6381,15 +6381,15 @@
       <c r="G176" s="19"/>
       <c r="H176" s="19"/>
       <c r="I176" s="12" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="J176" s="106"/>
       <c r="K176" s="100"/>
       <c r="L176" s="75" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="M176" s="67" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="177" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -6402,15 +6402,15 @@
       <c r="G177" s="19"/>
       <c r="H177" s="19"/>
       <c r="I177" s="13" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="J177" s="106"/>
       <c r="K177" s="100"/>
       <c r="L177" s="75" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="M177" s="67" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="178" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">

--- a/RWF_Entourage.xlsx
+++ b/RWF_Entourage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise-Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="265" documentId="8_{A60C4C07-97B7-C84A-9A2B-5740B6758233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E0AEBA9-CC99-1D40-ACDA-1A6E8A6C3015}"/>
+  <xr:revisionPtr revIDLastSave="279" documentId="8_{A60C4C07-97B7-C84A-9A2B-5740B6758233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13C1CDAC-5901-F645-BB2F-B3BD95BB498F}"/>
   <bookViews>
     <workbookView xWindow="9000" yWindow="4900" windowWidth="33100" windowHeight="15420" xr2:uid="{3F2EE892-A619-2747-9F28-51C106355EDF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="300">
   <si>
     <t>La galaxie Fassbinder</t>
   </si>
@@ -253,9 +253,6 @@
     <t>Compagne de Fassbinder à partir de la seconde moitié des années 1970 ; communauté de travail et de vie jusqu’en 1982</t>
   </si>
   <si>
-    <t>Présence également dans la restauration et la mémoire de l’œuvre après 1982</t>
-  </si>
-  <si>
     <t>Jeu, relation intime, présence biographique</t>
   </si>
   <si>
@@ -409,15 +406,6 @@
     <t xml:space="preserve">Prenez garde à la sainte putain (1971) </t>
   </si>
   <si>
-    <t xml:space="preserve">Prenez garde à la sainte putain (1971), </t>
-  </si>
-  <si>
-    <t>Pionniers à Ingoldstad (1971) - TV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L’Ombre des anges, à partir de la Pionniers à Ingoldstad (1971) - TVèce de Rainer Werner Fassbinder, L’Ordure la ville et la mort. </t>
-  </si>
-  <si>
     <t>Le marchand des quatre saisons (1972)</t>
   </si>
   <si>
@@ -667,12 +655,6 @@
     <t>La Femme du chef de gare  (1977) - TV</t>
   </si>
   <si>
-    <t>La Femme du chef de gare  (1977) - TV Despair (1978) (1978)</t>
-  </si>
-  <si>
-    <t>Despair (1978) (1978) L’Allemagne en automne  (1978)</t>
-  </si>
-  <si>
     <t>L’Allemagne en automne  (1978)</t>
   </si>
   <si>
@@ -697,25 +679,10 @@
     <t xml:space="preserve">Maman Küsters s’en va au ciel  (1975) </t>
   </si>
   <si>
-    <t>L’Amour est plus froid que la mort  (1969), Les Dieux de la peste  (1970), Pourquoi M. R. est-il atteint de folie meurtrière (1970)</t>
-  </si>
-  <si>
     <t>L’Amour est plus froid que la mort  (1969)</t>
   </si>
   <si>
-    <t>L’Amour est plus froid que la mort  (1969), Les Dieux de la peste  (1970), Le Soldat américain  (1970), Whity (1971),</t>
-  </si>
-  <si>
-    <t>L’Amour est plus froid que la mort  (1969), Les Dieux de la peste  (1970),</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le Le bouc  (1969) (1969) </t>
-  </si>
-  <si>
     <t>Le bouc  (1969)</t>
-  </si>
-  <si>
-    <t>L’Amour est plus froid que la mort  (1969),  Le bouc  (1969), Pourquoi M. R. est-il atteint de folie meurtrière (1970), Le Soldat américain  (1970), Whity (1971),</t>
   </si>
   <si>
     <t>L’Amour est plus froid que la mort  (1969), Le bouc  (1969), Les Dieux de la peste  (1970), Rio das Mortes, Prenez garde à la sainte putain (1971), M4, Les Larmes amères de Petra von Kant (1972)</t>
@@ -993,6 +960,39 @@
   </si>
   <si>
     <t>Carstensen.jpg</t>
+  </si>
+  <si>
+    <t>Le Le bouc  (1969)</t>
+  </si>
+  <si>
+    <t>Despair (1978)</t>
+  </si>
+  <si>
+    <t>Pionniers à Ingolstadt (1971) - TV</t>
+  </si>
+  <si>
+    <t>Despair (1978) ; L’Allemagne en automne  (1978)</t>
+  </si>
+  <si>
+    <t>L’Amour est plus froid que la mort  (1969); Les Dieux de la peste  (1970) ; Pourquoi M. R. est-il atteint de folie meurtrière (1970)</t>
+  </si>
+  <si>
+    <t>L’Amour est plus froid que la mort  (1969); Les Dieux de la peste  (1970) ; Le Soldat américain  (1970); Whity (1971)</t>
+  </si>
+  <si>
+    <t>Prenez garde à la sainte putain (1971)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Femme du chef de gare  (1977) - TV ; Despair (1978) </t>
+  </si>
+  <si>
+    <t>L’Amour est plus froid que la mort  (1969);  Le bouc  (1969); Pourquoi M. R. est-il atteint de folie meurtrière (1970); Le Soldat américain  (1970); Whity (1971);</t>
+  </si>
+  <si>
+    <t>L’Ombre des anges</t>
+  </si>
+  <si>
+    <t>L’Amour est plus froid que la mort  (1969); Les Dieux de la peste  (1970),</t>
   </si>
 </sst>
 </file>
@@ -2412,18 +2412,18 @@
       <c r="C1" s="53"/>
       <c r="D1" s="53"/>
       <c r="L1" s="63" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="M1" s="63" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="L2" s="63" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="M2" s="63" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -2433,16 +2433,16 @@
     </row>
     <row r="4" spans="1:13" ht="40" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="61" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>2</v>
@@ -2466,21 +2466,21 @@
         <v>8</v>
       </c>
       <c r="L4" s="69" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="M4" s="70" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="134" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B5" s="81" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="C5" s="87" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D5" s="55"/>
       <c r="E5" s="84" t="s">
@@ -2496,19 +2496,19 @@
         <v>12</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>205</v>
+        <v>289</v>
       </c>
       <c r="J5" s="84" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="K5" s="78" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L5" s="128" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="M5" s="131" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
@@ -2521,7 +2521,7 @@
       <c r="G6" s="85"/>
       <c r="H6" s="85"/>
       <c r="I6" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J6" s="85"/>
       <c r="K6" s="79"/>
@@ -2538,7 +2538,7 @@
       <c r="G7" s="85"/>
       <c r="H7" s="85"/>
       <c r="I7" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J7" s="85"/>
       <c r="K7" s="79"/>
@@ -2555,7 +2555,7 @@
       <c r="G8" s="85"/>
       <c r="H8" s="85"/>
       <c r="I8" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J8" s="85"/>
       <c r="K8" s="79"/>
@@ -2572,7 +2572,7 @@
       <c r="G9" s="85"/>
       <c r="H9" s="85"/>
       <c r="I9" s="7" t="s">
-        <v>106</v>
+        <v>291</v>
       </c>
       <c r="J9" s="85"/>
       <c r="K9" s="79"/>
@@ -2589,7 +2589,7 @@
       <c r="G10" s="85"/>
       <c r="H10" s="85"/>
       <c r="I10" s="6" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="J10" s="85"/>
       <c r="K10" s="79"/>
@@ -2606,7 +2606,7 @@
       <c r="G11" s="85"/>
       <c r="H11" s="85"/>
       <c r="I11" s="8" t="s">
-        <v>186</v>
+        <v>290</v>
       </c>
       <c r="J11" s="85"/>
       <c r="K11" s="79"/>
@@ -2623,7 +2623,7 @@
       <c r="G12" s="85"/>
       <c r="H12" s="85"/>
       <c r="I12" s="8" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="J12" s="85"/>
       <c r="K12" s="79"/>
@@ -2640,7 +2640,7 @@
       <c r="G13" s="85"/>
       <c r="H13" s="85"/>
       <c r="I13" s="6" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J13" s="85"/>
       <c r="K13" s="79"/>
@@ -2657,7 +2657,7 @@
       <c r="G14" s="85"/>
       <c r="H14" s="85"/>
       <c r="I14" s="6" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="J14" s="85"/>
       <c r="K14" s="79"/>
@@ -2674,7 +2674,7 @@
       <c r="G15" s="86"/>
       <c r="H15" s="86"/>
       <c r="I15" s="9" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="J15" s="86"/>
       <c r="K15" s="80"/>
@@ -2683,13 +2683,13 @@
     </row>
     <row r="16" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="134" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B16" s="81" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C16" s="87" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D16" s="55"/>
       <c r="E16" s="84" t="s">
@@ -2705,19 +2705,19 @@
         <v>16</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J16" s="84" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="K16" s="78" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L16" s="66" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="M16" s="67" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -2730,15 +2730,15 @@
       <c r="G17" s="85"/>
       <c r="H17" s="85"/>
       <c r="I17" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J17" s="85"/>
       <c r="K17" s="79"/>
       <c r="L17" s="66" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="M17" s="67" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -2751,15 +2751,15 @@
       <c r="G18" s="85"/>
       <c r="H18" s="85"/>
       <c r="I18" s="12" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="J18" s="85"/>
       <c r="K18" s="79"/>
       <c r="L18" s="66" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="M18" s="67" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -2772,15 +2772,15 @@
       <c r="G19" s="85"/>
       <c r="H19" s="85"/>
       <c r="I19" s="13" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="J19" s="85"/>
       <c r="K19" s="79"/>
       <c r="L19" s="66" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="M19" s="67" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -2793,15 +2793,15 @@
       <c r="G20" s="85"/>
       <c r="H20" s="85"/>
       <c r="I20" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="J20" s="85"/>
       <c r="K20" s="79"/>
       <c r="L20" s="66" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="M20" s="67" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -2814,15 +2814,15 @@
       <c r="G21" s="85"/>
       <c r="H21" s="85"/>
       <c r="I21" s="13" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="J21" s="85"/>
       <c r="K21" s="79"/>
       <c r="L21" s="66" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="M21" s="67" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -2835,15 +2835,15 @@
       <c r="G22" s="85"/>
       <c r="H22" s="85"/>
       <c r="I22" s="13" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J22" s="85"/>
       <c r="K22" s="79"/>
       <c r="L22" s="66" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="M22" s="67" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -2856,15 +2856,15 @@
       <c r="G23" s="85"/>
       <c r="H23" s="85"/>
       <c r="I23" s="13" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="J23" s="85"/>
       <c r="K23" s="79"/>
       <c r="L23" s="66" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="M23" s="67" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -2877,15 +2877,15 @@
       <c r="G24" s="85"/>
       <c r="H24" s="85"/>
       <c r="I24" s="13" t="s">
-        <v>192</v>
+        <v>292</v>
       </c>
       <c r="J24" s="85"/>
       <c r="K24" s="79"/>
       <c r="L24" s="66" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="M24" s="67" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -2898,15 +2898,15 @@
       <c r="G25" s="85"/>
       <c r="H25" s="85"/>
       <c r="I25" s="13" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="J25" s="85"/>
       <c r="K25" s="79"/>
       <c r="L25" s="66" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="M25" s="67" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -2919,15 +2919,15 @@
       <c r="G26" s="85"/>
       <c r="H26" s="85"/>
       <c r="I26" s="11" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="J26" s="85"/>
       <c r="K26" s="79"/>
       <c r="L26" s="66" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="M26" s="67" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -2940,15 +2940,15 @@
       <c r="G27" s="85"/>
       <c r="H27" s="85"/>
       <c r="I27" s="14" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="J27" s="85"/>
       <c r="K27" s="79"/>
       <c r="L27" s="66" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="M27" s="67" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -2961,26 +2961,26 @@
       <c r="G28" s="86"/>
       <c r="H28" s="86"/>
       <c r="I28" s="15" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="J28" s="86"/>
       <c r="K28" s="80"/>
       <c r="L28" s="66" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="M28" s="67" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="134" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B29" s="81" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C29" s="87" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D29" s="55"/>
       <c r="E29" s="84" t="s">
@@ -2996,19 +2996,19 @@
         <v>20</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="J29" s="84" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="K29" s="78" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="L29" s="71" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="M29" s="72" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3021,15 +3021,15 @@
       <c r="G30" s="85"/>
       <c r="H30" s="85"/>
       <c r="I30" s="12" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="J30" s="85"/>
       <c r="K30" s="79"/>
       <c r="L30" s="74" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="M30" s="67" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3042,15 +3042,15 @@
       <c r="G31" s="85"/>
       <c r="H31" s="85"/>
       <c r="I31" s="16" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="J31" s="85"/>
       <c r="K31" s="79"/>
       <c r="L31" s="75" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="M31" s="67" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3063,15 +3063,15 @@
       <c r="G32" s="85"/>
       <c r="H32" s="85"/>
       <c r="I32" s="12" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="J32" s="85"/>
       <c r="K32" s="79"/>
       <c r="L32" s="75" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="M32" s="67" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -3084,26 +3084,26 @@
       <c r="G33" s="86"/>
       <c r="H33" s="86"/>
       <c r="I33" s="17" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="J33" s="86"/>
       <c r="K33" s="80"/>
       <c r="L33" s="76" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="M33" s="73" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A34" s="81" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B34" s="81" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C34" s="87" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D34" s="55"/>
       <c r="E34" s="84" t="s">
@@ -3119,19 +3119,19 @@
         <v>24</v>
       </c>
       <c r="I34" s="21" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="J34" s="84" t="s">
         <v>25</v>
       </c>
       <c r="K34" s="90" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L34" s="74" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="M34" s="72" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="24" x14ac:dyDescent="0.2">
@@ -3146,15 +3146,15 @@
       </c>
       <c r="H35" s="85"/>
       <c r="I35" s="13" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="J35" s="85"/>
       <c r="K35" s="91"/>
       <c r="L35" s="75" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="M35" s="67" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3167,15 +3167,15 @@
       <c r="G36" s="19"/>
       <c r="H36" s="85"/>
       <c r="I36" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="J36" s="85"/>
       <c r="K36" s="91"/>
       <c r="L36" s="75" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="M36" s="67" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3188,15 +3188,15 @@
       <c r="G37" s="19"/>
       <c r="H37" s="85"/>
       <c r="I37" s="13" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="J37" s="85"/>
       <c r="K37" s="91"/>
       <c r="L37" s="75" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="M37" s="67" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -3212,21 +3212,21 @@
       <c r="J38" s="86"/>
       <c r="K38" s="92"/>
       <c r="L38" s="76" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="M38" s="73" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A39" s="81" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B39" s="81" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C39" s="87" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D39" s="55"/>
       <c r="E39" s="84" t="s">
@@ -3242,19 +3242,19 @@
         <v>29</v>
       </c>
       <c r="I39" s="23" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>30</v>
       </c>
       <c r="K39" s="78" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="L39" s="131" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="M39" s="67" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.2">
@@ -3267,7 +3267,7 @@
       <c r="G40" s="85"/>
       <c r="H40" s="85"/>
       <c r="I40" s="24" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="J40" s="26" t="s">
         <v>31</v>
@@ -3286,7 +3286,7 @@
       <c r="G41" s="85"/>
       <c r="H41" s="85"/>
       <c r="I41" s="13" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="J41" s="19"/>
       <c r="K41" s="79"/>
@@ -3303,7 +3303,7 @@
       <c r="G42" s="85"/>
       <c r="H42" s="85"/>
       <c r="I42" s="25" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="J42" s="19"/>
       <c r="K42" s="79"/>
@@ -3320,7 +3320,7 @@
       <c r="G43" s="85"/>
       <c r="H43" s="85"/>
       <c r="I43" s="13" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J43" s="19"/>
       <c r="K43" s="79"/>
@@ -3337,7 +3337,7 @@
       <c r="G44" s="85"/>
       <c r="H44" s="85"/>
       <c r="I44" s="13" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="J44" s="19"/>
       <c r="K44" s="79"/>
@@ -3354,7 +3354,7 @@
       <c r="G45" s="86"/>
       <c r="H45" s="86"/>
       <c r="I45" s="17" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="J45" s="20"/>
       <c r="K45" s="80"/>
@@ -3363,13 +3363,13 @@
     </row>
     <row r="46" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A46" s="81" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B46" s="81" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C46" s="87" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D46" s="55"/>
       <c r="E46" s="84" t="s">
@@ -3379,25 +3379,25 @@
         <v>21</v>
       </c>
       <c r="G46" s="84" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="H46" s="84" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="J46" s="84" t="s">
         <v>33</v>
       </c>
       <c r="K46" s="78" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L46" s="75" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="M46" s="67" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3410,15 +3410,15 @@
       <c r="G47" s="85"/>
       <c r="H47" s="85"/>
       <c r="I47" s="12" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="J47" s="85"/>
       <c r="K47" s="79"/>
       <c r="L47" s="75" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="M47" s="67" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3431,15 +3431,15 @@
       <c r="G48" s="85"/>
       <c r="H48" s="85"/>
       <c r="I48" s="27" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="J48" s="85"/>
       <c r="K48" s="79"/>
       <c r="L48" s="75" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="M48" s="67" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3452,15 +3452,15 @@
       <c r="G49" s="85"/>
       <c r="H49" s="85"/>
       <c r="I49" s="16" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="J49" s="85"/>
       <c r="K49" s="79"/>
       <c r="L49" s="75" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="M49" s="67" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3473,15 +3473,15 @@
       <c r="G50" s="85"/>
       <c r="H50" s="85"/>
       <c r="I50" s="13" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="J50" s="85"/>
       <c r="K50" s="79"/>
       <c r="L50" s="75" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="M50" s="67" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3494,15 +3494,15 @@
       <c r="G51" s="85"/>
       <c r="H51" s="85"/>
       <c r="I51" s="13" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="J51" s="85"/>
       <c r="K51" s="79"/>
       <c r="L51" s="75" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="M51" s="67" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3515,15 +3515,15 @@
       <c r="G52" s="85"/>
       <c r="H52" s="85"/>
       <c r="I52" s="11" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="J52" s="85"/>
       <c r="K52" s="79"/>
       <c r="L52" s="75" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="M52" s="67" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -3539,21 +3539,21 @@
       <c r="J53" s="86"/>
       <c r="K53" s="80"/>
       <c r="L53" s="75" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="M53" s="67" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A54" s="81" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B54" s="81" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C54" s="87" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D54" s="55"/>
       <c r="E54" s="84" t="s">
@@ -3569,19 +3569,19 @@
         <v>36</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>201</v>
+        <v>293</v>
       </c>
       <c r="J54" s="84" t="s">
         <v>37</v>
       </c>
       <c r="K54" s="78" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L54" s="75" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="M54" s="67" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3594,15 +3594,15 @@
       <c r="G55" s="85"/>
       <c r="H55" s="85"/>
       <c r="I55" s="11" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="J55" s="85"/>
       <c r="K55" s="79"/>
       <c r="L55" s="75" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="M55" s="67" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
     </row>
     <row r="56" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3615,15 +3615,15 @@
       <c r="G56" s="85"/>
       <c r="H56" s="85"/>
       <c r="I56" s="12" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="J56" s="85"/>
       <c r="K56" s="79"/>
       <c r="L56" s="75" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="M56" s="67" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3636,15 +3636,15 @@
       <c r="G57" s="85"/>
       <c r="H57" s="85"/>
       <c r="I57" s="13" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="J57" s="85"/>
       <c r="K57" s="79"/>
       <c r="L57" s="75" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="M57" s="67" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3657,15 +3657,15 @@
       <c r="G58" s="85"/>
       <c r="H58" s="85"/>
       <c r="I58" s="16" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="J58" s="85"/>
       <c r="K58" s="79"/>
       <c r="L58" s="75" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="M58" s="67" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3678,15 +3678,15 @@
       <c r="G59" s="85"/>
       <c r="H59" s="85"/>
       <c r="I59" s="13" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="J59" s="85"/>
       <c r="K59" s="79"/>
       <c r="L59" s="75" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="M59" s="67" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3699,15 +3699,15 @@
       <c r="G60" s="85"/>
       <c r="H60" s="85"/>
       <c r="I60" s="13" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J60" s="85"/>
       <c r="K60" s="79"/>
       <c r="L60" s="75" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="M60" s="67" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3720,15 +3720,15 @@
       <c r="G61" s="85"/>
       <c r="H61" s="85"/>
       <c r="I61" s="13" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="J61" s="85"/>
       <c r="K61" s="79"/>
       <c r="L61" s="75" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="M61" s="67" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -3741,26 +3741,26 @@
       <c r="G62" s="86"/>
       <c r="H62" s="86"/>
       <c r="I62" s="28" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="J62" s="86"/>
       <c r="K62" s="80"/>
       <c r="L62" s="75" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="M62" s="67" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A63" s="81" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="B63" s="81" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="C63" s="87" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="D63" s="55"/>
       <c r="E63" s="96"/>
@@ -3778,13 +3778,13 @@
         <v>41</v>
       </c>
       <c r="K63" s="78" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L63" s="75" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="M63" s="67" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="26" x14ac:dyDescent="0.2">
@@ -3799,15 +3799,15 @@
       <c r="G64" s="97"/>
       <c r="H64" s="85"/>
       <c r="I64" s="11" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J64" s="85"/>
       <c r="K64" s="79"/>
       <c r="L64" s="75" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="M64" s="67" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3820,15 +3820,15 @@
       <c r="G65" s="97"/>
       <c r="H65" s="85"/>
       <c r="I65" s="25" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="J65" s="85"/>
       <c r="K65" s="79"/>
       <c r="L65" s="75" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="M65" s="67" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3841,15 +3841,15 @@
       <c r="G66" s="97"/>
       <c r="H66" s="85"/>
       <c r="I66" s="13" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="J66" s="85"/>
       <c r="K66" s="79"/>
       <c r="L66" s="75" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="M66" s="67" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3862,15 +3862,15 @@
       <c r="G67" s="97"/>
       <c r="H67" s="85"/>
       <c r="I67" s="13" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="J67" s="85"/>
       <c r="K67" s="79"/>
       <c r="L67" s="75" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="M67" s="67" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3883,15 +3883,15 @@
       <c r="G68" s="97"/>
       <c r="H68" s="85"/>
       <c r="I68" s="11" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="J68" s="85"/>
       <c r="K68" s="79"/>
       <c r="L68" s="75" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="M68" s="67" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3904,15 +3904,15 @@
       <c r="G69" s="97"/>
       <c r="H69" s="85"/>
       <c r="I69" s="25" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="J69" s="85"/>
       <c r="K69" s="79"/>
       <c r="L69" s="75" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="M69" s="67" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3925,15 +3925,15 @@
       <c r="G70" s="97"/>
       <c r="H70" s="85"/>
       <c r="I70" s="16" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="J70" s="85"/>
       <c r="K70" s="79"/>
       <c r="L70" s="75" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="M70" s="67" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3946,15 +3946,15 @@
       <c r="G71" s="97"/>
       <c r="H71" s="85"/>
       <c r="I71" s="13" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="J71" s="85"/>
       <c r="K71" s="79"/>
       <c r="L71" s="75" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="M71" s="67" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3967,15 +3967,15 @@
       <c r="G72" s="97"/>
       <c r="H72" s="85"/>
       <c r="I72" s="16" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="J72" s="85"/>
       <c r="K72" s="79"/>
       <c r="L72" s="75" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="M72" s="67" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -3988,15 +3988,15 @@
       <c r="G73" s="97"/>
       <c r="H73" s="85"/>
       <c r="I73" s="13" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="J73" s="85"/>
       <c r="K73" s="79"/>
       <c r="L73" s="75" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="M73" s="67" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4009,15 +4009,15 @@
       <c r="G74" s="97"/>
       <c r="H74" s="85"/>
       <c r="I74" s="11" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="J74" s="85"/>
       <c r="K74" s="79"/>
       <c r="L74" s="75" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="M74" s="67" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
     </row>
     <row r="75" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -4030,15 +4030,15 @@
       <c r="G75" s="98"/>
       <c r="H75" s="86"/>
       <c r="I75" s="30" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="J75" s="86"/>
       <c r="K75" s="80"/>
       <c r="L75" s="75" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="M75" s="67" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4061,19 +4061,19 @@
         <v>44</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="J76" s="84" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="K76" s="93" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="L76" s="75" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="M76" s="67" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
     </row>
     <row r="77" spans="1:13" ht="39" x14ac:dyDescent="0.2">
@@ -4088,15 +4088,15 @@
       <c r="G77" s="85"/>
       <c r="H77" s="85"/>
       <c r="I77" s="11" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="J77" s="85"/>
       <c r="K77" s="94"/>
       <c r="L77" s="75" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="M77" s="67" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
     </row>
     <row r="78" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4109,15 +4109,15 @@
       <c r="G78" s="85"/>
       <c r="H78" s="85"/>
       <c r="I78" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J78" s="85"/>
       <c r="K78" s="94"/>
       <c r="L78" s="75" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="M78" s="67" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
     </row>
     <row r="79" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4130,15 +4130,15 @@
       <c r="G79" s="85"/>
       <c r="H79" s="85"/>
       <c r="I79" s="31" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="J79" s="85"/>
       <c r="K79" s="94"/>
       <c r="L79" s="75" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="M79" s="67" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
     </row>
     <row r="80" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4151,15 +4151,15 @@
       <c r="G80" s="85"/>
       <c r="H80" s="85"/>
       <c r="I80" s="31" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="J80" s="85"/>
       <c r="K80" s="94"/>
       <c r="L80" s="75" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="M80" s="67" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
     </row>
     <row r="81" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4172,15 +4172,15 @@
       <c r="G81" s="85"/>
       <c r="H81" s="85"/>
       <c r="I81" s="13" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="J81" s="85"/>
       <c r="K81" s="94"/>
       <c r="L81" s="75" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="M81" s="67" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
     </row>
     <row r="82" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4193,15 +4193,15 @@
       <c r="G82" s="85"/>
       <c r="H82" s="85"/>
       <c r="I82" s="13" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="J82" s="85"/>
       <c r="K82" s="94"/>
       <c r="L82" s="75" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="M82" s="67" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4214,15 +4214,15 @@
       <c r="G83" s="85"/>
       <c r="H83" s="85"/>
       <c r="I83" s="13" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="J83" s="85"/>
       <c r="K83" s="94"/>
       <c r="L83" s="75" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="M83" s="67" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
     </row>
     <row r="84" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4235,15 +4235,15 @@
       <c r="G84" s="85"/>
       <c r="H84" s="85"/>
       <c r="I84" s="25" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J84" s="85"/>
       <c r="K84" s="94"/>
       <c r="L84" s="75" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="M84" s="67" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4256,15 +4256,15 @@
       <c r="G85" s="85"/>
       <c r="H85" s="85"/>
       <c r="I85" s="31" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="J85" s="85"/>
       <c r="K85" s="94"/>
       <c r="L85" s="75" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="M85" s="67" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -4277,26 +4277,26 @@
       <c r="G86" s="86"/>
       <c r="H86" s="86"/>
       <c r="I86" s="30" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="J86" s="86"/>
       <c r="K86" s="95"/>
       <c r="L86" s="75" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="M86" s="67" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
     </row>
     <row r="87" spans="1:13" ht="52" x14ac:dyDescent="0.2">
       <c r="A87" s="81" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B87" s="81" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C87" s="87" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D87" s="55"/>
       <c r="E87" s="84"/>
@@ -4308,19 +4308,19 @@
       </c>
       <c r="H87" s="84"/>
       <c r="I87" s="32" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="K87" s="90" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="L87" s="75" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="M87" s="67" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="26" x14ac:dyDescent="0.2">
@@ -4335,17 +4335,17 @@
       </c>
       <c r="H88" s="85"/>
       <c r="I88" s="13" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="J88" s="26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K88" s="91"/>
       <c r="L88" s="75" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="M88" s="67" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
     </row>
     <row r="89" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4358,15 +4358,15 @@
       <c r="G89" s="19"/>
       <c r="H89" s="85"/>
       <c r="I89" s="13" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="J89" s="19"/>
       <c r="K89" s="91"/>
       <c r="L89" s="75" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="M89" s="67" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
     </row>
     <row r="90" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4379,15 +4379,15 @@
       <c r="G90" s="19"/>
       <c r="H90" s="85"/>
       <c r="I90" s="16" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="J90" s="19"/>
       <c r="K90" s="91"/>
       <c r="L90" s="75" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="M90" s="67" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
     </row>
     <row r="91" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4400,15 +4400,15 @@
       <c r="G91" s="19"/>
       <c r="H91" s="85"/>
       <c r="I91" s="13" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="J91" s="19"/>
       <c r="K91" s="91"/>
       <c r="L91" s="75" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="M91" s="67" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
     </row>
     <row r="92" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4421,15 +4421,15 @@
       <c r="G92" s="19"/>
       <c r="H92" s="85"/>
       <c r="I92" s="24" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J92" s="19"/>
       <c r="K92" s="91"/>
       <c r="L92" s="75" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="M92" s="67" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
     </row>
     <row r="93" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4442,15 +4442,15 @@
       <c r="G93" s="19"/>
       <c r="H93" s="85"/>
       <c r="I93" s="11" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="J93" s="19"/>
       <c r="K93" s="91"/>
       <c r="L93" s="75" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="M93" s="67" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4463,15 +4463,15 @@
       <c r="G94" s="19"/>
       <c r="H94" s="85"/>
       <c r="I94" s="11" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="J94" s="19"/>
       <c r="K94" s="91"/>
       <c r="L94" s="75" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="M94" s="67" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4484,15 +4484,15 @@
       <c r="G95" s="19"/>
       <c r="H95" s="85"/>
       <c r="I95" s="11" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="J95" s="19"/>
       <c r="K95" s="91"/>
       <c r="L95" s="75" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="M95" s="67" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
     </row>
     <row r="96" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4508,10 +4508,10 @@
       <c r="J96" s="19"/>
       <c r="K96" s="91"/>
       <c r="L96" s="75" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="M96" s="67" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
     </row>
     <row r="97" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4527,10 +4527,10 @@
       <c r="J97" s="19"/>
       <c r="K97" s="91"/>
       <c r="L97" s="75" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="M97" s="67" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
     </row>
     <row r="98" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4546,10 +4546,10 @@
       <c r="J98" s="19"/>
       <c r="K98" s="91"/>
       <c r="L98" s="75" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="M98" s="67" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
     </row>
     <row r="99" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -4565,21 +4565,21 @@
       <c r="J99" s="20"/>
       <c r="K99" s="92"/>
       <c r="L99" s="75" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="M99" s="67" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
     </row>
     <row r="100" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A100" s="81" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B100" s="81" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C100" s="87" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D100" s="55"/>
       <c r="E100" s="84" t="s">
@@ -4595,19 +4595,19 @@
         <v>48</v>
       </c>
       <c r="I100" s="5" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="J100" s="84" t="s">
         <v>49</v>
       </c>
       <c r="K100" s="78" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="L100" s="75" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="M100" s="67" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
     </row>
     <row r="101" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4620,15 +4620,15 @@
       <c r="G101" s="85"/>
       <c r="H101" s="85"/>
       <c r="I101" s="8" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="J101" s="85"/>
       <c r="K101" s="79"/>
       <c r="L101" s="75" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="M101" s="67" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
     </row>
     <row r="102" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4641,15 +4641,15 @@
       <c r="G102" s="85"/>
       <c r="H102" s="85"/>
       <c r="I102" s="8" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="J102" s="85"/>
       <c r="K102" s="79"/>
       <c r="L102" s="75" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="M102" s="67" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
     </row>
     <row r="103" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4662,15 +4662,15 @@
       <c r="G103" s="85"/>
       <c r="H103" s="85"/>
       <c r="I103" s="33" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="J103" s="85"/>
       <c r="K103" s="79"/>
       <c r="L103" s="75" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="M103" s="67" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
     </row>
     <row r="104" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4683,15 +4683,15 @@
       <c r="G104" s="85"/>
       <c r="H104" s="85"/>
       <c r="I104" s="34" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="J104" s="85"/>
       <c r="K104" s="79"/>
       <c r="L104" s="75" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="M104" s="67" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
     </row>
     <row r="105" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4704,15 +4704,15 @@
       <c r="G105" s="85"/>
       <c r="H105" s="85"/>
       <c r="I105" s="6" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="J105" s="85"/>
       <c r="K105" s="79"/>
       <c r="L105" s="75" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="M105" s="67" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
     </row>
     <row r="106" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -4725,23 +4725,23 @@
       <c r="G106" s="86"/>
       <c r="H106" s="86"/>
       <c r="I106" s="35" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="J106" s="86"/>
       <c r="K106" s="80"/>
       <c r="L106" s="75" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="M106" s="67" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
     </row>
     <row r="107" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A107" s="105" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B107" s="105" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C107" s="87" t="s">
         <v>50</v>
@@ -4754,17 +4754,17 @@
       <c r="G107" s="84"/>
       <c r="H107" s="84"/>
       <c r="I107" s="10" t="s">
-        <v>203</v>
+        <v>294</v>
       </c>
       <c r="J107" s="84"/>
       <c r="K107" s="78" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="L107" s="75" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="M107" s="67" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
     <row r="108" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4779,15 +4779,15 @@
       <c r="G108" s="85"/>
       <c r="H108" s="85"/>
       <c r="I108" s="11" t="s">
-        <v>105</v>
+        <v>295</v>
       </c>
       <c r="J108" s="85"/>
       <c r="K108" s="79"/>
       <c r="L108" s="75" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="M108" s="67" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
     <row r="109" spans="1:13" ht="26" x14ac:dyDescent="0.2">
@@ -4802,15 +4802,15 @@
       <c r="G109" s="85"/>
       <c r="H109" s="85"/>
       <c r="I109" s="13" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="J109" s="85"/>
       <c r="K109" s="79"/>
       <c r="L109" s="75" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="M109" s="67" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
     <row r="110" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4823,15 +4823,15 @@
       <c r="G110" s="85"/>
       <c r="H110" s="85"/>
       <c r="I110" s="13" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J110" s="85"/>
       <c r="K110" s="79"/>
       <c r="L110" s="75" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="M110" s="67" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
     <row r="111" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4844,15 +4844,15 @@
       <c r="G111" s="85"/>
       <c r="H111" s="85"/>
       <c r="I111" s="13" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="J111" s="85"/>
       <c r="K111" s="79"/>
       <c r="L111" s="75" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="M111" s="67" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
     <row r="112" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -4865,26 +4865,26 @@
       <c r="G112" s="86"/>
       <c r="H112" s="86"/>
       <c r="I112" s="17" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="J112" s="86"/>
       <c r="K112" s="80"/>
       <c r="L112" s="75" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="M112" s="67" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
     <row r="113" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A113" s="81" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B113" s="81" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C113" s="87" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D113" s="58"/>
       <c r="E113" s="4"/>
@@ -4898,19 +4898,19 @@
         <v>56</v>
       </c>
       <c r="I113" s="36" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="J113" s="84" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="K113" s="102" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="L113" s="75" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="M113" s="67" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
     </row>
     <row r="114" spans="1:13" ht="26" x14ac:dyDescent="0.2">
@@ -4925,15 +4925,15 @@
       <c r="G114" s="85"/>
       <c r="H114" s="85"/>
       <c r="I114" s="25" t="s">
-        <v>191</v>
+        <v>296</v>
       </c>
       <c r="J114" s="85"/>
       <c r="K114" s="103"/>
       <c r="L114" s="75" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="M114" s="67" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
     </row>
     <row r="115" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4946,15 +4946,15 @@
       <c r="G115" s="85"/>
       <c r="H115" s="85"/>
       <c r="I115" s="13" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="J115" s="85"/>
       <c r="K115" s="103"/>
       <c r="L115" s="75" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="M115" s="67" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
     </row>
     <row r="116" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4967,15 +4967,15 @@
       <c r="G116" s="85"/>
       <c r="H116" s="85"/>
       <c r="I116" s="12" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="J116" s="85"/>
       <c r="K116" s="103"/>
       <c r="L116" s="75" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="M116" s="67" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
     </row>
     <row r="117" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -4988,15 +4988,15 @@
       <c r="G117" s="85"/>
       <c r="H117" s="85"/>
       <c r="I117" s="11" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="J117" s="85"/>
       <c r="K117" s="103"/>
       <c r="L117" s="75" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="M117" s="67" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
     </row>
     <row r="118" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5009,15 +5009,15 @@
       <c r="G118" s="85"/>
       <c r="H118" s="85"/>
       <c r="I118" s="11" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="J118" s="85"/>
       <c r="K118" s="103"/>
       <c r="L118" s="75" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="M118" s="67" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
     </row>
     <row r="119" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5033,10 +5033,10 @@
       <c r="J119" s="85"/>
       <c r="K119" s="103"/>
       <c r="L119" s="75" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="M119" s="67" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
     </row>
     <row r="120" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -5048,27 +5048,25 @@
       <c r="F120" s="101"/>
       <c r="G120" s="86"/>
       <c r="H120" s="86"/>
-      <c r="I120" s="30" t="s">
-        <v>57</v>
-      </c>
+      <c r="I120" s="30"/>
       <c r="J120" s="86"/>
       <c r="K120" s="104"/>
       <c r="L120" s="75" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="M120" s="67" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
     </row>
     <row r="121" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A121" s="81" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B121" s="81" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C121" s="87" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D121" s="55"/>
       <c r="E121" s="84" t="s">
@@ -5078,25 +5076,25 @@
         <v>21</v>
       </c>
       <c r="G121" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="H121" s="84" t="s">
         <v>58</v>
       </c>
-      <c r="H121" s="84" t="s">
+      <c r="I121" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="J121" s="84" t="s">
         <v>59</v>
       </c>
-      <c r="I121" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="J121" s="84" t="s">
-        <v>60</v>
-      </c>
       <c r="K121" s="78" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="L121" s="75" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="M121" s="67" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
     </row>
     <row r="122" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5109,15 +5107,15 @@
       <c r="G122" s="85"/>
       <c r="H122" s="85"/>
       <c r="I122" s="13" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="J122" s="85"/>
       <c r="K122" s="79"/>
       <c r="L122" s="75" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="M122" s="67" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
     </row>
     <row r="123" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5130,15 +5128,15 @@
       <c r="G123" s="85"/>
       <c r="H123" s="85"/>
       <c r="I123" s="13" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="J123" s="85"/>
       <c r="K123" s="79"/>
       <c r="L123" s="75" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="M123" s="67" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
     </row>
     <row r="124" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5151,15 +5149,15 @@
       <c r="G124" s="85"/>
       <c r="H124" s="85"/>
       <c r="I124" s="12" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="J124" s="85"/>
       <c r="K124" s="79"/>
       <c r="L124" s="75" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="M124" s="67" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
     </row>
     <row r="125" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5172,15 +5170,15 @@
       <c r="G125" s="85"/>
       <c r="H125" s="85"/>
       <c r="I125" s="25" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="J125" s="85"/>
       <c r="K125" s="79"/>
       <c r="L125" s="75" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="M125" s="67" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
     </row>
     <row r="126" spans="1:13" ht="85" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -5193,54 +5191,54 @@
       <c r="G126" s="86"/>
       <c r="H126" s="86"/>
       <c r="I126" s="30" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="J126" s="86"/>
       <c r="K126" s="80"/>
       <c r="L126" s="75" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="M126" s="67" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
     </row>
     <row r="127" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="81" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B127" s="81" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C127" s="87" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D127" s="55"/>
       <c r="E127" s="84" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F127" s="84" t="s">
         <v>27</v>
       </c>
       <c r="G127" s="84" t="s">
+        <v>61</v>
+      </c>
+      <c r="H127" s="84" t="s">
         <v>62</v>
       </c>
-      <c r="H127" s="84" t="s">
+      <c r="I127" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J127" s="84" t="s">
         <v>63</v>
       </c>
-      <c r="I127" s="37" t="s">
-        <v>195</v>
-      </c>
-      <c r="J127" s="84" t="s">
-        <v>64</v>
-      </c>
       <c r="K127" s="78" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="L127" s="75" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="M127" s="67" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
     </row>
     <row r="128" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5253,15 +5251,15 @@
       <c r="G128" s="85"/>
       <c r="H128" s="85"/>
       <c r="I128" s="16" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="J128" s="85"/>
       <c r="K128" s="79"/>
       <c r="L128" s="75" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="M128" s="67" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
     </row>
     <row r="129" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5274,15 +5272,15 @@
       <c r="G129" s="85"/>
       <c r="H129" s="85"/>
       <c r="I129" s="13" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="J129" s="85"/>
       <c r="K129" s="79"/>
       <c r="L129" s="75" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="M129" s="67" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
     </row>
     <row r="130" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5295,15 +5293,15 @@
       <c r="G130" s="85"/>
       <c r="H130" s="85"/>
       <c r="I130" s="13" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="J130" s="85"/>
       <c r="K130" s="79"/>
       <c r="L130" s="75" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="M130" s="67" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
     </row>
     <row r="131" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5316,15 +5314,15 @@
       <c r="G131" s="85"/>
       <c r="H131" s="85"/>
       <c r="I131" s="13" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J131" s="85"/>
       <c r="K131" s="79"/>
       <c r="L131" s="75" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="M131" s="67" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
     </row>
     <row r="132" spans="1:13" ht="29" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -5337,54 +5335,54 @@
       <c r="G132" s="86"/>
       <c r="H132" s="86"/>
       <c r="I132" s="12" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J132" s="86"/>
       <c r="K132" s="80"/>
       <c r="L132" s="75" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="M132" s="67" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
     </row>
     <row r="133" spans="1:13" ht="26" x14ac:dyDescent="0.2">
       <c r="A133" s="81" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B133" s="81" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C133" s="87" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D133" s="87"/>
       <c r="E133" s="84" t="s">
         <v>9</v>
       </c>
       <c r="F133" s="84" t="s">
+        <v>64</v>
+      </c>
+      <c r="G133" s="84" t="s">
         <v>65</v>
       </c>
-      <c r="G133" s="84" t="s">
+      <c r="H133" s="108" t="s">
         <v>66</v>
       </c>
-      <c r="H133" s="108" t="s">
+      <c r="I133" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="J133" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="I133" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="J133" s="38" t="s">
-        <v>68</v>
-      </c>
       <c r="K133" s="78" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="L133" s="75" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="M133" s="67" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
     </row>
     <row r="134" spans="1:13" ht="26" x14ac:dyDescent="0.2">
@@ -5397,17 +5395,17 @@
       <c r="G134" s="85"/>
       <c r="H134" s="109"/>
       <c r="I134" s="11" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="J134" s="39" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K134" s="79"/>
       <c r="L134" s="75" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="M134" s="67" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
     </row>
     <row r="135" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5420,17 +5418,17 @@
       <c r="G135" s="85"/>
       <c r="H135" s="109"/>
       <c r="I135" s="12" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="J135" s="14" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="K135" s="79"/>
       <c r="L135" s="75" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="M135" s="67" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
     </row>
     <row r="136" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5443,15 +5441,15 @@
       <c r="G136" s="85"/>
       <c r="H136" s="109"/>
       <c r="I136" s="12" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="J136" s="19"/>
       <c r="K136" s="79"/>
       <c r="L136" s="75" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="M136" s="67" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
     </row>
     <row r="137" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5464,15 +5462,15 @@
       <c r="G137" s="85"/>
       <c r="H137" s="109"/>
       <c r="I137" s="25" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="J137" s="19"/>
       <c r="K137" s="79"/>
       <c r="L137" s="75" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="M137" s="67" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
     </row>
     <row r="138" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5485,15 +5483,15 @@
       <c r="G138" s="85"/>
       <c r="H138" s="109"/>
       <c r="I138" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="J138" s="19"/>
       <c r="K138" s="79"/>
       <c r="L138" s="75" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="M138" s="67" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
     </row>
     <row r="139" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5506,15 +5504,15 @@
       <c r="G139" s="85"/>
       <c r="H139" s="109"/>
       <c r="I139" s="13" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="J139" s="19"/>
       <c r="K139" s="79"/>
       <c r="L139" s="75" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="M139" s="67" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
     </row>
     <row r="140" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5527,15 +5525,15 @@
       <c r="G140" s="85"/>
       <c r="H140" s="109"/>
       <c r="I140" s="16" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="J140" s="19"/>
       <c r="K140" s="79"/>
       <c r="L140" s="75" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="M140" s="67" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
     </row>
     <row r="141" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5548,15 +5546,15 @@
       <c r="G141" s="85"/>
       <c r="H141" s="109"/>
       <c r="I141" s="13" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J141" s="19"/>
       <c r="K141" s="79"/>
       <c r="L141" s="75" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="M141" s="67" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
     </row>
     <row r="142" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5569,15 +5567,15 @@
       <c r="G142" s="85"/>
       <c r="H142" s="109"/>
       <c r="I142" s="11" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="J142" s="19"/>
       <c r="K142" s="79"/>
       <c r="L142" s="75" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="M142" s="67" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
     </row>
     <row r="143" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -5590,52 +5588,52 @@
       <c r="G143" s="86"/>
       <c r="H143" s="110"/>
       <c r="I143" s="30" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="J143" s="20"/>
       <c r="K143" s="80"/>
       <c r="L143" s="75" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="M143" s="67" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
     </row>
     <row r="144" spans="1:13" ht="59" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="81" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B144" s="81" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C144" s="87" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D144" s="87"/>
       <c r="E144" s="84" t="s">
         <v>9</v>
       </c>
       <c r="F144" s="84" t="s">
+        <v>69</v>
+      </c>
+      <c r="G144" s="84" t="s">
         <v>70</v>
       </c>
-      <c r="G144" s="84" t="s">
+      <c r="H144" s="84" t="s">
         <v>71</v>
-      </c>
-      <c r="H144" s="84" t="s">
-        <v>72</v>
       </c>
       <c r="I144" s="40"/>
       <c r="J144" s="84" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K144" s="78" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="L144" s="75" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="M144" s="67" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
     </row>
     <row r="145" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5651,10 +5649,10 @@
       <c r="J145" s="85"/>
       <c r="K145" s="79"/>
       <c r="L145" s="75" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="M145" s="67" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
     </row>
     <row r="146" spans="1:13" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -5670,88 +5668,88 @@
       <c r="J146" s="86"/>
       <c r="K146" s="80"/>
       <c r="L146" s="75" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="M146" s="67" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
     </row>
     <row r="147" spans="1:13" ht="79" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A147" s="62" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B147" s="54" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C147" s="54" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D147" s="54"/>
       <c r="E147" s="41" t="s">
+        <v>73</v>
+      </c>
+      <c r="F147" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="F147" s="41" t="s">
+      <c r="G147" s="41" t="s">
         <v>75</v>
       </c>
-      <c r="G147" s="41" t="s">
+      <c r="H147" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="H147" s="41" t="s">
+      <c r="I147" s="42" t="s">
+        <v>298</v>
+      </c>
+      <c r="J147" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="I147" s="42" t="s">
-        <v>107</v>
-      </c>
-      <c r="J147" s="41" t="s">
-        <v>78</v>
-      </c>
       <c r="K147" s="65" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="L147" s="75" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="M147" s="67" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
     </row>
     <row r="148" spans="1:13" ht="24" x14ac:dyDescent="0.2">
       <c r="A148" s="139" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B148" s="81" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C148" s="87" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D148" s="87"/>
       <c r="E148" s="84" t="s">
         <v>9</v>
       </c>
       <c r="F148" s="84" t="s">
+        <v>78</v>
+      </c>
+      <c r="G148" s="84" t="s">
         <v>79</v>
       </c>
-      <c r="G148" s="84" t="s">
+      <c r="H148" s="84" t="s">
         <v>80</v>
       </c>
-      <c r="H148" s="84" t="s">
+      <c r="I148" s="43" t="s">
+        <v>197</v>
+      </c>
+      <c r="J148" s="84" t="s">
         <v>81</v>
       </c>
-      <c r="I148" s="43" t="s">
-        <v>208</v>
-      </c>
-      <c r="J148" s="84" t="s">
-        <v>82</v>
-      </c>
       <c r="K148" s="78" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="L148" s="75" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="M148" s="67" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
     </row>
     <row r="149" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5764,15 +5762,15 @@
       <c r="G149" s="85"/>
       <c r="H149" s="85"/>
       <c r="I149" s="44" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="J149" s="85"/>
       <c r="K149" s="79"/>
       <c r="L149" s="75" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="M149" s="67" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
     </row>
     <row r="150" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5785,15 +5783,15 @@
       <c r="G150" s="85"/>
       <c r="H150" s="85"/>
       <c r="I150" s="45" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="J150" s="85"/>
       <c r="K150" s="79"/>
       <c r="L150" s="75" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="M150" s="67" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
     </row>
     <row r="151" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5806,15 +5804,15 @@
       <c r="G151" s="85"/>
       <c r="H151" s="85"/>
       <c r="I151" s="44" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="J151" s="85"/>
       <c r="K151" s="79"/>
       <c r="L151" s="75" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="M151" s="67" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
     </row>
     <row r="152" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5827,15 +5825,15 @@
       <c r="G152" s="85"/>
       <c r="H152" s="85"/>
       <c r="I152" s="46" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="J152" s="85"/>
       <c r="K152" s="79"/>
       <c r="L152" s="75" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="M152" s="67" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
     </row>
     <row r="153" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5848,15 +5846,15 @@
       <c r="G153" s="85"/>
       <c r="H153" s="85"/>
       <c r="I153" s="45" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="J153" s="85"/>
       <c r="K153" s="79"/>
       <c r="L153" s="75" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="M153" s="67" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
     </row>
     <row r="154" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5869,15 +5867,15 @@
       <c r="G154" s="85"/>
       <c r="H154" s="85"/>
       <c r="I154" s="18" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="J154" s="85"/>
       <c r="K154" s="79"/>
       <c r="L154" s="75" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="M154" s="67" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
     </row>
     <row r="155" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5893,10 +5891,10 @@
       <c r="J155" s="85"/>
       <c r="K155" s="79"/>
       <c r="L155" s="75" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="M155" s="67" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
     </row>
     <row r="156" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -5912,21 +5910,21 @@
       <c r="J156" s="86"/>
       <c r="K156" s="80"/>
       <c r="L156" s="75" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="M156" s="67" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
     </row>
     <row r="157" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A157" s="136" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B157" s="111" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C157" s="118" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D157" s="118"/>
       <c r="E157" s="84"/>
@@ -5936,19 +5934,19 @@
       <c r="G157" s="84"/>
       <c r="H157" s="84"/>
       <c r="I157" s="47" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="J157" s="84" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K157" s="78" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="L157" s="75" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="M157" s="67" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
     </row>
     <row r="158" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5961,15 +5959,15 @@
       <c r="G158" s="85"/>
       <c r="H158" s="85"/>
       <c r="I158" s="44" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="J158" s="85"/>
       <c r="K158" s="79"/>
       <c r="L158" s="75" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="M158" s="67" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
     </row>
     <row r="159" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -5982,15 +5980,15 @@
       <c r="G159" s="85"/>
       <c r="H159" s="85"/>
       <c r="I159" s="46" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="J159" s="85"/>
       <c r="K159" s="79"/>
       <c r="L159" s="75" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="M159" s="67" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
     </row>
     <row r="160" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -6003,15 +6001,15 @@
       <c r="G160" s="85"/>
       <c r="H160" s="85"/>
       <c r="I160" s="44" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="J160" s="85"/>
       <c r="K160" s="79"/>
       <c r="L160" s="75" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="M160" s="67" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
     </row>
     <row r="161" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -6024,15 +6022,15 @@
       <c r="G161" s="85"/>
       <c r="H161" s="85"/>
       <c r="I161" s="44" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="J161" s="85"/>
       <c r="K161" s="79"/>
       <c r="L161" s="75" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="M161" s="67" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
     </row>
     <row r="162" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -6045,15 +6043,15 @@
       <c r="G162" s="85"/>
       <c r="H162" s="85"/>
       <c r="I162" s="46" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J162" s="85"/>
       <c r="K162" s="79"/>
       <c r="L162" s="75" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="M162" s="67" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
     </row>
     <row r="163" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -6066,15 +6064,15 @@
       <c r="G163" s="85"/>
       <c r="H163" s="85"/>
       <c r="I163" s="46" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="J163" s="85"/>
       <c r="K163" s="79"/>
       <c r="L163" s="75" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="M163" s="67" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
     </row>
     <row r="164" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -6087,15 +6085,15 @@
       <c r="G164" s="85"/>
       <c r="H164" s="85"/>
       <c r="I164" s="48" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="J164" s="85"/>
       <c r="K164" s="79"/>
       <c r="L164" s="75" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="M164" s="67" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
     </row>
     <row r="165" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
@@ -6108,54 +6106,54 @@
       <c r="G165" s="114"/>
       <c r="H165" s="114"/>
       <c r="I165" s="49" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J165" s="114"/>
       <c r="K165" s="124"/>
       <c r="L165" s="75" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="M165" s="67" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
     </row>
     <row r="166" spans="1:13" ht="53" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="142" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B166" s="125" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C166" s="121" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D166" s="121"/>
       <c r="E166" s="126" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F166" s="126" t="s">
         <v>27</v>
       </c>
       <c r="G166" s="126" t="s">
+        <v>85</v>
+      </c>
+      <c r="H166" s="126" t="s">
+        <v>287</v>
+      </c>
+      <c r="I166" s="50" t="s">
+        <v>299</v>
+      </c>
+      <c r="J166" s="126" t="s">
         <v>86</v>
       </c>
-      <c r="H166" s="126" t="s">
-        <v>298</v>
-      </c>
-      <c r="I166" s="50" t="s">
-        <v>204</v>
-      </c>
-      <c r="J166" s="126" t="s">
-        <v>87</v>
-      </c>
       <c r="K166" s="127" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="L166" s="75" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="M166" s="67" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
     </row>
     <row r="167" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -6168,15 +6166,15 @@
       <c r="G167" s="85"/>
       <c r="H167" s="85"/>
       <c r="I167" s="11" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="J167" s="85"/>
       <c r="K167" s="79"/>
       <c r="L167" s="75" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="M167" s="67" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
     </row>
     <row r="168" spans="1:13" ht="83" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -6189,26 +6187,26 @@
       <c r="G168" s="86"/>
       <c r="H168" s="86"/>
       <c r="I168" s="51" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="J168" s="86"/>
       <c r="K168" s="80"/>
       <c r="L168" s="75" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="M168" s="67" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
     </row>
     <row r="169" spans="1:13" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="139" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B169" s="81" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C169" s="87" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D169" s="87"/>
       <c r="E169" s="84" t="s">
@@ -6218,25 +6216,25 @@
         <v>27</v>
       </c>
       <c r="G169" s="84" t="s">
+        <v>87</v>
+      </c>
+      <c r="H169" s="84" t="s">
+        <v>285</v>
+      </c>
+      <c r="I169" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="J169" s="84" t="s">
         <v>88</v>
       </c>
-      <c r="H169" s="84" t="s">
-        <v>296</v>
-      </c>
-      <c r="I169" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="J169" s="84" t="s">
-        <v>89</v>
-      </c>
       <c r="K169" s="78" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="L169" s="75" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="M169" s="67" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
     </row>
     <row r="170" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -6249,15 +6247,15 @@
       <c r="G170" s="85"/>
       <c r="H170" s="85"/>
       <c r="I170" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J170" s="85"/>
       <c r="K170" s="79"/>
       <c r="L170" s="75" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="M170" s="67" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
     </row>
     <row r="171" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -6273,10 +6271,10 @@
       <c r="J171" s="85"/>
       <c r="K171" s="79"/>
       <c r="L171" s="75" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="M171" s="67" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
     </row>
     <row r="172" spans="1:13" ht="53" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -6292,21 +6290,21 @@
       <c r="J172" s="86"/>
       <c r="K172" s="80"/>
       <c r="L172" s="75" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="M172" s="67" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
     </row>
     <row r="173" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A173" s="136" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B173" s="111" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C173" s="118" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D173" s="118"/>
       <c r="E173" s="84"/>
@@ -6314,19 +6312,19 @@
       <c r="G173" s="40"/>
       <c r="H173" s="4"/>
       <c r="I173" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J173" s="84" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K173" s="78" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="L173" s="75" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="M173" s="67" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
     </row>
     <row r="174" spans="1:13" ht="39" x14ac:dyDescent="0.2">
@@ -6339,21 +6337,21 @@
         <v>27</v>
       </c>
       <c r="G174" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="H174" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="H174" s="26" t="s">
-        <v>91</v>
-      </c>
       <c r="I174" s="24" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="J174" s="85"/>
       <c r="K174" s="79"/>
       <c r="L174" s="75" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="M174" s="67" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
     </row>
     <row r="175" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -6366,15 +6364,15 @@
       <c r="G175" s="19"/>
       <c r="H175" s="29"/>
       <c r="I175" s="16" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="J175" s="85"/>
       <c r="K175" s="79"/>
       <c r="L175" s="75" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="M175" s="67" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
     </row>
     <row r="176" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -6387,15 +6385,15 @@
       <c r="G176" s="19"/>
       <c r="H176" s="19"/>
       <c r="I176" s="12" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="J176" s="85"/>
       <c r="K176" s="79"/>
       <c r="L176" s="75" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="M176" s="67" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
     </row>
     <row r="177" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -6408,15 +6406,15 @@
       <c r="G177" s="19"/>
       <c r="H177" s="19"/>
       <c r="I177" s="13" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="J177" s="85"/>
       <c r="K177" s="79"/>
       <c r="L177" s="75" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="M177" s="67" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
     </row>
     <row r="178" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">

--- a/RWF_Entourage.xlsx
+++ b/RWF_Entourage.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/frederiquehammerli/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A5CF673-97C9-3347-A8B4-260D193F6455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87C7E253-17AB-3745-A761-5A8A48E996EE}"/>
   <bookViews>
-    <workbookView xWindow="1760" yWindow="2160" windowWidth="44800" windowHeight="24600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="44800" windowHeight="24600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entourage" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="272">
   <si>
     <t>ID canonique</t>
   </si>
@@ -65,9 +65,6 @@
     <t>Portrait</t>
   </si>
   <si>
-    <t>Ancien ID</t>
-  </si>
-  <si>
     <t>pers-armin-meier</t>
   </si>
   <si>
@@ -131,9 +128,6 @@
     <t>film-1970-les-dieux-de-la-peste; film-1973-le-monde-sur-un-fil; film-1974-martha; film-1974-tous-les-autres-s-appellent-ali; film-1975-maman-kusters-s-en-va-au-ciel</t>
   </si>
   <si>
-    <t>Sensualité populaire</t>
-  </si>
-  <si>
     <t>Valentin.jpg</t>
   </si>
   <si>
@@ -237,9 +231,6 @@
   </si>
   <si>
     <t>Ben_salem.jpg</t>
-  </si>
-  <si>
-    <t>Ben_salem</t>
   </si>
   <si>
     <t>pers-gottfried-john</t>
@@ -264,10 +255,6 @@
     <t>film-1972-huit-heures-ne-font-pas-un-jour; film-1975-maman-kusters-s-en-va-au-ciel; film-1978-despair; film-1978-l-annee-des-treize-lunes; film-1979-le-mariage-de-maria-braun; film-1980-berlin-alexanderplatz; film-1981-le-secret-de-veronika-voss; film-1981-lili-marleen; film-1981-lola-une-femme-allemande</t>
   </si>
   <si>
-    <t>Fascination du méchant, +journTous les autres s’appellent Ali  (1974)ste
-+ Le Soldat américain  (1970)itz et Reinhold !</t>
-  </si>
-  <si>
     <t>Gottfried.jpg</t>
   </si>
   <si>
@@ -415,9 +402,6 @@
     <t>Irm Hermann</t>
   </si>
   <si>
-    <t>Hermann Irm</t>
-  </si>
-  <si>
     <t>Jeu, répétition de rôle, tension sociale</t>
   </si>
   <si>
@@ -428,9 +412,6 @@
   </si>
   <si>
     <t>film-1969-l-amour-est-plus-froid-que-la-mort; film-1969-le-bouc; film-1970-les-dieux-de-la-peste; film-1972-le-marchand-des-quatre-saisons; film-1972-les-larmes-ameres-de-petra-von-kant; film-1974-effi-briest; film-1974-nora-helmer; film-1974-tous-les-autres-s-appellent-ali; film-1975-le-droit-du-plus-fort; film-1975-maman-kusters-s-en-va-au-ciel; film-1981-lili-marleen</t>
-  </si>
-  <si>
-    <t>Corps de la frustration sociale, de l’Tous les autres s’appellent Ali  (1974)énation et du domestique</t>
   </si>
   <si>
     <t>Hermann.jpg</t>
@@ -527,11 +508,6 @@
     <t>film-1969-l-amour-est-plus-froid-que-la-mort; film-1969-le-bouc; film-1970-le-soldat-americain; film-1970-pourquoi-m-r-est-il-atteint-de-folie-meurtriere; film-1971-prenez-garde-a-la-sainte-putain; film-1971-whity; film-1972-huit-heures-ne-font-pas-un-jour; film-1972-le-marchand-des-quatre-saisons; film-1972-les-larmes-ameres-de-petra-von-kant; film-1974-effi-briest; film-1974-martha; film-1975-le-droit-du-plus-fort; film-1975-maman-kusters-s-en-va-au-ciel; film-1975-peur-de-la-peur; film-1976-le-roti-de-satan; film-1979-le-mariage-de-maria-braun; film-1981-lili-marleen; film-1982-querelle</t>
   </si>
   <si>
-    <t>Collaborateur total, à la frontière du jeu et de la fabrication matérielle
-Chef Décorateur
-Identité visuelle des Le monde sur un fil (1973)ms de RWF</t>
-  </si>
-  <si>
     <t>Raab.jpg</t>
   </si>
   <si>
@@ -596,9 +572,6 @@
     <t>Eder.jpg</t>
   </si>
   <si>
-    <t>Eder</t>
-  </si>
-  <si>
     <t>pers-margit-carstensen</t>
   </si>
   <si>
@@ -623,10 +596,6 @@
     <t>film-1972-les-larmes-ameres-de-petra-von-kant; film-1974-martha; film-1975-maman-kusters-s-en-va-au-ciel; film-1975-peur-de-la-peur; film-1976-le-roti-de-satan; film-1976-roulette-chinoise; film-1979-la-troisieme-generation</t>
   </si>
   <si>
-    <t>Grande figure du conflit conjugal, social et psychique
-Couple avec Karlheinz Böhm</t>
-  </si>
-  <si>
     <t>Carstensen.jpg</t>
   </si>
   <si>
@@ -660,13 +629,7 @@
     <t>film-1971-prenez-garde-a-la-sainte-putain; film-1971-whity; film-1973-le-monde-sur-un-fil; film-1974-martha; film-1974-tous-les-autres-s-appellent-ali; film-1975-le-droit-du-plus-fort; film-1975-maman-kusters-s-en-va-au-ciel; film-1976-je-veux-seulement-que-vous-m-aimiez; film-1976-le-roti-de-satan; film-1976-roulette-chinoise; film-1978-despair; film-1978-l-allemagne-en-automne; film-1979-le-mariage-de-maria-braun; film-1981-lili-marleen</t>
   </si>
   <si>
-    <t>FormTous les autres s’appellent Ali  (1974)Le Soldat américain  (1970)tion du grand style visuel tardif</t>
-  </si>
-  <si>
     <t>Ballhaus.jpg</t>
-  </si>
-  <si>
-    <t>Balhaus</t>
   </si>
   <si>
     <t>pers-peer-raben</t>
@@ -782,9 +745,6 @@
     <t>film-1969-l-amour-est-plus-froid-que-la-mort; film-1970-le-voyage-a-niklashausen; film-1970-les-dieux-de-la-peste; film-1974-effi-briest</t>
   </si>
   <si>
-    <t>Lien entre théâtre et premiers essais Le monde sur un fil (1973)miques</t>
-  </si>
-  <si>
     <t>Strätz.jpg</t>
   </si>
   <si>
@@ -806,9 +766,6 @@
     <t>film-1975-maman-kusters-s-en-va-au-ciel; film-1976-le-roti-de-satan; film-1976-roulette-chinoise; film-1978-despair; film-1978-l-annee-des-treize-lunes; film-1979-la-troisieme-generation; film-1979-le-mariage-de-maria-braun; film-1980-berlin-alexanderplatz</t>
   </si>
   <si>
-    <t>Incarne souvent des personnages de travestis ou qui se déguisent, il incarne une inquiétante étrangeté.</t>
-  </si>
-  <si>
     <t>Volker.jpg</t>
   </si>
   <si>
@@ -855,13 +812,43 @@
   </si>
   <si>
     <t>Les statuts « À rapprocher » concernent actuellement Le Petit Chaos et Rio das Mortes.</t>
+  </si>
+  <si>
+    <t>Formation du grand style visuel tardif</t>
+  </si>
+  <si>
+    <t>Grande figure du conflit conjugal, social et psychique</t>
+  </si>
+  <si>
+    <t>Couple avec Karlheinz Böhm</t>
+  </si>
+  <si>
+    <t>Fascination du méchant, journaliste, Reinhold</t>
+  </si>
+  <si>
+    <t>Corps de la frustration sociale, de l'aliénation et du domestique</t>
+  </si>
+  <si>
+    <t>Collaborateur total, à la frontière du jeu et de la fabrication matérielle, Chef Décorateur , identité visuelle des films de RWF</t>
+  </si>
+  <si>
+    <t>Lien entre théâtre et premiers essais filmiques</t>
+  </si>
+  <si>
+    <t>Sensualité,  populaire, Incarne souvent des personnages de travestis ou qui se déguisent, il incarne une inquiétante étrangeté.</t>
+  </si>
+  <si>
+    <t>Hermann</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Irm</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -900,8 +887,14 @@
       <color rgb="FF7A1F2B"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -911,6 +904,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF7A1F2B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7A1E2B"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -984,10 +983,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1007,89 +1033,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF7A1E2B"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1102,28 +1067,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EntourageV30" displayName="EntourageV30" ref="A1:O24" totalsRowShown="0" dataDxfId="1">
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O24">
-    <sortCondition ref="C24"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EntourageV30" displayName="EntourageV30" ref="A1:N24" totalsRowShown="0">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N24">
+    <sortCondition ref="C1:C24"/>
   </sortState>
-  <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID canonique" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Nom canonique" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Nom source" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Prénom source" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Surnom" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Strate" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Fonction dominante" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Type de collaboration" dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Vie privée / lien avec Fassbinder" dataDxfId="7"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Œuvres de Fassbinder" dataDxfId="6"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="IDs films — Œuvres de Fassbinder" dataDxfId="5"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Œuvres non rapprochées" dataDxfId="4"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Rôle dans l’univers Fassbinder" dataDxfId="3"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Portrait" dataDxfId="2"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Ancien ID" dataDxfId="0"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID canonique"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Nom canonique"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Nom source"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Prénom source"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Surnom"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Strate"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Fonction dominante"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Type de collaboration"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Vie privée / lien avec Fassbinder"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Œuvres de Fassbinder"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="IDs films — Œuvres de Fassbinder"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Œuvres non rapprochées"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Rôle dans l’univers Fassbinder" dataDxfId="0"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Portrait"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1322,7 +1286,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
@@ -1338,10 +1302,9 @@
     <col min="12" max="12" width="26" customWidth="1"/>
     <col min="13" max="13" width="38" customWidth="1"/>
     <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="15" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="42" customHeight="1">
+    <row r="1" spans="1:14" ht="42" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1378,973 +1341,905 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="17" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:14" ht="72" customHeight="1">
+      <c r="A2" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="L2" s="2"/>
+      <c r="M2" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="72" customHeight="1">
+      <c r="A3" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="L3" s="3"/>
+      <c r="M3" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="72" customHeight="1">
+      <c r="A4" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="L4" s="3"/>
+      <c r="M4" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="72" customHeight="1">
+      <c r="A5" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="L5" s="3"/>
+      <c r="M5" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="72" customHeight="1">
+      <c r="A6" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="L6" s="3"/>
+      <c r="M6" s="18" t="s">
+        <v>263</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="72" customHeight="1">
+      <c r="A7" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="L7" s="3"/>
+      <c r="M7" s="18" t="s">
+        <v>264</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="72" customHeight="1">
+      <c r="A8" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="L8" s="3"/>
+      <c r="M8" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="72" customHeight="1">
+      <c r="A9" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="M9" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="72" customHeight="1">
+      <c r="A10" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="L10" s="3"/>
+      <c r="M10" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="72" customHeight="1">
+      <c r="A11" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="L11" s="3"/>
+      <c r="M11" s="18" t="s">
+        <v>265</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="72" customHeight="1">
+      <c r="A12" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="L12" s="3"/>
+      <c r="M12" s="18" t="s">
+        <v>266</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="72" customHeight="1">
+      <c r="A13" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="L13" s="3"/>
+      <c r="M13" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="72" customHeight="1">
+      <c r="A14" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="L14" s="3"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="72" customHeight="1">
+      <c r="A15" s="6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" ht="72" customHeight="1">
-      <c r="A2" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10" t="s">
+      <c r="B15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15" s="3"/>
+      <c r="M15" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="72" customHeight="1">
+      <c r="A16" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="L16" s="3"/>
+      <c r="M16" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="72" customHeight="1">
+      <c r="A17" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="L17" s="3"/>
+      <c r="M17" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="72" customHeight="1">
+      <c r="A18" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J18" s="3"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="72" customHeight="1">
+      <c r="A19" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="L19" s="3"/>
+      <c r="M19" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="72" customHeight="1">
+      <c r="A20" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="G2" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="O2" s="10" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="72" customHeight="1">
-      <c r="A3" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>208</v>
-      </c>
-      <c r="K3" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13" t="s">
-        <v>210</v>
-      </c>
-      <c r="N3" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="O3" s="13" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="72" customHeight="1">
-      <c r="A4" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13" t="s">
+      <c r="K20" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M20" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="72" customHeight="1">
+      <c r="A21" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="L21" s="3"/>
+      <c r="M21" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="72" customHeight="1">
+      <c r="A22" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="L22" s="3"/>
+      <c r="M22" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="72" customHeight="1">
+      <c r="A23" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K23" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" s="3"/>
+      <c r="M23" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="72" customHeight="1">
+      <c r="A24" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="K4" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="N4" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="O4" s="13" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="72" customHeight="1">
-      <c r="A5" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="I5" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="J5" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="N5" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="O5" s="13" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="72" customHeight="1">
-      <c r="A6" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="G6" s="13" t="s">
+      <c r="H24" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="N6" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="O6" s="13" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="72" customHeight="1">
-      <c r="A7" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="J7" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="K7" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="N7" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="O7" s="13" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="72" customHeight="1">
-      <c r="A8" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="I8" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="J8" s="13" t="s">
-        <v>229</v>
-      </c>
-      <c r="K8" s="14" t="s">
-        <v>230</v>
-      </c>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="N8" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="O8" s="13" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="72" customHeight="1">
-      <c r="A9" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="J9" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="K9" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="L9" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="M9" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="N9" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="O9" s="13" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="72" customHeight="1">
-      <c r="A10" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="K10" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="N10" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="O10" s="13" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="72" customHeight="1">
-      <c r="A11" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="J11" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="K11" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="N11" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="O11" s="13" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="72" customHeight="1">
-      <c r="A12" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="J12" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="K12" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="N12" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="O12" s="13" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="72" customHeight="1">
-      <c r="A13" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="K13" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="O13" s="13" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="72" customHeight="1">
-      <c r="A14" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="J14" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="K14" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="N14" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="O14" s="13" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="72" customHeight="1">
-      <c r="A15" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J15" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="K15" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="N15" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="O15" s="13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="72" customHeight="1">
-      <c r="A16" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="J16" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="K16" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="L16" s="13"/>
-      <c r="M16" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="N16" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="O16" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="72" customHeight="1">
-      <c r="A17" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="J17" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="K17" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="N17" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="O17" s="13" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="72" customHeight="1">
-      <c r="A18" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>214</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="J18" s="13"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="N18" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="O18" s="13" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="72" customHeight="1">
-      <c r="A19" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="J19" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="K19" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="N19" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="O19" s="13" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="72" customHeight="1">
-      <c r="A20" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="J20" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="K20" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="L20" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="M20" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="N20" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="O20" s="13" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" ht="72" customHeight="1">
-      <c r="A21" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="D21" s="13" t="s">
+      <c r="I24" s="4"/>
+      <c r="J24" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13" t="s">
+      <c r="K24" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="G21" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="H21" s="13" t="s">
+      <c r="L24" s="4"/>
+      <c r="M24" s="18" t="s">
+        <v>269</v>
+      </c>
+      <c r="N24" s="4" t="s">
         <v>246</v>
-      </c>
-      <c r="I21" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="J21" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="K21" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="L21" s="13"/>
-      <c r="M21" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="N21" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="O21" s="13" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" ht="72" customHeight="1">
-      <c r="A22" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="J22" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="K22" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="L22" s="13"/>
-      <c r="M22" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="N22" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="O22" s="13" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" ht="72" customHeight="1">
-      <c r="A23" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="J23" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="K23" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="L23" s="13"/>
-      <c r="M23" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="N23" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="O23" s="13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" ht="72" customHeight="1">
-      <c r="A24" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>253</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16" t="s">
-        <v>256</v>
-      </c>
-      <c r="K24" s="17" t="s">
-        <v>257</v>
-      </c>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="N24" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="O24" s="16" t="s">
-        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -2366,82 +2261,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+    </row>
+    <row r="3" spans="1:4" ht="34" customHeight="1">
+      <c r="A3" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+    </row>
+    <row r="4" spans="1:4" ht="34" customHeight="1">
+      <c r="A4" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+    </row>
+    <row r="5" spans="1:4" ht="34" customHeight="1">
+      <c r="A5" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+    </row>
+    <row r="6" spans="1:4" ht="34" customHeight="1">
+      <c r="A6" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+    </row>
+    <row r="7" spans="1:4" ht="34" customHeight="1">
+      <c r="A7" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+    </row>
+    <row r="8" spans="1:4" ht="34" customHeight="1">
+      <c r="A8" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+    </row>
+    <row r="9" spans="1:4" ht="34" customHeight="1">
+      <c r="A9" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-    </row>
-    <row r="3" spans="1:4" ht="34" customHeight="1">
-      <c r="A3" s="2" t="s">
+      <c r="B9" s="16" t="s">
         <v>261</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:4" ht="34" customHeight="1">
-      <c r="A4" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-    </row>
-    <row r="5" spans="1:4" ht="34" customHeight="1">
-      <c r="A5" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-    </row>
-    <row r="6" spans="1:4" ht="34" customHeight="1">
-      <c r="A6" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-    </row>
-    <row r="7" spans="1:4" ht="34" customHeight="1">
-      <c r="A7" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-    </row>
-    <row r="8" spans="1:4" ht="34" customHeight="1">
-      <c r="A8" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:4" ht="34" customHeight="1">
-      <c r="A9" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/RWF_Entourage.xlsx
+++ b/RWF_Entourage.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise 2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87C7E253-17AB-3745-A761-5A8A48E996EE}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72551B27-2F30-F147-88AF-8923F1D6667E}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="44800" windowHeight="24600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5700" yWindow="880" windowWidth="44800" windowHeight="24600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entourage" sheetId="1" r:id="rId1"/>
@@ -444,9 +444,6 @@
     <t>film-1976-roulette-chinoise; film-1977-la-femme-du-chef-de-gare; film-1978-despair; film-1979-la-troisieme-generation; film-1980-berlin-alexanderplatz; film-1981-le-secret-de-veronika-voss; film-1981-lola-une-femme-allemande</t>
   </si>
   <si>
-    <t>Fig essentielle de la dernière période, à la fois techniquement indispensable et historiquement décisive pour la conservation de l’héritage Fassbinder</t>
-  </si>
-  <si>
     <t>Lorenz.jpg</t>
   </si>
   <si>
@@ -672,9 +669,6 @@
   </si>
   <si>
     <t>Factory / période centrale</t>
-  </si>
-  <si>
-    <t>Jeu, théâtre Le Monde sur le Le monde sur un fil (1973)  (1973)mé, relation de pouvoir</t>
   </si>
   <si>
     <t>Proche du milieu artistique, sans statut de relation intime centrale comparable aux membres du noyau fondateur</t>
@@ -820,28 +814,34 @@
     <t>Grande figure du conflit conjugal, social et psychique</t>
   </si>
   <si>
-    <t>Couple avec Karlheinz Böhm</t>
-  </si>
-  <si>
     <t>Fascination du méchant, journaliste, Reinhold</t>
   </si>
   <si>
     <t>Corps de la frustration sociale, de l'aliénation et du domestique</t>
   </si>
   <si>
-    <t>Collaborateur total, à la frontière du jeu et de la fabrication matérielle, Chef Décorateur , identité visuelle des films de RWF</t>
-  </si>
-  <si>
     <t>Lien entre théâtre et premiers essais filmiques</t>
   </si>
   <si>
-    <t>Sensualité,  populaire, Incarne souvent des personnages de travestis ou qui se déguisent, il incarne une inquiétante étrangeté.</t>
-  </si>
-  <si>
     <t>Hermann</t>
   </si>
   <si>
     <t xml:space="preserve"> Irm</t>
+  </si>
+  <si>
+    <t>Jeu, théâtre filmé, relation de pouvoir</t>
+  </si>
+  <si>
+    <t>Figure sensuelle et populaire</t>
+  </si>
+  <si>
+    <t>Collaborateur total, à la frontière du jeu et de la fabrication matérielle, chef décorateur , identité visuelle des films de RWF</t>
+  </si>
+  <si>
+    <t>Figure essentielle de la dernière période, à la fois techniquement indispensable et historiquement décisive pour la conservation de l’héritage Fassbinder</t>
+  </si>
+  <si>
+    <t>Incarne souvent des personnages de travestis ou qui se déguisent, dégage une inquiétante étrangeté.</t>
   </si>
 </sst>
 </file>
@@ -983,7 +983,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1039,6 +1039,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1064,6 +1067,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1390,42 +1397,42 @@
     </row>
     <row r="3" spans="1:14" ht="72" customHeight="1">
       <c r="A3" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>194</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="9" t="s">
         <v>199</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>200</v>
       </c>
       <c r="L3" s="3"/>
       <c r="M3" s="18" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="72" customHeight="1">
@@ -1470,16 +1477,16 @@
     </row>
     <row r="5" spans="1:14" ht="72" customHeight="1">
       <c r="A5" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
@@ -1489,37 +1496,37 @@
         <v>19</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="K5" s="9" t="s">
         <v>148</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>149</v>
       </c>
       <c r="L5" s="3"/>
       <c r="M5" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="N5" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="72" customHeight="1">
       <c r="A6" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>184</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>185</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
@@ -1529,23 +1536,23 @@
         <v>30</v>
       </c>
       <c r="H6" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="K6" s="9" t="s">
         <v>188</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>189</v>
       </c>
       <c r="L6" s="3"/>
       <c r="M6" s="18" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="72" customHeight="1">
@@ -1582,7 +1589,7 @@
       </c>
       <c r="L7" s="3"/>
       <c r="M7" s="18" t="s">
-        <v>264</v>
+        <v>122</v>
       </c>
       <c r="N7" s="3" t="s">
         <v>123</v>
@@ -1590,80 +1597,80 @@
     </row>
     <row r="8" spans="1:14" ht="72" customHeight="1">
       <c r="A8" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>213</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>214</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H8" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="K8" s="9" t="s">
         <v>217</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>219</v>
       </c>
       <c r="L8" s="3"/>
       <c r="M8" s="18" t="s">
-        <v>122</v>
+        <v>218</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="72" customHeight="1">
       <c r="A9" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>173</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>174</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="K9" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="K9" s="9" t="s">
+      <c r="L9" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="M9" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="M9" s="18" t="s">
-        <v>220</v>
-      </c>
       <c r="N9" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="72" customHeight="1">
@@ -1696,7 +1703,7 @@
       </c>
       <c r="L10" s="3"/>
       <c r="M10" s="18" t="s">
-        <v>180</v>
+        <v>262</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>77</v>
@@ -1710,10 +1717,10 @@
         <v>125</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -1734,7 +1741,7 @@
       </c>
       <c r="L11" s="3"/>
       <c r="M11" s="18" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="N11" s="3" t="s">
         <v>130</v>
@@ -1774,7 +1781,7 @@
       </c>
       <c r="L12" s="3"/>
       <c r="M12" s="18" t="s">
-        <v>266</v>
+        <v>87</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>88</v>
@@ -1782,36 +1789,34 @@
     </row>
     <row r="13" spans="1:14" ht="72" customHeight="1">
       <c r="A13" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>225</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="L13" s="3"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="L13" s="3"/>
-      <c r="M13" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="72" customHeight="1">
@@ -1845,9 +1850,11 @@
         <v>139</v>
       </c>
       <c r="L14" s="3"/>
-      <c r="M14" s="18"/>
+      <c r="M14" s="18" t="s">
+        <v>270</v>
+      </c>
       <c r="N14" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="72" customHeight="1">
@@ -1884,7 +1891,7 @@
       </c>
       <c r="L15" s="3"/>
       <c r="M15" s="18" t="s">
-        <v>140</v>
+        <v>24</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>25</v>
@@ -1924,7 +1931,7 @@
       </c>
       <c r="L16" s="3"/>
       <c r="M16" s="18" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="N16" s="3" t="s">
         <v>46</v>
@@ -1932,78 +1939,78 @@
     </row>
     <row r="17" spans="1:14" ht="72" customHeight="1">
       <c r="A17" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>155</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3" t="s">
         <v>93</v>
       </c>
       <c r="G17" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="H17" s="3" t="s">
+      <c r="I17" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="J17" s="3" t="s">
+      <c r="K17" s="9" t="s">
         <v>159</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>160</v>
       </c>
       <c r="L17" s="3"/>
       <c r="M17" s="18" t="s">
-        <v>45</v>
+        <v>269</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="72" customHeight="1">
       <c r="A18" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>205</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3" t="s">
         <v>93</v>
       </c>
       <c r="G18" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="I18" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>208</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="9"/>
       <c r="L18" s="3"/>
       <c r="M18" s="18" t="s">
-        <v>267</v>
+        <v>208</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="72" customHeight="1">
@@ -2040,7 +2047,7 @@
       </c>
       <c r="L19" s="3"/>
       <c r="M19" s="18" t="s">
-        <v>209</v>
+        <v>57</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>58</v>
@@ -2082,7 +2089,7 @@
         <v>99</v>
       </c>
       <c r="M20" s="18" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>101</v>
@@ -2090,56 +2097,56 @@
     </row>
     <row r="21" spans="1:14" ht="72" customHeight="1">
       <c r="A21" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>231</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>233</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>30</v>
       </c>
       <c r="H21" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="K21" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="L21" s="3"/>
       <c r="M21" s="18" t="s">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="72" customHeight="1">
       <c r="A22" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>165</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3" t="s">
@@ -2152,20 +2159,20 @@
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="K22" s="9" t="s">
         <v>167</v>
-      </c>
-      <c r="K22" s="9" t="s">
-        <v>168</v>
       </c>
       <c r="L22" s="3"/>
       <c r="M22" s="18" t="s">
-        <v>268</v>
+        <v>168</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="72" customHeight="1">
@@ -2199,8 +2206,8 @@
         <v>34</v>
       </c>
       <c r="L23" s="3"/>
-      <c r="M23" s="18" t="s">
-        <v>169</v>
+      <c r="M23" s="19" t="s">
+        <v>268</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>35</v>
@@ -2208,16 +2215,16 @@
     </row>
     <row r="24" spans="1:14" ht="72" customHeight="1">
       <c r="A24" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="D24" s="4" t="s">
         <v>241</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>243</v>
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
@@ -2229,17 +2236,17 @@
       </c>
       <c r="I24" s="4"/>
       <c r="J24" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="L24" s="4"/>
       <c r="M24" s="18" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -2261,79 +2268,79 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
-      <c r="A1" s="19" t="s">
-        <v>247</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
+      <c r="A1" s="20" t="s">
+        <v>245</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
     </row>
     <row r="3" spans="1:4" ht="34" customHeight="1">
       <c r="A3" s="11" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
     </row>
     <row r="4" spans="1:4" ht="34" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
     </row>
     <row r="5" spans="1:4" ht="34" customHeight="1">
       <c r="A5" s="13" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
     </row>
     <row r="6" spans="1:4" ht="34" customHeight="1">
       <c r="A6" s="13" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
     </row>
     <row r="7" spans="1:4" ht="34" customHeight="1">
       <c r="A7" s="13" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
     </row>
     <row r="8" spans="1:4" ht="34" customHeight="1">
       <c r="A8" s="13" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
     </row>
     <row r="9" spans="1:4" ht="34" customHeight="1">
       <c r="A9" s="15" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>

--- a/RWF_Entourage.xlsx
+++ b/RWF_Entourage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72551B27-2F30-F147-88AF-8923F1D6667E}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDD91AC3-AB95-CC47-83AC-EE0E9D47DA8A}"/>
   <bookViews>
-    <workbookView xWindow="5700" yWindow="880" windowWidth="44800" windowHeight="24600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="29400" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entourage" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="282">
   <si>
     <t>ID canonique</t>
   </si>
@@ -842,13 +842,83 @@
   </si>
   <si>
     <t>Incarne souvent des personnages de travestis ou qui se déguisent, dégage une inquiétante étrangeté.</t>
+  </si>
+  <si>
+    <t>Elisabeth</t>
+  </si>
+  <si>
+    <t>Elisabeth Trissenaar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actrice autrichienne de formatrice classique, elle est formée au prestigieux Max Reinhardt Seminar. Elle rejoint l'univers de RWF en 1974 pour une production au Theater am Turm (TAT) de Francfort. Perçue comme une intruse par le premier cercle, son travail avec le metteur en scène et compagnon Hans Neuenfelsla matintient à une certaine distance critique vis-à-vis du « système » Fassbinder, ne vivant jamais en communauté avec le groupe. </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Aux côtés de Schygulla (la malléable) et de Carstensen (la nerveuse), Trissenaar incarne une féminité plus mûre, terrienne et dotée d'une autorité naturelle. Fassbinder l'utilise pour son jeu stylisé. Son personnage dans </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>La femme du chef de gare</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> présente des points communs avec celui d'Elvira dans </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>l'année des treize lunes :</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> elle aussi être prête à abandonner son identité au nom du désir. </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeu, prestige d'une actrice renommée. </t>
+  </si>
+  <si>
+    <t>Trissenaar.jpeg</t>
+  </si>
+  <si>
+    <t>pers-elisabeth-trissenaar</t>
+  </si>
+  <si>
+    <t>La Femme du chef de gare; L’Année des treize lunes; Le Mariage de Maria Braun; Berlin Alexanderplatz</t>
+  </si>
+  <si>
+    <t>film-1977-la-femme-du-chef-de-gare; film-1978-l-annee-des-treize-lunes; film-1979-le-mariage-de-maria-braun; film-1980-berlin-alexanderplatz</t>
+  </si>
+  <si>
+    <t>Trissenaar</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -892,6 +962,25 @@
       <color rgb="FF333333"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="IBM Plex Mono"/>
     </font>
   </fonts>
   <fills count="4">
@@ -983,7 +1072,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1042,7 +1131,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1074,9 +1169,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EntourageV30" displayName="EntourageV30" ref="A1:N24" totalsRowShown="0">
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N24">
-    <sortCondition ref="C1:C24"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EntourageV30" displayName="EntourageV30" ref="A1:N25" totalsRowShown="0">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N25">
+    <sortCondition ref="C1:C25"/>
   </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID canonique"/>
@@ -1293,7 +1388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
@@ -2136,60 +2231,62 @@
       </c>
     </row>
     <row r="22" spans="1:14" ht="72" customHeight="1">
-      <c r="A22" s="6" t="s">
-        <v>161</v>
+      <c r="A22" s="22" t="s">
+        <v>278</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>162</v>
+        <v>273</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>163</v>
+        <v>281</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>30</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>31</v>
+        <v>276</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>166</v>
+        <v>274</v>
+      </c>
+      <c r="J22" s="20" t="s">
+        <v>279</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>167</v>
+        <v>280</v>
       </c>
       <c r="L22" s="3"/>
       <c r="M22" s="18" t="s">
-        <v>168</v>
+        <v>275</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>169</v>
+        <v>277</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="72" customHeight="1">
       <c r="A23" s="6" t="s">
-        <v>26</v>
+        <v>161</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>27</v>
+        <v>162</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>28</v>
+        <v>163</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>29</v>
+        <v>164</v>
       </c>
       <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
+      <c r="F23" s="3" t="s">
+        <v>82</v>
+      </c>
       <c r="G23" s="3" t="s">
         <v>30</v>
       </c>
@@ -2197,55 +2294,93 @@
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="K23" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="L23" s="3"/>
+      <c r="M23" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="72" customHeight="1">
+      <c r="A24" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="K23" s="9" t="s">
+      <c r="K24" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L23" s="3"/>
-      <c r="M23" s="19" t="s">
+      <c r="L24" s="3"/>
+      <c r="M24" s="19" t="s">
         <v>268</v>
       </c>
-      <c r="N23" s="3" t="s">
+      <c r="N24" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="72" customHeight="1">
-      <c r="A24" s="7" t="s">
+    <row r="25" spans="1:14" ht="72" customHeight="1">
+      <c r="A25" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B25" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C25" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D25" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4" t="s">
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="H25" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4" t="s">
+      <c r="I25" s="4"/>
+      <c r="J25" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="K24" s="10" t="s">
+      <c r="K25" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="L24" s="4"/>
-      <c r="M24" s="18" t="s">
+      <c r="L25" s="4"/>
+      <c r="M25" s="18" t="s">
         <v>271</v>
       </c>
-      <c r="N24" s="4" t="s">
+      <c r="N25" s="4" t="s">
         <v>244</v>
       </c>
     </row>
@@ -2268,12 +2403,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>245</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
     </row>
     <row r="3" spans="1:4" ht="34" customHeight="1">
       <c r="A3" s="11" t="s">

--- a/RWF_Entourage.xlsx
+++ b/RWF_Entourage.xlsx
@@ -8,20 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDD91AC3-AB95-CC47-83AC-EE0E9D47DA8A}"/>
+  <xr:revisionPtr revIDLastSave="123" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FC6438C-5FF4-294D-BCE5-E2269E718857}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="29400" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8460" yWindow="4600" windowWidth="29400" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entourage" sheetId="1" r:id="rId1"/>
     <sheet name="Mode_emploi" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="302">
   <si>
     <t>ID canonique</t>
   </si>
@@ -913,12 +926,122 @@
   <si>
     <t>Trissenaar</t>
   </si>
+  <si>
+    <t>pers-waldleitner-luggi</t>
+  </si>
+  <si>
+    <t>Luggi Waldleitner</t>
+  </si>
+  <si>
+    <t>Waldleitner</t>
+  </si>
+  <si>
+    <t>Luggi</t>
+  </si>
+  <si>
+    <t>Producteur</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">RWF se rapproche de Waldleitner pour Berlin Alexander Plats. La pbrouille du cinéaste avec son producteur historique, Fengler ) propos des droits du </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>Mariage de Maria Braun</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> ouvre de nouvelles collaborations. </t>
+    </r>
+  </si>
+  <si>
+    <t>Waldleitner.jpeg</t>
+  </si>
+  <si>
+    <t>Lili Marleen;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rwf-1981-lili-marleen; </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Producteur de films divertissants faisant quelques incursions dans le cinéma de prestigue, d'auteur. </t>
+  </si>
+  <si>
+    <t>Production de prestige; Collaboration ponctuelle et opportuniste</t>
+  </si>
+  <si>
+    <t>Fengler</t>
+  </si>
+  <si>
+    <t>Michael Fengler</t>
+  </si>
+  <si>
+    <t>pers-michael-fengler</t>
+  </si>
+  <si>
+    <t>Producteur, collaborateur</t>
+  </si>
+  <si>
+    <t>Il fait partie du groupe qui fonde l'antiteater et la société de production antiteater-X-Film</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Il assure la photographie du court-métrage Le Petit Chaos (1967) et participe au montage du Clochard (1966). Il l co-réalise </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Pourquoi monsieur R. est-il atteint de folie meurtrière</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ? (1970). Produit plus de 12 films de RWF.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">un des plus proches collaborateurs de RWF jusqu'à son éviction après </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Maria Braun</t>
+    </r>
+  </si>
+  <si>
+    <t>Petit Chaos; Le Clochard; Le Bouc; Les Dieux de la peste; Pourquoi M. R. est-il atteint de folie meurtrière ?; Le Voyage à Niklashausen; Rio das Mortes; Whity; Le Marchand des quatre saisons; Le Rôti de Satan; Roulette chinoise; Le Mariage de Maria Braun</t>
+  </si>
+  <si>
+    <t>film-1966-le-clochard; film-1967-le-clochard; film-1969-le-bouc; film-1969-l-amour-est-plus-froid-que-la-mort; film-1970-les-dieux-de-la-peste; film-1970-pourquoi-m-r-est-il-atteint-de-folie-meurtriere; film-1970-rio-das-mortes; film-1971-prenez-garde-a-la-sainte-putain; film-1971-whity; film-1972-le-marchand-des-quatre-saisons; film-1976-le-roti-de-satan; film-1976-roulette-chinoise; film-1979-le-mariage-de-maria-braun</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -980,6 +1103,15 @@
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
+      <name val="IBM Plex Mono"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="IBM Plex Mono"/>
     </font>
   </fonts>
@@ -1072,7 +1204,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1134,9 +1266,21 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1169,9 +1313,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EntourageV30" displayName="EntourageV30" ref="A1:N25" totalsRowShown="0">
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N25">
-    <sortCondition ref="C1:C25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EntourageV30" displayName="EntourageV30" ref="A1:N27" totalsRowShown="0">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N27">
+    <sortCondition ref="C1:C27"/>
   </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID canonique"/>
@@ -1388,7 +1532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
@@ -1770,561 +1914,561 @@
     </row>
     <row r="10" spans="1:14" ht="72" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>70</v>
+        <v>295</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>71</v>
+        <v>294</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>72</v>
+        <v>293</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>73</v>
+        <v>193</v>
       </c>
       <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
+      <c r="F10" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="G10" s="3" t="s">
-        <v>19</v>
+        <v>296</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="I10" s="3"/>
+        <v>299</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>297</v>
+      </c>
       <c r="J10" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>76</v>
+        <v>300</v>
+      </c>
+      <c r="K10" s="26" t="s">
+        <v>301</v>
       </c>
       <c r="L10" s="3"/>
       <c r="M10" s="18" t="s">
-        <v>262</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>77</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="N10" s="3"/>
     </row>
     <row r="11" spans="1:14" ht="72" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>125</v>
+        <v>71</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>265</v>
+        <v>72</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>266</v>
+        <v>73</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>127</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>128</v>
+        <v>75</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="L11" s="3"/>
       <c r="M11" s="18" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>130</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="72" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>78</v>
+        <v>124</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>79</v>
+        <v>125</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>80</v>
+        <v>265</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>81</v>
+        <v>266</v>
       </c>
       <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>82</v>
-      </c>
+      <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>83</v>
+        <v>126</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="L12" s="3"/>
       <c r="M12" s="18" t="s">
-        <v>87</v>
+        <v>263</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>88</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="72" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>220</v>
+        <v>78</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>221</v>
+        <v>79</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>222</v>
+        <v>80</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>223</v>
+        <v>81</v>
       </c>
       <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>82</v>
+      </c>
       <c r="G13" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>84</v>
+      </c>
       <c r="J13" s="3" t="s">
-        <v>225</v>
+        <v>85</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>226</v>
+        <v>86</v>
       </c>
       <c r="L13" s="3"/>
-      <c r="M13" s="19"/>
+      <c r="M13" s="18" t="s">
+        <v>87</v>
+      </c>
       <c r="N13" s="3" t="s">
-        <v>227</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="72" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>131</v>
+        <v>220</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>132</v>
+        <v>221</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>133</v>
+        <v>222</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>134</v>
+        <v>223</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>137</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>138</v>
+        <v>225</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>139</v>
+        <v>226</v>
       </c>
       <c r="L14" s="3"/>
-      <c r="M14" s="18" t="s">
-        <v>270</v>
-      </c>
+      <c r="M14" s="19"/>
       <c r="N14" s="3" t="s">
-        <v>140</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="72" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>14</v>
+        <v>131</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>16</v>
+        <v>133</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>17</v>
+        <v>134</v>
       </c>
       <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>18</v>
-      </c>
+      <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
-        <v>19</v>
+        <v>135</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>20</v>
+        <v>136</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>21</v>
+        <v>137</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>22</v>
+        <v>138</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>23</v>
+        <v>139</v>
       </c>
       <c r="L15" s="3"/>
       <c r="M15" s="18" t="s">
-        <v>24</v>
+        <v>270</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>25</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="72" customHeight="1">
       <c r="A16" s="6" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="L16" s="3"/>
       <c r="M16" s="18" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="72" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>151</v>
+        <v>36</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>152</v>
+        <v>37</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>153</v>
+        <v>38</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>154</v>
+        <v>39</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3" t="s">
-        <v>93</v>
+        <v>40</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>155</v>
+        <v>30</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>157</v>
+        <v>42</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>158</v>
+        <v>43</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>159</v>
+        <v>44</v>
       </c>
       <c r="L17" s="3"/>
       <c r="M17" s="18" t="s">
-        <v>269</v>
+        <v>45</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>160</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="72" customHeight="1">
       <c r="A18" s="6" t="s">
-        <v>201</v>
+        <v>151</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>202</v>
+        <v>152</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>203</v>
+        <v>153</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>204</v>
+        <v>154</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3" t="s">
         <v>93</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>205</v>
+        <v>155</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>206</v>
+        <v>156</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="9"/>
+        <v>157</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>159</v>
+      </c>
       <c r="L18" s="3"/>
       <c r="M18" s="18" t="s">
-        <v>208</v>
+        <v>269</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>209</v>
+        <v>160</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="72" customHeight="1">
       <c r="A19" s="6" t="s">
-        <v>47</v>
+        <v>201</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>48</v>
+        <v>202</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>49</v>
+        <v>203</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>50</v>
+        <v>204</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>52</v>
+        <v>205</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>53</v>
+        <v>206</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>56</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="J19" s="3"/>
+      <c r="K19" s="9"/>
       <c r="L19" s="3"/>
       <c r="M19" s="18" t="s">
-        <v>57</v>
+        <v>208</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>58</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="72" customHeight="1">
       <c r="A20" s="6" t="s">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>91</v>
+        <v>49</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>94</v>
+        <v>52</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>99</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="L20" s="3"/>
       <c r="M20" s="18" t="s">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>101</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="72" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>228</v>
+        <v>89</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>229</v>
+        <v>90</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>230</v>
+        <v>91</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>231</v>
+        <v>92</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3" t="s">
-        <v>232</v>
+        <v>93</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>233</v>
+        <v>95</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>234</v>
+        <v>96</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>235</v>
+        <v>97</v>
       </c>
       <c r="K21" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="L21" s="3"/>
+        <v>98</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>99</v>
+      </c>
       <c r="M21" s="18" t="s">
-        <v>264</v>
+        <v>100</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>237</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="72" customHeight="1">
-      <c r="A22" s="22" t="s">
-        <v>278</v>
+      <c r="A22" s="6" t="s">
+        <v>228</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>273</v>
+        <v>229</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>281</v>
+        <v>230</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>272</v>
+        <v>231</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3" t="s">
-        <v>51</v>
+        <v>232</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>30</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>276</v>
+        <v>233</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="J22" s="20" t="s">
-        <v>279</v>
+        <v>234</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>235</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>280</v>
+        <v>236</v>
       </c>
       <c r="L22" s="3"/>
       <c r="M22" s="18" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>277</v>
+        <v>237</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="72" customHeight="1">
-      <c r="A23" s="6" t="s">
-        <v>161</v>
+      <c r="A23" s="21" t="s">
+        <v>278</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>162</v>
+        <v>273</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>163</v>
+        <v>281</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>30</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>31</v>
+        <v>276</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>166</v>
+        <v>274</v>
+      </c>
+      <c r="J23" s="20" t="s">
+        <v>279</v>
       </c>
       <c r="K23" s="9" t="s">
-        <v>167</v>
+        <v>280</v>
       </c>
       <c r="L23" s="3"/>
       <c r="M23" s="18" t="s">
-        <v>168</v>
+        <v>275</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>169</v>
+        <v>277</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="72" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>26</v>
+        <v>161</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>27</v>
+        <v>162</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>28</v>
+        <v>163</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>29</v>
+        <v>164</v>
       </c>
       <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
+      <c r="F24" s="3" t="s">
+        <v>82</v>
+      </c>
       <c r="G24" s="3" t="s">
         <v>30</v>
       </c>
@@ -2332,56 +2476,132 @@
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="K24" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="L24" s="3"/>
+      <c r="M24" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="72" customHeight="1">
+      <c r="A25" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J24" s="3" t="s">
+      <c r="J25" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="K24" s="9" t="s">
+      <c r="K25" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L24" s="3"/>
-      <c r="M24" s="19" t="s">
+      <c r="L25" s="3"/>
+      <c r="M25" s="19" t="s">
         <v>268</v>
       </c>
-      <c r="N24" s="3" t="s">
+      <c r="N25" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="72" customHeight="1">
-      <c r="A25" s="7" t="s">
+    <row r="26" spans="1:14" ht="72" customHeight="1">
+      <c r="A26" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B26" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C26" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D26" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4" t="s">
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H25" s="4" t="s">
+      <c r="H26" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4" t="s">
+      <c r="I26" s="4"/>
+      <c r="J26" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="K25" s="10" t="s">
+      <c r="K26" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="L25" s="4"/>
-      <c r="M25" s="18" t="s">
+      <c r="L26" s="4"/>
+      <c r="M26" s="18" t="s">
         <v>271</v>
       </c>
-      <c r="N25" s="4" t="s">
+      <c r="N26" s="4" t="s">
         <v>244</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" s="22" customFormat="1" ht="108" customHeight="1">
+      <c r="A27" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>283</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>284</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="F27" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="G27" s="22" t="s">
+        <v>286</v>
+      </c>
+      <c r="H27" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="I27" s="23" t="s">
+        <v>287</v>
+      </c>
+      <c r="J27" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="K27" s="23" t="s">
+        <v>290</v>
+      </c>
+      <c r="M27" s="24" t="s">
+        <v>291</v>
+      </c>
+      <c r="N27" s="22" t="s">
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -2403,12 +2623,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="25" t="s">
         <v>245</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
     </row>
     <row r="3" spans="1:4" ht="34" customHeight="1">
       <c r="A3" s="11" t="s">

--- a/RWF_Entourage.xlsx
+++ b/RWF_Entourage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="123" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FC6438C-5FF4-294D-BCE5-E2269E718857}"/>
+  <xr:revisionPtr revIDLastSave="124" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61F4F2DD-DFC0-A34B-A22C-C6712AA958A5}"/>
   <bookViews>
-    <workbookView xWindow="8460" yWindow="4600" windowWidth="29400" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="29400" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entourage" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="303">
   <si>
     <t>ID canonique</t>
   </si>
@@ -1035,6 +1035,9 @@
   </si>
   <si>
     <t>film-1966-le-clochard; film-1967-le-clochard; film-1969-le-bouc; film-1969-l-amour-est-plus-froid-que-la-mort; film-1970-les-dieux-de-la-peste; film-1970-pourquoi-m-r-est-il-atteint-de-folie-meurtriere; film-1970-rio-das-mortes; film-1971-prenez-garde-a-la-sainte-putain; film-1971-whity; film-1972-le-marchand-des-quatre-saisons; film-1976-le-roti-de-satan; film-1976-roulette-chinoise; film-1979-le-mariage-de-maria-braun</t>
+  </si>
+  <si>
+    <t>Fengler.jpg</t>
   </si>
 </sst>
 </file>
@@ -1278,10 +1281,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1941,14 +1944,16 @@
       <c r="J10" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="K10" s="26" t="s">
+      <c r="K10" s="25" t="s">
         <v>301</v>
       </c>
       <c r="L10" s="3"/>
       <c r="M10" s="18" t="s">
         <v>298</v>
       </c>
-      <c r="N10" s="3"/>
+      <c r="N10" s="3" t="s">
+        <v>302</v>
+      </c>
     </row>
     <row r="11" spans="1:14" ht="72" customHeight="1">
       <c r="A11" s="6" t="s">
@@ -2623,12 +2628,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>245</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
     </row>
     <row r="3" spans="1:4" ht="34" customHeight="1">
       <c r="A3" s="11" t="s">

--- a/RWF_Entourage.xlsx
+++ b/RWF_Entourage.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise_Fassbinder/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="124" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61F4F2DD-DFC0-A34B-A22C-C6712AA958A5}"/>
+  <xr:revisionPtr revIDLastSave="170" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6B9E8A1-0809-A74D-A644-FB185C63A2CE}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="29400" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="315">
   <si>
     <t>ID canonique</t>
   </si>
@@ -326,12 +326,6 @@
   </si>
   <si>
     <t>Proche collaboratrice de longue durée, liée au noyau fondateur du groupe et à l’intimité artistique de Fassbinder</t>
-  </si>
-  <si>
-    <t>L’Amour est plus froid que la mort; Le Bouc; Les Dieux de la peste; Prenez garde à la sainte putain; Huit heures ne font pas un jour; Le Marchand des quatre saisons; Les Larmes amères de Petra von Kant; Effi Briest; La Troisième génération; Le Mariage de Maria Braun; Berlin Alexanderplatz; Lili Marleen</t>
-  </si>
-  <si>
-    <t>film-1969-l-amour-est-plus-froid-que-la-mort; film-1969-le-bouc; film-1970-les-dieux-de-la-peste; film-1971-prenez-garde-a-la-sainte-putain; film-1972-huit-heures-ne-font-pas-un-jour; film-1972-le-marchand-des-quatre-saisons; film-1972-les-larmes-ameres-de-petra-von-kant; film-1974-effi-briest; film-1979-la-troisieme-generation; film-1979-le-mariage-de-maria-braun; film-1980-berlin-alexanderplatz; film-1981-lili-marleen</t>
   </si>
   <si>
     <t>Rio das Mortes</t>
@@ -942,26 +936,6 @@
     <t>Producteur</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">RWF se rapproche de Waldleitner pour Berlin Alexander Plats. La pbrouille du cinéaste avec son producteur historique, Fengler ) propos des droits du </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>Mariage de Maria Braun</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t xml:space="preserve"> ouvre de nouvelles collaborations. </t>
-    </r>
-  </si>
-  <si>
     <t>Waldleitner.jpeg</t>
   </si>
   <si>
@@ -969,12 +943,6 @@
   </si>
   <si>
     <t xml:space="preserve">rwf-1981-lili-marleen; </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Producteur de films divertissants faisant quelques incursions dans le cinéma de prestigue, d'auteur. </t>
-  </si>
-  <si>
-    <t>Production de prestige; Collaboration ponctuelle et opportuniste</t>
   </si>
   <si>
     <t>Fengler</t>
@@ -1039,12 +1007,135 @@
   <si>
     <t>Fengler.jpg</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">RWF se rapproche de Waldleitner pour Berlin Alexander Plats. La brouille du cinéaste avec son producteur historique, Fengler à propos des droits du </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>Mariage de Maria Braun</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> ouvre de nouvelles collaborations. Waldleitner est à l'origine du projet de </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>Lili Marleen, dont il détroit les droits de la chanson</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Production de prestige; Collaboration ponctuelle et opportuniste; </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Producteur majeur du cinéma ouest allemand, plutôt tourné vers l'industrie et les films divertissants. Il fait quelques incursions dans le cinéma de prestigue, d'auteur. </t>
+  </si>
+  <si>
+    <t>Bohm</t>
+  </si>
+  <si>
+    <t>Le Soldat américain;Prenez garde à la sainte putain; Tous les autres s’appellent Ali;Le Droit du plus fort; Le Rôti de Satan; Berlin Alexanderplatz</t>
+  </si>
+  <si>
+    <t>film-1970-le-soldat-americain; film-1971-prenez-garde-a-la-sainte-putain; film-1974-tous-les-autres-s-appellent-ali;film-1975-le-droit-du-plus-fort; film-1976-le-roti-de-satan; film-1980-berlin-alexanderplatz</t>
+  </si>
+  <si>
+    <t>film-1969-l-amour-est-plus-froid-que-la-mort; film-1969-le-bouc; film-1970-les-dieux-de-la-peste; film-1970-rio-das-mortes; film-1971-prenez-garde-a-la-sainte-putain; film-1972-huit-heures-ne-font-pas-un-jour; film-1972-le-marchand-des-quatre-saisons; film-1972-les-larmes-ameres-de-petra-von-kant; film-1974-effi-briest; film-1979-la-troisieme-generation; film-1979-le-mariage-de-maria-braun; film-1980-berlin-alexanderplatz; film-1981-lili-marleen</t>
+  </si>
+  <si>
+    <t>L’Amour est plus froid que la mort; Le Bouc; Les Dieux de la peste; Rio das Mortes; Prenez garde à la sainte putain; Huit heures ne font pas un jour; Le Marchand des quatre saisons; Les Larmes amères de Petra von Kant; Effi Briest; La Troisième génération; Le Mariage de Maria Braun; Berlin Alexanderplatz; Lili Marleen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collaboration durant toute la carrière de RWF. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeu. </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Un des "mauvais garçons" du Nouveau cinéma allemand. Il est associé à  l'« École de Munich », tournant pour des réalisateurs comme Rudolf Thome, Klaus Lemke ou Roland Klick avant de collaborer avec RWF pour lequel il offre une relecture du gangster de film noir. Il est le "doc" du </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Soldat américain et tient le rôle principal de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Prenez garde à la sainte putain. Fils de Martha dans</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tous les autres s'appellent Ali</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, il devient une figure de l'oppression ordinaire. virilité ironique et désenchantée</t>
+    </r>
+  </si>
+  <si>
+    <t>Noyau théâtral / Stock company/ période centrale et tardive</t>
+  </si>
+  <si>
+    <t>stock company</t>
+  </si>
+  <si>
+    <t>Hark</t>
+  </si>
+  <si>
+    <t>Hark Bohm</t>
+  </si>
+  <si>
+    <t>pers-hark-bohm</t>
+  </si>
+  <si>
+    <t>Bohm.H.jpg</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1116,6 +1207,11 @@
     <font>
       <sz val="8"/>
       <name val="IBM Plex Mono"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1278,13 +1374,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1316,9 +1412,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EntourageV30" displayName="EntourageV30" ref="A1:N27" totalsRowShown="0">
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N27">
-    <sortCondition ref="C1:C27"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EntourageV30" displayName="EntourageV30" ref="A1:N28" totalsRowShown="0">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N28">
+    <sortCondition ref="C1:C28"/>
   </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID canonique"/>
@@ -1535,8 +1631,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <dimension ref="A1:N28"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -1599,82 +1695,82 @@
     </row>
     <row r="2" spans="1:14" ht="72" customHeight="1">
       <c r="A2" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="K2" s="8" t="s">
         <v>108</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>110</v>
       </c>
       <c r="L2" s="2"/>
       <c r="M2" s="18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="72" customHeight="1">
       <c r="A3" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>193</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="K3" s="9" t="s">
         <v>197</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>199</v>
       </c>
       <c r="L3" s="3"/>
       <c r="M3" s="18" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="72" customHeight="1">
@@ -1719,16 +1815,16 @@
     </row>
     <row r="5" spans="1:14" ht="72" customHeight="1">
       <c r="A5" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>144</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
@@ -1738,780 +1834,782 @@
         <v>19</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="K5" s="9" t="s">
         <v>146</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>148</v>
       </c>
       <c r="L5" s="3"/>
       <c r="M5" s="18" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="72" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>181</v>
+        <v>313</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>182</v>
+        <v>312</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>184</v>
+        <v>301</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>311</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>82</v>
+        <v>310</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>185</v>
+        <v>307</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>186</v>
+        <v>306</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>187</v>
+        <v>302</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>188</v>
+        <v>303</v>
       </c>
       <c r="L6" s="3"/>
       <c r="M6" s="18" t="s">
-        <v>261</v>
+        <v>308</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>189</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="72" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>113</v>
+        <v>179</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>114</v>
+        <v>180</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>115</v>
+        <v>181</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>116</v>
+        <v>182</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>117</v>
+        <v>30</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>118</v>
+        <v>183</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>119</v>
+        <v>184</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>120</v>
+        <v>185</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="L7" s="3"/>
       <c r="M7" s="18" t="s">
-        <v>122</v>
+        <v>259</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>123</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="72" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>210</v>
+        <v>111</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>211</v>
+        <v>112</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>212</v>
+        <v>113</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>213</v>
+        <v>114</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>214</v>
+        <v>309</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>267</v>
+        <v>116</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>215</v>
+        <v>117</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>216</v>
+        <v>118</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>217</v>
+        <v>119</v>
       </c>
       <c r="L8" s="3"/>
       <c r="M8" s="18" t="s">
-        <v>218</v>
+        <v>120</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>219</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="72" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>170</v>
+        <v>208</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>171</v>
+        <v>209</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>172</v>
+        <v>210</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>173</v>
+        <v>211</v>
       </c>
       <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
+      <c r="F9" s="3" t="s">
+        <v>212</v>
+      </c>
       <c r="G9" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="H9" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>265</v>
+      </c>
       <c r="I9" s="3" t="s">
-        <v>175</v>
+        <v>213</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>176</v>
+        <v>214</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>178</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="L9" s="3"/>
       <c r="M9" s="18" t="s">
-        <v>179</v>
+        <v>216</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>180</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="72" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>295</v>
+        <v>168</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>294</v>
+        <v>169</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>293</v>
+        <v>170</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="E10" s="3"/>
-      <c r="F10" s="3" t="s">
-        <v>93</v>
-      </c>
+      <c r="F10" s="3"/>
       <c r="G10" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>299</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="H10" s="3"/>
       <c r="I10" s="3" t="s">
-        <v>297</v>
+        <v>173</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="K10" s="25" t="s">
-        <v>301</v>
-      </c>
-      <c r="L10" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>176</v>
+      </c>
       <c r="M10" s="18" t="s">
-        <v>298</v>
+        <v>177</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>302</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="72" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>70</v>
+        <v>290</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>71</v>
+        <v>289</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>72</v>
+        <v>288</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>73</v>
+        <v>191</v>
       </c>
       <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
+      <c r="F11" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="G11" s="3" t="s">
-        <v>19</v>
+        <v>291</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="I11" s="3"/>
+        <v>294</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>292</v>
+      </c>
       <c r="J11" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>76</v>
+        <v>295</v>
+      </c>
+      <c r="K11" s="24" t="s">
+        <v>296</v>
       </c>
       <c r="L11" s="3"/>
       <c r="M11" s="18" t="s">
-        <v>262</v>
+        <v>293</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>77</v>
+        <v>297</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="72" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>125</v>
+        <v>71</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>265</v>
+        <v>72</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>266</v>
+        <v>73</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>127</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>128</v>
+        <v>75</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="L12" s="3"/>
       <c r="M12" s="18" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>130</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="72" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>80</v>
+        <v>263</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>81</v>
+        <v>264</v>
       </c>
       <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>82</v>
-      </c>
+      <c r="F13" s="3"/>
       <c r="G13" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>84</v>
+        <v>125</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="L13" s="3"/>
       <c r="M13" s="18" t="s">
-        <v>87</v>
+        <v>261</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>88</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="72" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>220</v>
+        <v>78</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>221</v>
+        <v>79</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>222</v>
+        <v>80</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>223</v>
+        <v>81</v>
       </c>
       <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>82</v>
+      </c>
       <c r="G14" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>84</v>
+      </c>
       <c r="J14" s="3" t="s">
-        <v>225</v>
+        <v>85</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>226</v>
+        <v>86</v>
       </c>
       <c r="L14" s="3"/>
-      <c r="M14" s="19"/>
+      <c r="M14" s="18" t="s">
+        <v>87</v>
+      </c>
       <c r="N14" s="3" t="s">
-        <v>227</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="72" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>131</v>
+        <v>218</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>132</v>
+        <v>219</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>133</v>
+        <v>220</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>134</v>
+        <v>221</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>137</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>138</v>
+        <v>223</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>139</v>
+        <v>224</v>
       </c>
       <c r="L15" s="3"/>
-      <c r="M15" s="18" t="s">
-        <v>270</v>
-      </c>
+      <c r="M15" s="19"/>
       <c r="N15" s="3" t="s">
-        <v>140</v>
+        <v>225</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="72" customHeight="1">
       <c r="A16" s="6" t="s">
-        <v>14</v>
+        <v>129</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>15</v>
+        <v>130</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>16</v>
+        <v>131</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>17</v>
+        <v>132</v>
       </c>
       <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>18</v>
-      </c>
+      <c r="F16" s="3"/>
       <c r="G16" s="3" t="s">
-        <v>19</v>
+        <v>133</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>22</v>
+        <v>136</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>23</v>
+        <v>137</v>
       </c>
       <c r="L16" s="3"/>
       <c r="M16" s="18" t="s">
-        <v>24</v>
+        <v>268</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>25</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="72" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="L17" s="3"/>
       <c r="M17" s="18" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="72" customHeight="1">
       <c r="A18" s="6" t="s">
-        <v>151</v>
+        <v>36</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>152</v>
+        <v>37</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>153</v>
+        <v>38</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>154</v>
+        <v>39</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3" t="s">
-        <v>93</v>
+        <v>40</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>155</v>
+        <v>30</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>157</v>
+        <v>42</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>158</v>
+        <v>43</v>
       </c>
       <c r="K18" s="9" t="s">
-        <v>159</v>
+        <v>44</v>
       </c>
       <c r="L18" s="3"/>
       <c r="M18" s="18" t="s">
-        <v>269</v>
+        <v>45</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>160</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="72" customHeight="1">
       <c r="A19" s="6" t="s">
-        <v>201</v>
+        <v>149</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>202</v>
+        <v>150</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>203</v>
+        <v>151</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>204</v>
+        <v>152</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3" t="s">
         <v>93</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>205</v>
+        <v>153</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>206</v>
+        <v>154</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="9"/>
+        <v>155</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>157</v>
+      </c>
       <c r="L19" s="3"/>
       <c r="M19" s="18" t="s">
-        <v>208</v>
+        <v>267</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>209</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="72" customHeight="1">
       <c r="A20" s="6" t="s">
-        <v>47</v>
+        <v>199</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>48</v>
+        <v>200</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>49</v>
+        <v>201</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>50</v>
+        <v>202</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>52</v>
+        <v>203</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>53</v>
+        <v>204</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K20" s="9" t="s">
-        <v>56</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="J20" s="3"/>
+      <c r="K20" s="9"/>
       <c r="L20" s="3"/>
       <c r="M20" s="18" t="s">
-        <v>57</v>
+        <v>206</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>58</v>
+        <v>207</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="72" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>91</v>
+        <v>49</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>94</v>
+        <v>52</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
       <c r="K21" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>99</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="L21" s="3"/>
       <c r="M21" s="18" t="s">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>101</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="72" customHeight="1">
       <c r="A22" s="6" t="s">
-        <v>228</v>
+        <v>89</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>229</v>
+        <v>90</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>230</v>
+        <v>91</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>231</v>
+        <v>92</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3" t="s">
-        <v>232</v>
+        <v>93</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>233</v>
+        <v>95</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>234</v>
+        <v>96</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>235</v>
+        <v>305</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="L22" s="3"/>
+        <v>304</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>97</v>
+      </c>
       <c r="M22" s="18" t="s">
-        <v>264</v>
+        <v>98</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>237</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="72" customHeight="1">
-      <c r="A23" s="21" t="s">
-        <v>278</v>
+      <c r="A23" s="6" t="s">
+        <v>226</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>273</v>
+        <v>227</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>281</v>
+        <v>228</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>272</v>
+        <v>229</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3" t="s">
-        <v>51</v>
+        <v>230</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>30</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>276</v>
+        <v>231</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="J23" s="20" t="s">
-        <v>279</v>
+        <v>232</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>233</v>
       </c>
       <c r="K23" s="9" t="s">
-        <v>280</v>
+        <v>234</v>
       </c>
       <c r="L23" s="3"/>
       <c r="M23" s="18" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>277</v>
+        <v>235</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="72" customHeight="1">
-      <c r="A24" s="6" t="s">
-        <v>161</v>
+      <c r="A24" s="21" t="s">
+        <v>276</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>162</v>
+        <v>271</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>163</v>
+        <v>279</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>30</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>31</v>
+        <v>274</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>166</v>
+        <v>272</v>
+      </c>
+      <c r="J24" s="20" t="s">
+        <v>277</v>
       </c>
       <c r="K24" s="9" t="s">
-        <v>167</v>
+        <v>278</v>
       </c>
       <c r="L24" s="3"/>
       <c r="M24" s="18" t="s">
-        <v>168</v>
+        <v>273</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>169</v>
+        <v>275</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="72" customHeight="1">
       <c r="A25" s="6" t="s">
-        <v>26</v>
+        <v>159</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>27</v>
+        <v>160</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>28</v>
+        <v>161</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>29</v>
+        <v>162</v>
       </c>
       <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
+      <c r="F25" s="3" t="s">
+        <v>82</v>
+      </c>
       <c r="G25" s="3" t="s">
         <v>30</v>
       </c>
@@ -2519,94 +2617,132 @@
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="K25" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="L25" s="3"/>
+      <c r="M25" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="72" customHeight="1">
+      <c r="A26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J25" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="K25" s="9" t="s">
+      <c r="K26" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L25" s="3"/>
-      <c r="M25" s="19" t="s">
-        <v>268</v>
-      </c>
-      <c r="N25" s="3" t="s">
+      <c r="L26" s="3"/>
+      <c r="M26" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="N26" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="72" customHeight="1">
-      <c r="A26" s="7" t="s">
+    <row r="27" spans="1:14" ht="72" customHeight="1">
+      <c r="A27" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="D27" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="K27" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4" t="s">
+      <c r="L27" s="4"/>
+      <c r="M27" s="18" t="s">
+        <v>269</v>
+      </c>
+      <c r="N27" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="K26" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="L26" s="4"/>
-      <c r="M26" s="18" t="s">
-        <v>271</v>
-      </c>
-      <c r="N26" s="4" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" s="22" customFormat="1" ht="108" customHeight="1">
-      <c r="A27" s="22" t="s">
+    </row>
+    <row r="28" spans="1:14" s="22" customFormat="1" ht="108" customHeight="1">
+      <c r="A28" s="22" t="s">
+        <v>280</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="C28" s="22" t="s">
         <v>282</v>
       </c>
-      <c r="B27" s="22" t="s">
+      <c r="D28" s="22" t="s">
         <v>283</v>
       </c>
-      <c r="C27" s="22" t="s">
+      <c r="F28" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="G28" s="22" t="s">
         <v>284</v>
       </c>
-      <c r="D27" s="22" t="s">
+      <c r="H28" s="22" t="s">
+        <v>299</v>
+      </c>
+      <c r="I28" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="J28" s="22" t="s">
+        <v>286</v>
+      </c>
+      <c r="K28" s="23" t="s">
+        <v>287</v>
+      </c>
+      <c r="M28" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="N28" s="22" t="s">
         <v>285</v>
-      </c>
-      <c r="F27" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="G27" s="22" t="s">
-        <v>286</v>
-      </c>
-      <c r="H27" s="22" t="s">
-        <v>292</v>
-      </c>
-      <c r="I27" s="23" t="s">
-        <v>287</v>
-      </c>
-      <c r="J27" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="K27" s="23" t="s">
-        <v>290</v>
-      </c>
-      <c r="M27" s="24" t="s">
-        <v>291</v>
-      </c>
-      <c r="N27" s="22" t="s">
-        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -2620,7 +2756,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="80" customWidth="1"/>
@@ -2628,79 +2764,79 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
-      <c r="A1" s="26" t="s">
-        <v>245</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
+      <c r="A1" s="25" t="s">
+        <v>243</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
     </row>
     <row r="3" spans="1:4" ht="34" customHeight="1">
       <c r="A3" s="11" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
     </row>
     <row r="4" spans="1:4" ht="34" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
     </row>
     <row r="5" spans="1:4" ht="34" customHeight="1">
       <c r="A5" s="13" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
     </row>
     <row r="6" spans="1:4" ht="34" customHeight="1">
       <c r="A6" s="13" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
     </row>
     <row r="7" spans="1:4" ht="34" customHeight="1">
       <c r="A7" s="13" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
     </row>
     <row r="8" spans="1:4" ht="34" customHeight="1">
       <c r="A8" s="13" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
     </row>
     <row r="9" spans="1:4" ht="34" customHeight="1">
       <c r="A9" s="15" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>

--- a/RWF_Entourage.xlsx
+++ b/RWF_Entourage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="170" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6B9E8A1-0809-A74D-A644-FB185C63A2CE}"/>
+  <xr:revisionPtr revIDLastSave="172" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72464BCF-5356-E846-B855-96227B1550E1}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="29400" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7400" yWindow="1180" windowWidth="29400" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entourage" sheetId="1" r:id="rId1"/>
@@ -1052,12 +1052,6 @@
     <t>Bohm</t>
   </si>
   <si>
-    <t>Le Soldat américain;Prenez garde à la sainte putain; Tous les autres s’appellent Ali;Le Droit du plus fort; Le Rôti de Satan; Berlin Alexanderplatz</t>
-  </si>
-  <si>
-    <t>film-1970-le-soldat-americain; film-1971-prenez-garde-a-la-sainte-putain; film-1974-tous-les-autres-s-appellent-ali;film-1975-le-droit-du-plus-fort; film-1976-le-roti-de-satan; film-1980-berlin-alexanderplatz</t>
-  </si>
-  <si>
     <t>film-1969-l-amour-est-plus-froid-que-la-mort; film-1969-le-bouc; film-1970-les-dieux-de-la-peste; film-1970-rio-das-mortes; film-1971-prenez-garde-a-la-sainte-putain; film-1972-huit-heures-ne-font-pas-un-jour; film-1972-le-marchand-des-quatre-saisons; film-1972-les-larmes-ameres-de-petra-von-kant; film-1974-effi-briest; film-1979-la-troisieme-generation; film-1979-le-mariage-de-maria-braun; film-1980-berlin-alexanderplatz; film-1981-lili-marleen</t>
   </si>
   <si>
@@ -1129,6 +1123,12 @@
   </si>
   <si>
     <t>Bohm.H.jpg</t>
+  </si>
+  <si>
+    <t>Le Soldat américain;Prenez garde à la sainte putain; Effi Briest; Tous les autres s’appellent Ali;Le Droit du plus fort; Le Rôti de Satan; Berlin Alexanderplatz</t>
+  </si>
+  <si>
+    <t>film-1970-le-soldat-americain; film-1971-prenez-garde-a-la-sainte-putain; film-1974-effi-briest; film-1974-tous-les-autres-s-appellent-ali;film-1975-le-droit-du-plus-fort; film-1976-le-roti-de-satan; film-1980-berlin-alexanderplatz</t>
   </si>
 </sst>
 </file>
@@ -1377,10 +1377,10 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1632,7 +1632,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -1855,42 +1855,42 @@
     </row>
     <row r="6" spans="1:14" ht="72" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="D6" s="26" t="s">
-        <v>311</v>
+      <c r="D6" s="25" t="s">
+        <v>309</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="L6" s="3"/>
       <c r="M6" s="18" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="72" customHeight="1">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>115</v>
@@ -2498,10 +2498,10 @@
         <v>96</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>97</v>
@@ -2756,7 +2756,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="80" customWidth="1"/>
@@ -2764,12 +2764,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>243</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
     </row>
     <row r="3" spans="1:4" ht="34" customHeight="1">
       <c r="A3" s="11" t="s">

--- a/RWF_Entourage.xlsx
+++ b/RWF_Entourage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="172" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72464BCF-5356-E846-B855-96227B1550E1}"/>
+  <xr:revisionPtr revIDLastSave="173" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B3880C9-78B6-BF4A-901C-5E4C8FBC3C33}"/>
   <bookViews>
     <workbookView xWindow="7400" yWindow="1180" windowWidth="29400" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="314">
   <si>
     <t>ID canonique</t>
   </si>
@@ -428,9 +428,6 @@
   </si>
   <si>
     <t>Juliane Lorenz</t>
-  </si>
-  <si>
-    <t>Lorenz</t>
   </si>
   <si>
     <t>Juliane</t>
@@ -1735,42 +1732,42 @@
     </row>
     <row r="3" spans="1:14" ht="72" customHeight="1">
       <c r="A3" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>190</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>191</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="9" t="s">
         <v>196</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>197</v>
       </c>
       <c r="L3" s="3"/>
       <c r="M3" s="18" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="72" customHeight="1">
@@ -1815,16 +1812,16 @@
     </row>
     <row r="5" spans="1:14" ht="72" customHeight="1">
       <c r="A5" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>142</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
@@ -1834,77 +1831,77 @@
         <v>19</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="K5" s="9" t="s">
         <v>145</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>146</v>
       </c>
       <c r="L5" s="3"/>
       <c r="M5" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="N5" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="72" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J6" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="K6" s="9" t="s">
         <v>313</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>314</v>
       </c>
       <c r="L6" s="3"/>
       <c r="M6" s="18" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="72" customHeight="1">
       <c r="A7" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>182</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
@@ -1914,23 +1911,23 @@
         <v>30</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="K7" s="9" t="s">
         <v>185</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>186</v>
       </c>
       <c r="L7" s="3"/>
       <c r="M7" s="18" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="72" customHeight="1">
@@ -1948,7 +1945,7 @@
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>115</v>
@@ -1975,120 +1972,120 @@
     </row>
     <row r="9" spans="1:14" ht="72" customHeight="1">
       <c r="A9" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>211</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="I9" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="K9" s="9" t="s">
         <v>214</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>215</v>
       </c>
       <c r="L9" s="3"/>
       <c r="M9" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="N9" s="3" t="s">
         <v>216</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="72" customHeight="1">
       <c r="A10" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>171</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="K10" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="K10" s="9" t="s">
+      <c r="L10" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="L10" s="3" t="s">
+      <c r="M10" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="M10" s="18" t="s">
+      <c r="N10" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="72" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
         <v>93</v>
       </c>
       <c r="G11" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="I11" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="J11" s="3" t="s">
+      <c r="K11" s="24" t="s">
         <v>295</v>
-      </c>
-      <c r="K11" s="24" t="s">
-        <v>296</v>
       </c>
       <c r="L11" s="3"/>
       <c r="M11" s="18" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="72" customHeight="1">
@@ -2121,7 +2118,7 @@
       </c>
       <c r="L12" s="3"/>
       <c r="M12" s="18" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>77</v>
@@ -2135,10 +2132,10 @@
         <v>123</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>264</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -2159,7 +2156,7 @@
       </c>
       <c r="L13" s="3"/>
       <c r="M13" s="18" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>128</v>
@@ -2207,34 +2204,34 @@
     </row>
     <row r="15" spans="1:14" ht="72" customHeight="1">
       <c r="A15" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>220</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>221</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="K15" s="9" t="s">
         <v>223</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>224</v>
       </c>
       <c r="L15" s="3"/>
       <c r="M15" s="19"/>
       <c r="N15" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="72" customHeight="1">
@@ -2244,35 +2241,33 @@
       <c r="B16" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="3"/>
+      <c r="D16" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="I16" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="K16" s="9" t="s">
         <v>136</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>137</v>
       </c>
       <c r="L16" s="3"/>
       <c r="M16" s="18" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="72" customHeight="1">
@@ -2357,78 +2352,78 @@
     </row>
     <row r="19" spans="1:14" ht="72" customHeight="1">
       <c r="A19" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>152</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3" t="s">
         <v>93</v>
       </c>
       <c r="G19" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="H19" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="I19" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="J19" s="3" t="s">
+      <c r="K19" s="9" t="s">
         <v>156</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>157</v>
       </c>
       <c r="L19" s="3"/>
       <c r="M19" s="18" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="72" customHeight="1">
       <c r="A20" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>202</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3" t="s">
         <v>93</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="H20" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="I20" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>205</v>
       </c>
       <c r="J20" s="3"/>
       <c r="K20" s="9"/>
       <c r="L20" s="3"/>
       <c r="M20" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="N20" s="3" t="s">
         <v>206</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="72" customHeight="1">
@@ -2498,10 +2493,10 @@
         <v>96</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>97</v>
@@ -2515,56 +2510,56 @@
     </row>
     <row r="23" spans="1:14" ht="72" customHeight="1">
       <c r="A23" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>228</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>229</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>30</v>
       </c>
       <c r="H23" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="K23" s="9" t="s">
         <v>233</v>
-      </c>
-      <c r="K23" s="9" t="s">
-        <v>234</v>
       </c>
       <c r="L23" s="3"/>
       <c r="M23" s="18" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="72" customHeight="1">
       <c r="A24" s="21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
@@ -2574,37 +2569,37 @@
         <v>30</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J24" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="K24" s="9" t="s">
         <v>277</v>
-      </c>
-      <c r="K24" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="L24" s="3"/>
       <c r="M24" s="18" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="72" customHeight="1">
       <c r="A25" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3" t="s">
@@ -2617,20 +2612,20 @@
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="J25" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="J25" s="3" t="s">
+      <c r="K25" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="K25" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="L25" s="3"/>
       <c r="M25" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="N25" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="N25" s="3" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="72" customHeight="1">
@@ -2665,7 +2660,7 @@
       </c>
       <c r="L26" s="3"/>
       <c r="M26" s="19" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>35</v>
@@ -2673,16 +2668,16 @@
     </row>
     <row r="27" spans="1:14" ht="72" customHeight="1">
       <c r="A27" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="C27" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="D27" s="4" t="s">
         <v>238</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>239</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
@@ -2694,55 +2689,55 @@
       </c>
       <c r="I27" s="4"/>
       <c r="J27" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="K27" s="10" t="s">
         <v>240</v>
-      </c>
-      <c r="K27" s="10" t="s">
-        <v>241</v>
       </c>
       <c r="L27" s="4"/>
       <c r="M27" s="18" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="N27" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="28" spans="1:14" s="22" customFormat="1" ht="108" customHeight="1">
       <c r="A28" s="22" t="s">
+        <v>279</v>
+      </c>
+      <c r="B28" s="22" t="s">
         <v>280</v>
       </c>
-      <c r="B28" s="22" t="s">
+      <c r="C28" s="22" t="s">
         <v>281</v>
       </c>
-      <c r="C28" s="22" t="s">
+      <c r="D28" s="22" t="s">
         <v>282</v>
-      </c>
-      <c r="D28" s="22" t="s">
-        <v>283</v>
       </c>
       <c r="F28" s="22" t="s">
         <v>51</v>
       </c>
       <c r="G28" s="22" t="s">
+        <v>283</v>
+      </c>
+      <c r="H28" s="22" t="s">
+        <v>298</v>
+      </c>
+      <c r="I28" s="23" t="s">
+        <v>297</v>
+      </c>
+      <c r="J28" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="K28" s="23" t="s">
+        <v>286</v>
+      </c>
+      <c r="M28" s="23" t="s">
+        <v>299</v>
+      </c>
+      <c r="N28" s="22" t="s">
         <v>284</v>
-      </c>
-      <c r="H28" s="22" t="s">
-        <v>299</v>
-      </c>
-      <c r="I28" s="23" t="s">
-        <v>298</v>
-      </c>
-      <c r="J28" s="22" t="s">
-        <v>286</v>
-      </c>
-      <c r="K28" s="23" t="s">
-        <v>287</v>
-      </c>
-      <c r="M28" s="23" t="s">
-        <v>300</v>
-      </c>
-      <c r="N28" s="22" t="s">
-        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -2765,7 +2760,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
       <c r="A1" s="26" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -2773,70 +2768,70 @@
     </row>
     <row r="3" spans="1:4" ht="34" customHeight="1">
       <c r="A3" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>244</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>245</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
     </row>
     <row r="4" spans="1:4" ht="34" customHeight="1">
       <c r="A4" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>246</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>247</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
     </row>
     <row r="5" spans="1:4" ht="34" customHeight="1">
       <c r="A5" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>248</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>249</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
     </row>
     <row r="6" spans="1:4" ht="34" customHeight="1">
       <c r="A6" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="B6" s="14" t="s">
         <v>250</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>251</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
     </row>
     <row r="7" spans="1:4" ht="34" customHeight="1">
       <c r="A7" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>252</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>253</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
     </row>
     <row r="8" spans="1:4" ht="34" customHeight="1">
       <c r="A8" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>254</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>255</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
     </row>
     <row r="9" spans="1:4" ht="34" customHeight="1">
       <c r="A9" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>256</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>257</v>
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>

--- a/RWF_Entourage.xlsx
+++ b/RWF_Entourage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="173" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B3880C9-78B6-BF4A-901C-5E4C8FBC3C33}"/>
+  <xr:revisionPtr revIDLastSave="174" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{955CE60F-0222-A445-B5CC-0DA865AEBA8A}"/>
   <bookViews>
     <workbookView xWindow="7400" yWindow="1180" windowWidth="29400" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="315">
   <si>
     <t>ID canonique</t>
   </si>
@@ -1126,6 +1126,9 @@
   </si>
   <si>
     <t>film-1970-le-soldat-americain; film-1971-prenez-garde-a-la-sainte-putain; film-1974-effi-briest; film-1974-tous-les-autres-s-appellent-ali;film-1975-le-droit-du-plus-fort; film-1976-le-roti-de-satan; film-1980-berlin-alexanderplatz</t>
+  </si>
+  <si>
+    <t>Lorenz</t>
   </si>
 </sst>
 </file>
@@ -2241,7 +2244,9 @@
       <c r="B16" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C16" s="3"/>
+      <c r="C16" s="3" t="s">
+        <v>314</v>
+      </c>
       <c r="D16" s="3" t="s">
         <v>131</v>
       </c>

--- a/RWF_Entourage.xlsx
+++ b/RWF_Entourage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="174" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{955CE60F-0222-A445-B5CC-0DA865AEBA8A}"/>
+  <xr:revisionPtr revIDLastSave="251" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFF68A21-1AE4-9449-96A2-F1524DD20AC5}"/>
   <bookViews>
-    <workbookView xWindow="7400" yWindow="1180" windowWidth="29400" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18440" yWindow="5020" windowWidth="29400" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entourage" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="348">
   <si>
     <t>ID canonique</t>
   </si>
@@ -96,9 +96,6 @@
     <t>Acteur</t>
   </si>
   <si>
-    <t>Jeu, relation intime, présence biographique</t>
-  </si>
-  <si>
     <t>Compagnon de Fassbinder, figure de la dimension autobiographique et affective la plus douloureuse</t>
   </si>
   <si>
@@ -195,9 +192,6 @@
     <t>Cinéaste, monteur, collaborateur</t>
   </si>
   <si>
-    <t>Montage, relais artistique</t>
-  </si>
-  <si>
     <t>Compagnonnage artistique plus que vie privée centrale</t>
   </si>
   <si>
@@ -228,9 +222,6 @@
     <t>Acteur, partenaire</t>
   </si>
   <si>
-    <t>Jeu, présence incarnée, dimension autobiographique</t>
-  </si>
-  <si>
     <t>Partenaire intime de Fassbinder au moment de Angst essen Seele auf</t>
   </si>
   <si>
@@ -247,9 +238,6 @@
   </si>
   <si>
     <t>pers-gottfried-john</t>
-  </si>
-  <si>
-    <t>Gottfried John</t>
   </si>
   <si>
     <t>Gottfried</t>
@@ -286,9 +274,6 @@
     <t>Factory</t>
   </si>
   <si>
-    <t>Jeu, masculinité, présence marginale</t>
-  </si>
-  <si>
     <t>Présence récurrente du cercle de travail, au croisement du professionnel et du relationnel</t>
   </si>
   <si>
@@ -325,9 +310,6 @@
     <t>Jeu, présence, incarnation, image publique</t>
   </si>
   <si>
-    <t>Proche collaboratrice de longue durée, liée au noyau fondateur du groupe et à l’intimité artistique de Fassbinder</t>
-  </si>
-  <si>
     <t>Rio das Mortes</t>
   </si>
   <si>
@@ -352,9 +334,6 @@
     <t>Acteur, assistant, production</t>
   </si>
   <si>
-    <t>Jeu, soutien de production, présence interne</t>
-  </si>
-  <si>
     <t>Proche compagnon de travail et membre du cercle masculin du collectif</t>
   </si>
   <si>
@@ -385,12 +364,6 @@
     <t>Actrice, chanteuse</t>
   </si>
   <si>
-    <t>Jeu, performance, chanson, scène</t>
-  </si>
-  <si>
-    <t>Figure importante du cercle initial, liée au théâtre, à la scène et à la sphère intime du milieu Fassbinder, épouse de RWF</t>
-  </si>
-  <si>
     <t>L’Amour est plus froid que la mort; Le Soldat américain; Les Dieux de la peste; Pourquoi M. R. est-il atteint de folie meurtrière ?; Le Marchand des quatre saisons; Le Monde sur un fil; Tous les autres s’appellent Ali; Le Droit du plus fort; Maman Küsters s’en va au ciel; Le Rôti de Satan; Despair; L’Année des treize lunes</t>
   </si>
   <si>
@@ -407,9 +380,6 @@
   </si>
   <si>
     <t>Irm Hermann</t>
-  </si>
-  <si>
-    <t>Jeu, répétition de rôle, tension sociale</t>
   </si>
   <si>
     <t>Membre du cercle intime de travail, présence durable du premier collectif, associée à la sphère domestique et quotidienne du groupe</t>
@@ -494,12 +464,6 @@
     <t>Kurt</t>
   </si>
   <si>
-    <t>Acteur, scénariste, costumier</t>
-  </si>
-  <si>
-    <t>Jeu, écriture, conception plastique</t>
-  </si>
-  <si>
     <t>Ami proche, membre central du collectif, très intégré à la vie quotidienne du groupe Fassbinder</t>
   </si>
   <si>
@@ -643,9 +607,6 @@
   </si>
   <si>
     <t>Peer</t>
-  </si>
-  <si>
-    <t>Compositeur</t>
   </si>
   <si>
     <t>Musique, ambiance, structure émotionnelle</t>
@@ -1046,9 +1007,6 @@
     <t xml:space="preserve">Producteur majeur du cinéma ouest allemand, plutôt tourné vers l'industrie et les films divertissants. Il fait quelques incursions dans le cinéma de prestigue, d'auteur. </t>
   </si>
   <si>
-    <t>Bohm</t>
-  </si>
-  <si>
     <t>film-1969-l-amour-est-plus-froid-que-la-mort; film-1969-le-bouc; film-1970-les-dieux-de-la-peste; film-1970-rio-das-mortes; film-1971-prenez-garde-a-la-sainte-putain; film-1972-huit-heures-ne-font-pas-un-jour; film-1972-le-marchand-des-quatre-saisons; film-1972-les-larmes-ameres-de-petra-von-kant; film-1974-effi-briest; film-1979-la-troisieme-generation; film-1979-le-mariage-de-maria-braun; film-1980-berlin-alexanderplatz; film-1981-lili-marleen</t>
   </si>
   <si>
@@ -1104,18 +1062,12 @@
     </r>
   </si>
   <si>
-    <t>Noyau théâtral / Stock company/ période centrale et tardive</t>
-  </si>
-  <si>
     <t>stock company</t>
   </si>
   <si>
     <t>Hark</t>
   </si>
   <si>
-    <t>Hark Bohm</t>
-  </si>
-  <si>
     <t>pers-hark-bohm</t>
   </si>
   <si>
@@ -1129,6 +1081,180 @@
   </si>
   <si>
     <t>Lorenz</t>
+  </si>
+  <si>
+    <t>Famille</t>
+  </si>
+  <si>
+    <t>Fassbinder</t>
+  </si>
+  <si>
+    <t>Helmut</t>
+  </si>
+  <si>
+    <t>Helmut Fassbinder</t>
+  </si>
+  <si>
+    <t>perso-Helmut-Fassbinder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Père de RWF. Médecin, amateur de poésie. Il se spérare de Liselotte (Lilo), la mère de RWD, et quitte Munich pour Francfort. Il vut de la rente que lui procure la location d'appartements de rendements, essentiellement auprès de travailleurs immigrés. Adulte, RWF refuse tout contact avec lui d'après Katz. </t>
+  </si>
+  <si>
+    <t>Udo Kier</t>
+  </si>
+  <si>
+    <t>Dodo</t>
+  </si>
+  <si>
+    <t>Enfance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ami de jeunesse de RWF. </t>
+  </si>
+  <si>
+    <t>Kier</t>
+  </si>
+  <si>
+    <t>Udo</t>
+  </si>
+  <si>
+    <t>pers-udo-kier</t>
+  </si>
+  <si>
+    <t>John Gottfried</t>
+  </si>
+  <si>
+    <t>Christoph Roser</t>
+  </si>
+  <si>
+    <t>Roser</t>
+  </si>
+  <si>
+    <t>Christoph</t>
+  </si>
+  <si>
+    <t>pers-christoph-roser</t>
+  </si>
+  <si>
+    <t>Vie amoureuse</t>
+  </si>
+  <si>
+    <t>Le premier des compagnons de RWF. Disposant d'un d'économies, il les consacre à la production des deux premiers films de RWF</t>
+  </si>
+  <si>
+    <r>
+      <t>RWF la rencontre dans un cours de théâtre. Proche collaboratrice de longue durée, liée au noyau fondateur du groupe et à l’intimité artistique de Fassbinder. Il l'écarte des tournages après Effi Briest, tourne à nouveau avec elle à partir du M</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ariage de Maria Braun</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> et Lili Marleen, mais la rupture est consommée. </t>
+    </r>
+  </si>
+  <si>
+    <t>Noyau théâtral/Vie amoureuse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figure importante du cercle initial, liée au théâtre, à la scène et à la sphère intime du milieu Fassbinder, épouse de RWF. Il la maltraite et subit ses crises de jalousie. </t>
+  </si>
+  <si>
+    <t>La tante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montage, relais artistique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acteur, scénariste, costumier, décorateur, homme à tout faire </t>
+  </si>
+  <si>
+    <t>Willi</t>
+  </si>
+  <si>
+    <t>Acteur, compositeur</t>
+  </si>
+  <si>
+    <t>Joue les jeunes premiers chez RWF</t>
+  </si>
+  <si>
+    <t>La schletelle, ma meilleure copine en second</t>
+  </si>
+  <si>
+    <t>Jeu, écriture, conception plastique -</t>
+  </si>
+  <si>
+    <t>Emma Patate, ma meilleure copine</t>
+  </si>
+  <si>
+    <t>Noyau théâtral / Stock company/ période centrale et tardive/ vie amoureuse</t>
+  </si>
+  <si>
+    <t>Jeu, performance, chanson, scène
+seconde épouse de RWF</t>
+  </si>
+  <si>
+    <t>Hark Böhm</t>
+  </si>
+  <si>
+    <t>"mon nègre Bavarois"</t>
+  </si>
+  <si>
+    <t>Jeu, soutien de production, conseil artistique</t>
+  </si>
+  <si>
+    <t>Ilse Lo Zott</t>
+  </si>
+  <si>
+    <t>Factory/vie amoureuse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeu, présence incarnée, dimension autobiographique
+2ème des trois grands amours de RWF. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeu, 
+3ème des trois grands amours de RWF. Ancien Garçon boucher. </t>
+  </si>
+  <si>
+    <t>Jeu, masculinité, présence marginale
+Premier des trois grands amours de RWF. Ancien marin.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeu. Production. 
+Ancienne secrétaire. 
+Première épouse de RWF dont elle est éperdument amoureuse. Régulièrement humiliée par RWF, elle est une "victime née". </t>
+  </si>
+  <si>
+    <t>Nooyau théâtral</t>
+  </si>
+  <si>
+    <t>Rainer Werner Fasbbinder</t>
+  </si>
+  <si>
+    <t>Mary ou Bloody Mary</t>
+  </si>
+  <si>
+    <t>perso-Rainer-Werner-Fassbinder</t>
+  </si>
+  <si>
+    <t>Rainer Werner</t>
+  </si>
+  <si>
+    <t>Réalisateur</t>
   </si>
 </sst>
 </file>
@@ -1303,7 +1429,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1365,22 +1491,34 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1412,9 +1550,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EntourageV30" displayName="EntourageV30" ref="A1:N28" totalsRowShown="0">
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N28">
-    <sortCondition ref="C1:C28"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EntourageV30" displayName="EntourageV30" ref="A1:N32" totalsRowShown="0">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N32">
+    <sortCondition ref="C1:C32"/>
   </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID canonique"/>
@@ -1631,7 +1769,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
@@ -1695,1054 +1833,1194 @@
     </row>
     <row r="2" spans="1:14" ht="72" customHeight="1">
       <c r="A2" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="K2" s="8" t="s">
         <v>101</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>108</v>
       </c>
       <c r="L2" s="2"/>
       <c r="M2" s="18" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="72" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="L3" s="3"/>
       <c r="M3" s="18" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="72" customHeight="1">
       <c r="A4" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
         <v>18</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="K4" s="9" t="s">
         <v>64</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>67</v>
       </c>
       <c r="L4" s="3"/>
       <c r="M4" s="18" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="72" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>138</v>
+        <v>294</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>139</v>
+        <v>333</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>141</v>
+        <v>130</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>293</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>18</v>
+        <v>292</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>142</v>
+        <v>290</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>143</v>
+        <v>289</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>144</v>
+        <v>296</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>145</v>
+        <v>297</v>
       </c>
       <c r="L5" s="3"/>
       <c r="M5" s="18" t="s">
-        <v>146</v>
+        <v>291</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>147</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="72" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>310</v>
+        <v>128</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>309</v>
+        <v>129</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="D6" s="25" t="s">
-        <v>308</v>
+        <v>130</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>131</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>307</v>
+        <v>18</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>304</v>
+        <v>132</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>303</v>
+        <v>133</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>312</v>
+        <v>134</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>313</v>
+        <v>135</v>
       </c>
       <c r="L6" s="3"/>
       <c r="M6" s="18" t="s">
-        <v>305</v>
+        <v>136</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>311</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="72" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="L7" s="3"/>
       <c r="M7" s="18" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="72" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>116</v>
+        <v>332</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>117</v>
+        <v>321</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="L8" s="3"/>
       <c r="M8" s="18" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="72" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E9" s="3"/>
+        <v>197</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>328</v>
+      </c>
       <c r="F9" s="3" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="L9" s="3"/>
       <c r="M9" s="18" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="72" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
+      <c r="F10" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="G10" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H10" s="3"/>
+        <v>159</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="I10" s="3" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="M10" s="18" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="72" customHeight="1">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="97" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>190</v>
+        <v>301</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>293</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="K11" s="24" t="s">
-        <v>295</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="J11" s="3"/>
+      <c r="K11" s="26"/>
       <c r="L11" s="3"/>
-      <c r="M11" s="18" t="s">
-        <v>292</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="72" customHeight="1">
+      <c r="M11" s="18"/>
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" ht="97" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>70</v>
+        <v>345</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>71</v>
+        <v>343</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>72</v>
+        <v>300</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E12" s="3"/>
+        <v>346</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>344</v>
+      </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>74</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="H12" s="3"/>
       <c r="I12" s="3"/>
-      <c r="J12" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="K12" s="9" t="s">
-        <v>76</v>
-      </c>
+      <c r="J12" s="3"/>
+      <c r="K12" s="26"/>
       <c r="L12" s="3"/>
-      <c r="M12" s="18" t="s">
-        <v>259</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>77</v>
-      </c>
+      <c r="M12" s="18"/>
+      <c r="N12" s="3"/>
     </row>
     <row r="13" spans="1:14" ht="72" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>122</v>
+        <v>276</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>123</v>
+        <v>275</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>263</v>
+        <v>178</v>
       </c>
       <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="G13" s="3" t="s">
-        <v>30</v>
+        <v>277</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>124</v>
+        <v>280</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>127</v>
+        <v>281</v>
+      </c>
+      <c r="K13" s="30" t="s">
+        <v>282</v>
       </c>
       <c r="L13" s="3"/>
       <c r="M13" s="18" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>128</v>
+        <v>283</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="72" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>79</v>
+        <v>312</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3" t="s">
-        <v>82</v>
+        <v>320</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>84</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="L14" s="3"/>
       <c r="M14" s="18" t="s">
-        <v>87</v>
+        <v>246</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="72" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>217</v>
+        <v>113</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>218</v>
+        <v>114</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>219</v>
+        <v>249</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>342</v>
+      </c>
       <c r="G15" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
+        <v>29</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>115</v>
+      </c>
       <c r="J15" s="3" t="s">
-        <v>222</v>
+        <v>116</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>223</v>
+        <v>117</v>
       </c>
       <c r="L15" s="3"/>
-      <c r="M15" s="19"/>
+      <c r="M15" s="18" t="s">
+        <v>247</v>
+      </c>
       <c r="N15" s="3" t="s">
-        <v>224</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="72" customHeight="1">
       <c r="A16" s="6" t="s">
-        <v>129</v>
+        <v>74</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>314</v>
+        <v>76</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
+        <v>77</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>337</v>
+      </c>
       <c r="G16" s="3" t="s">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>133</v>
+        <v>340</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>136</v>
+        <v>81</v>
       </c>
       <c r="L16" s="3"/>
       <c r="M16" s="18" t="s">
-        <v>267</v>
+        <v>82</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>137</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="72" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>14</v>
+        <v>311</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>15</v>
+        <v>305</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>16</v>
+        <v>309</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="3"/>
+        <v>310</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>306</v>
+      </c>
       <c r="F17" s="3" t="s">
-        <v>18</v>
+        <v>307</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>23</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="9"/>
       <c r="L17" s="3"/>
-      <c r="M17" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>25</v>
-      </c>
+      <c r="M17" s="18"/>
+      <c r="N17" s="3"/>
     </row>
     <row r="18" spans="1:14" ht="72" customHeight="1">
       <c r="A18" s="6" t="s">
-        <v>36</v>
+        <v>204</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>37</v>
+        <v>205</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>38</v>
+        <v>206</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>39</v>
+        <v>207</v>
       </c>
       <c r="E18" s="3"/>
-      <c r="F18" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="F18" s="3"/>
       <c r="G18" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>42</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
-        <v>43</v>
+        <v>209</v>
       </c>
       <c r="K18" s="9" t="s">
-        <v>44</v>
+        <v>210</v>
       </c>
       <c r="L18" s="3"/>
-      <c r="M18" s="18" t="s">
-        <v>45</v>
+      <c r="M18" s="19" t="s">
+        <v>327</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>46</v>
+        <v>211</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="72" customHeight="1">
       <c r="A19" s="6" t="s">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>149</v>
+        <v>120</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>150</v>
+        <v>298</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="E19" s="3"/>
-      <c r="F19" s="3" t="s">
-        <v>93</v>
-      </c>
+      <c r="F19" s="3"/>
       <c r="G19" s="3" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>154</v>
+        <v>124</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="L19" s="3"/>
       <c r="M19" s="18" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>157</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="72" customHeight="1">
       <c r="A20" s="6" t="s">
-        <v>198</v>
+        <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>199</v>
+        <v>15</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>200</v>
+        <v>16</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>201</v>
+        <v>17</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3" t="s">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>203</v>
+        <v>339</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="J20" s="3"/>
-      <c r="K20" s="9"/>
+        <v>20</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>22</v>
+      </c>
       <c r="L20" s="3"/>
       <c r="M20" s="18" t="s">
-        <v>205</v>
+        <v>23</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>206</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="72" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="K21" s="9" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="L21" s="3"/>
       <c r="M21" s="18" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="72" customHeight="1">
       <c r="A22" s="6" t="s">
-        <v>89</v>
+        <v>138</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>91</v>
+        <v>140</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E22" s="3"/>
+        <v>141</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>330</v>
+      </c>
       <c r="F22" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>94</v>
+        <v>324</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>95</v>
+        <v>329</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>96</v>
+        <v>142</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>302</v>
+        <v>143</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>97</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="L22" s="3"/>
       <c r="M22" s="18" t="s">
-        <v>98</v>
+        <v>253</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>99</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="72" customHeight="1">
       <c r="A23" s="6" t="s">
-        <v>225</v>
+        <v>186</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>226</v>
+        <v>187</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>227</v>
+        <v>188</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="E23" s="3"/>
+        <v>189</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>325</v>
+      </c>
       <c r="F23" s="3" t="s">
-        <v>229</v>
+        <v>88</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>30</v>
+        <v>326</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="K23" s="9" t="s">
-        <v>233</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="J23" s="3"/>
+      <c r="K23" s="9"/>
       <c r="L23" s="3"/>
       <c r="M23" s="18" t="s">
-        <v>261</v>
+        <v>192</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>234</v>
+        <v>193</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="72" customHeight="1">
-      <c r="A24" s="21" t="s">
-        <v>275</v>
+      <c r="A24" s="6" t="s">
+        <v>316</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>270</v>
+        <v>313</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>278</v>
+        <v>314</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>269</v>
+        <v>315</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>30</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="G24" s="3"/>
       <c r="H24" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="J24" s="20" t="s">
-        <v>276</v>
-      </c>
-      <c r="K24" s="9" t="s">
-        <v>277</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="9"/>
       <c r="L24" s="3"/>
-      <c r="M24" s="18" t="s">
-        <v>272</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>274</v>
-      </c>
+      <c r="M24" s="18"/>
+      <c r="N24" s="3"/>
     </row>
     <row r="25" spans="1:14" ht="72" customHeight="1">
       <c r="A25" s="6" t="s">
-        <v>158</v>
+        <v>46</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>159</v>
+        <v>47</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>160</v>
+        <v>48</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="E25" s="3"/>
+        <v>49</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>322</v>
+      </c>
       <c r="F25" s="3" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>31</v>
+        <v>323</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>162</v>
+        <v>52</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="K25" s="9" t="s">
-        <v>164</v>
+        <v>54</v>
       </c>
       <c r="L25" s="3"/>
       <c r="M25" s="18" t="s">
-        <v>165</v>
+        <v>55</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>166</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="72" customHeight="1">
       <c r="A26" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="K26" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M26" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="72" customHeight="1">
+      <c r="A27" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="K27" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="L27" s="3"/>
+      <c r="M27" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="72" customHeight="1">
+      <c r="A28" s="28" t="s">
+        <v>262</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="J28" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="L28" s="3"/>
+      <c r="M28" s="18" t="s">
+        <v>259</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="72" customHeight="1">
+      <c r="A29" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="K29" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="L29" s="3"/>
+      <c r="M29" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="72" customHeight="1">
+      <c r="A30" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3" t="s">
+      <c r="H30" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H26" s="3" t="s">
+      <c r="I30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="J30" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J26" s="3" t="s">
+      <c r="K30" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K26" s="9" t="s">
+      <c r="L30" s="3"/>
+      <c r="M30" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="N30" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="L26" s="3"/>
-      <c r="M26" s="19" t="s">
-        <v>265</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="72" customHeight="1">
-      <c r="A27" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4" t="s">
+    </row>
+    <row r="31" spans="1:14" ht="72" customHeight="1">
+      <c r="A31" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H27" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="K27" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="L27" s="4"/>
-      <c r="M27" s="18" t="s">
+      <c r="H31" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="K31" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="L31" s="4"/>
+      <c r="M31" s="18" t="s">
+        <v>255</v>
+      </c>
+      <c r="N31" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" s="21" customFormat="1" ht="108" customHeight="1">
+      <c r="A32" s="27" t="s">
+        <v>266</v>
+      </c>
+      <c r="B32" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="C32" s="27" t="s">
         <v>268</v>
       </c>
-      <c r="N27" s="4" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" s="22" customFormat="1" ht="108" customHeight="1">
-      <c r="A28" s="22" t="s">
-        <v>279</v>
-      </c>
-      <c r="B28" s="22" t="s">
-        <v>280</v>
-      </c>
-      <c r="C28" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="D28" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="F28" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="G28" s="22" t="s">
-        <v>283</v>
-      </c>
-      <c r="H28" s="22" t="s">
-        <v>298</v>
-      </c>
-      <c r="I28" s="23" t="s">
-        <v>297</v>
-      </c>
-      <c r="J28" s="22" t="s">
+      <c r="D32" s="27" t="s">
+        <v>269</v>
+      </c>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="G32" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="H32" s="27" t="s">
         <v>285</v>
       </c>
-      <c r="K28" s="23" t="s">
+      <c r="I32" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="J32" s="27" t="s">
+        <v>272</v>
+      </c>
+      <c r="K32" s="29" t="s">
+        <v>273</v>
+      </c>
+      <c r="L32" s="27"/>
+      <c r="M32" s="22" t="s">
         <v>286</v>
       </c>
-      <c r="M28" s="23" t="s">
-        <v>299</v>
-      </c>
-      <c r="N28" s="22" t="s">
-        <v>284</v>
+      <c r="N32" s="27" t="s">
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -2764,79 +3042,79 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
-      <c r="A1" s="26" t="s">
-        <v>242</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
+      <c r="A1" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
     </row>
     <row r="3" spans="1:4" ht="34" customHeight="1">
       <c r="A3" s="11" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
     </row>
     <row r="4" spans="1:4" ht="34" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
     </row>
     <row r="5" spans="1:4" ht="34" customHeight="1">
       <c r="A5" s="13" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
     </row>
     <row r="6" spans="1:4" ht="34" customHeight="1">
       <c r="A6" s="13" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
     </row>
     <row r="7" spans="1:4" ht="34" customHeight="1">
       <c r="A7" s="13" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
     </row>
     <row r="8" spans="1:4" ht="34" customHeight="1">
       <c r="A8" s="13" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
     </row>
     <row r="9" spans="1:4" ht="34" customHeight="1">
       <c r="A9" s="15" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>

--- a/RWF_Entourage.xlsx
+++ b/RWF_Entourage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="251" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFF68A21-1AE4-9449-96A2-F1524DD20AC5}"/>
+  <xr:revisionPtr revIDLastSave="286" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DE4C9BC-5C7F-A44D-B969-ADEC7560026E}"/>
   <bookViews>
-    <workbookView xWindow="18440" yWindow="5020" windowWidth="29400" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12620" yWindow="4000" windowWidth="29400" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entourage" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="353">
   <si>
     <t>ID canonique</t>
   </si>
@@ -151,9 +151,6 @@
   </si>
   <si>
     <t>Brigitte</t>
-  </si>
-  <si>
-    <t>Période centrale / tardive</t>
   </si>
   <si>
     <t>Jeu, décalage social, figure populaire</t>
@@ -576,9 +573,6 @@
     <t>Michael</t>
   </si>
   <si>
-    <t>Factory / période tardive</t>
-  </si>
-  <si>
     <t>Directeur de la photographie</t>
   </si>
   <si>
@@ -631,9 +625,6 @@
   </si>
   <si>
     <t>Peter</t>
-  </si>
-  <si>
-    <t>Factory / période centrale</t>
   </si>
   <si>
     <t>Proche du milieu artistique, sans statut de relation intime centrale comparable aux membres du noyau fondateur</t>
@@ -1062,9 +1053,6 @@
     </r>
   </si>
   <si>
-    <t>stock company</t>
-  </si>
-  <si>
     <t>Hark</t>
   </si>
   <si>
@@ -1167,9 +1155,6 @@
     </r>
   </si>
   <si>
-    <t>Noyau théâtral/Vie amoureuse</t>
-  </si>
-  <si>
     <t xml:space="preserve">Figure importante du cercle initial, liée au théâtre, à la scène et à la sphère intime du milieu Fassbinder, épouse de RWF. Il la maltraite et subit ses crises de jalousie. </t>
   </si>
   <si>
@@ -1198,9 +1183,6 @@
   </si>
   <si>
     <t>Emma Patate, ma meilleure copine</t>
-  </si>
-  <si>
-    <t>Noyau théâtral / Stock company/ période centrale et tardive/ vie amoureuse</t>
   </si>
   <si>
     <t>Jeu, performance, chanson, scène
@@ -1239,9 +1221,6 @@
 Première épouse de RWF dont elle est éperdument amoureuse. Régulièrement humiliée par RWF, elle est une "victime née". </t>
   </si>
   <si>
-    <t>Nooyau théâtral</t>
-  </si>
-  <si>
     <t>Rainer Werner Fasbbinder</t>
   </si>
   <si>
@@ -1255,6 +1234,42 @@
   </si>
   <si>
     <t>Réalisateur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Factory </t>
+  </si>
+  <si>
+    <t>Famille/Factory</t>
+  </si>
+  <si>
+    <t>Noyau théâtral/Factory</t>
+  </si>
+  <si>
+    <t>Période centrale/Collaborateurs réguliers</t>
+  </si>
+  <si>
+    <t>Factory/ période centrale</t>
+  </si>
+  <si>
+    <t>Noyau théâtral/factory</t>
+  </si>
+  <si>
+    <t>Période centrale/vie amoureuse</t>
+  </si>
+  <si>
+    <t>Collaborations ponctuelles.</t>
+  </si>
+  <si>
+    <t>Période tardive/Vie amoureuse</t>
+  </si>
+  <si>
+    <t>Collaborations régulières</t>
+  </si>
+  <si>
+    <t>Collaobrations ponctuelles</t>
+  </si>
+  <si>
+    <t>Collaboration ponctuelles</t>
   </si>
 </sst>
 </file>
@@ -1429,7 +1444,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1497,28 +1512,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1833,610 +1842,610 @@
     </row>
     <row r="2" spans="1:14" ht="72" customHeight="1">
       <c r="A2" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="8" t="s">
         <v>100</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>101</v>
       </c>
       <c r="L2" s="2"/>
       <c r="M2" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="N2" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="72" customHeight="1">
       <c r="A3" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>178</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="K3" s="9" t="s">
         <v>182</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>184</v>
       </c>
       <c r="L3" s="3"/>
       <c r="M3" s="18" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="72" customHeight="1">
       <c r="A4" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="9" t="s">
         <v>63</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>64</v>
       </c>
       <c r="L4" s="3"/>
       <c r="M4" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="N4" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="72" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D5" s="25" t="s">
-        <v>293</v>
+        <v>129</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>289</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>292</v>
+        <v>343</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="L5" s="3"/>
       <c r="M5" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="N5" s="3" t="s">
         <v>291</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="72" customHeight="1">
       <c r="A6" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="23" t="s">
         <v>130</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>131</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>18</v>
+        <v>344</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H6" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="K6" s="9" t="s">
         <v>134</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>135</v>
       </c>
       <c r="L6" s="3"/>
       <c r="M6" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="N6" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="72" customHeight="1">
       <c r="A7" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>78</v>
+        <v>344</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>29</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="K7" s="9" t="s">
         <v>172</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>173</v>
       </c>
       <c r="L7" s="3"/>
       <c r="M7" s="18" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="72" customHeight="1">
       <c r="A8" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="J8" s="3" t="s">
+      <c r="K8" s="9" t="s">
         <v>109</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>110</v>
       </c>
       <c r="L8" s="3"/>
       <c r="M8" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="N8" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="72" customHeight="1">
       <c r="A9" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>197</v>
-      </c>
       <c r="E9" s="3" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>198</v>
+        <v>345</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="L9" s="3"/>
       <c r="M9" s="18" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="72" customHeight="1">
       <c r="A10" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>158</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>299</v>
+        <v>342</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>29</v>
       </c>
       <c r="I10" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="K10" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="K10" s="9" t="s">
+      <c r="L10" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="L10" s="3" t="s">
+      <c r="M10" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="M10" s="18" t="s">
+      <c r="N10" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="97" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="J11" s="3"/>
-      <c r="K11" s="26"/>
+      <c r="K11" s="25"/>
       <c r="L11" s="3"/>
       <c r="M11" s="18"/>
       <c r="N11" s="3"/>
     </row>
     <row r="12" spans="1:14" ht="97" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
-      <c r="K12" s="26"/>
+      <c r="K12" s="25"/>
       <c r="L12" s="3"/>
       <c r="M12" s="18"/>
       <c r="N12" s="3"/>
     </row>
     <row r="13" spans="1:14" ht="72" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G13" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>280</v>
-      </c>
       <c r="I13" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="K13" s="30" t="s">
-        <v>282</v>
+      <c r="K13" s="27" t="s">
+        <v>279</v>
       </c>
       <c r="L13" s="3"/>
       <c r="M13" s="18" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="72" customHeight="1">
       <c r="A14" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3" t="s">
-        <v>320</v>
+        <v>348</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K14" s="9" t="s">
         <v>71</v>
-      </c>
-      <c r="K14" s="9" t="s">
-        <v>72</v>
       </c>
       <c r="L14" s="3"/>
       <c r="M14" s="18" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="72" customHeight="1">
       <c r="A15" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="C15" s="3" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>29</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="I15" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="K15" s="9" t="s">
         <v>116</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>117</v>
       </c>
       <c r="L15" s="3"/>
       <c r="M15" s="18" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="72" customHeight="1">
       <c r="A16" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="E16" s="3" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="I16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="K16" s="9" t="s">
         <v>80</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>81</v>
       </c>
       <c r="L16" s="3"/>
       <c r="M16" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="N16" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="72" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>309</v>
-      </c>
       <c r="D17" s="3" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
@@ -2447,74 +2456,76 @@
     </row>
     <row r="18" spans="1:14" ht="72" customHeight="1">
       <c r="A18" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K18" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L18" s="3"/>
       <c r="M18" s="19" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="72" customHeight="1">
       <c r="A19" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="3"/>
+      <c r="F19" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="I19" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="J19" s="3" t="s">
+      <c r="K19" s="9" t="s">
         <v>125</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>126</v>
       </c>
       <c r="L19" s="3"/>
       <c r="M19" s="18" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="72" customHeight="1">
@@ -2532,13 +2543,13 @@
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3" t="s">
-        <v>18</v>
+        <v>347</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>20</v>
@@ -2572,131 +2583,131 @@
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3" t="s">
-        <v>39</v>
+        <v>350</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>29</v>
       </c>
       <c r="H21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="K21" s="9" t="s">
         <v>42</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>43</v>
       </c>
       <c r="L21" s="3"/>
       <c r="M21" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="N21" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="72" customHeight="1">
       <c r="A22" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="K22" s="9" t="s">
         <v>143</v>
-      </c>
-      <c r="K22" s="9" t="s">
-        <v>144</v>
       </c>
       <c r="L22" s="3"/>
       <c r="M22" s="18" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="72" customHeight="1">
       <c r="A23" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="E23" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H23" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="I23" s="3" t="s">
         <v>189</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>191</v>
       </c>
       <c r="J23" s="3"/>
       <c r="K23" s="9"/>
       <c r="L23" s="3"/>
       <c r="M23" s="18" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="72" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
@@ -2707,184 +2718,184 @@
     </row>
     <row r="25" spans="1:14" ht="72" customHeight="1">
       <c r="A25" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="E25" s="3" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="F25" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="H25" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="I25" s="3" t="s">
+      <c r="J25" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="J25" s="3" t="s">
+      <c r="K25" s="9" t="s">
         <v>53</v>
-      </c>
-      <c r="K25" s="9" t="s">
-        <v>54</v>
       </c>
       <c r="L25" s="3"/>
       <c r="M25" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="N25" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="N25" s="3" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="72" customHeight="1">
       <c r="A26" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="C26" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="H26" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="H26" s="3" t="s">
+      <c r="I26" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="K26" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="L26" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="K26" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="L26" s="3" t="s">
+      <c r="M26" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="M26" s="18" t="s">
+      <c r="N26" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="72" customHeight="1">
       <c r="A27" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>215</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>29</v>
       </c>
       <c r="H27" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="K27" s="9" t="s">
         <v>217</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="K27" s="9" t="s">
-        <v>220</v>
       </c>
       <c r="L27" s="3"/>
       <c r="M27" s="18" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="72" customHeight="1">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>265</v>
-      </c>
       <c r="D28" s="3" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>29</v>
       </c>
       <c r="H28" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="J28" s="20" t="s">
         <v>260</v>
       </c>
-      <c r="I28" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="J28" s="20" t="s">
-        <v>263</v>
-      </c>
       <c r="K28" s="9" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="L28" s="3"/>
       <c r="M28" s="18" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="72" customHeight="1">
       <c r="A29" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>149</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>29</v>
@@ -2893,20 +2904,20 @@
         <v>30</v>
       </c>
       <c r="I29" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J29" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="J29" s="3" t="s">
+      <c r="K29" s="9" t="s">
         <v>151</v>
-      </c>
-      <c r="K29" s="9" t="s">
-        <v>152</v>
       </c>
       <c r="L29" s="3"/>
       <c r="M29" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="N29" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="72" customHeight="1">
@@ -2923,7 +2934,9 @@
         <v>28</v>
       </c>
       <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
+      <c r="F30" s="3" t="s">
+        <v>352</v>
+      </c>
       <c r="G30" s="3" t="s">
         <v>29</v>
       </c>
@@ -2941,7 +2954,7 @@
       </c>
       <c r="L30" s="3"/>
       <c r="M30" s="19" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="N30" s="3" t="s">
         <v>34</v>
@@ -2949,19 +2962,21 @@
     </row>
     <row r="31" spans="1:14" ht="72" customHeight="1">
       <c r="A31" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="D31" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>225</v>
-      </c>
       <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
+      <c r="F31" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="G31" s="4" t="s">
         <v>19</v>
       </c>
@@ -2970,57 +2985,55 @@
       </c>
       <c r="I31" s="4"/>
       <c r="J31" s="4" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L31" s="4"/>
       <c r="M31" s="18" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="N31" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="32" spans="1:14" s="21" customFormat="1" ht="108" customHeight="1">
-      <c r="A32" s="27" t="s">
+      <c r="A32" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>265</v>
+      </c>
+      <c r="D32" s="21" t="s">
         <v>266</v>
       </c>
-      <c r="B32" s="27" t="s">
+      <c r="F32" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="G32" s="21" t="s">
         <v>267</v>
       </c>
-      <c r="C32" s="27" t="s">
+      <c r="H32" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="I32" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="J32" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="K32" s="22" t="s">
+        <v>270</v>
+      </c>
+      <c r="M32" s="22" t="s">
+        <v>283</v>
+      </c>
+      <c r="N32" s="21" t="s">
         <v>268</v>
-      </c>
-      <c r="D32" s="27" t="s">
-        <v>269</v>
-      </c>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="G32" s="27" t="s">
-        <v>270</v>
-      </c>
-      <c r="H32" s="27" t="s">
-        <v>285</v>
-      </c>
-      <c r="I32" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="J32" s="27" t="s">
-        <v>272</v>
-      </c>
-      <c r="K32" s="29" t="s">
-        <v>273</v>
-      </c>
-      <c r="L32" s="27"/>
-      <c r="M32" s="22" t="s">
-        <v>286</v>
-      </c>
-      <c r="N32" s="27" t="s">
-        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -3042,79 +3055,79 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
-      <c r="A1" s="23" t="s">
-        <v>229</v>
-      </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
+      <c r="A1" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
     </row>
     <row r="3" spans="1:4" ht="34" customHeight="1">
       <c r="A3" s="11" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
     </row>
     <row r="4" spans="1:4" ht="34" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
     </row>
     <row r="5" spans="1:4" ht="34" customHeight="1">
       <c r="A5" s="13" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
     </row>
     <row r="6" spans="1:4" ht="34" customHeight="1">
       <c r="A6" s="13" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
     </row>
     <row r="7" spans="1:4" ht="34" customHeight="1">
       <c r="A7" s="13" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
     </row>
     <row r="8" spans="1:4" ht="34" customHeight="1">
       <c r="A8" s="13" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
     </row>
     <row r="9" spans="1:4" ht="34" customHeight="1">
       <c r="A9" s="15" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>

--- a/RWF_Entourage.xlsx
+++ b/RWF_Entourage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="286" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DE4C9BC-5C7F-A44D-B969-ADEC7560026E}"/>
+  <xr:revisionPtr revIDLastSave="301" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77283BBA-015D-BD45-ABAF-40D93DDE40A3}"/>
   <bookViews>
     <workbookView xWindow="12620" yWindow="4000" windowWidth="29400" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="354">
   <si>
     <t>ID canonique</t>
   </si>
@@ -96,9 +96,6 @@
     <t>Acteur</t>
   </si>
   <si>
-    <t>Compagnon de Fassbinder, figure de la dimension autobiographique et affective la plus douloureuse</t>
-  </si>
-  <si>
     <t>Maman Küsters s’en va au ciel; Peur de la peur; Je veux seulement que vous m’aimiez; Roulette chinoise; La Femme du chef de gare; L’Allemagne en automne</t>
   </si>
   <si>
@@ -243,10 +240,6 @@
     <t>John</t>
   </si>
   <si>
-    <t>Rôles ambigus : méchant absolu
-(James Bond !)</t>
-  </si>
-  <si>
     <t>Huit heures ne font pas un jour; Maman Küsters s’en va au ciel; Despair; L’Année des treize lunes; Le Mariage de Maria Braun; Berlin Alexanderplatz; Le Secret de Veronika Voss; Lili Marleen; Lola, une femme allemande</t>
   </si>
   <si>
@@ -268,9 +261,6 @@
     <t>Günther</t>
   </si>
   <si>
-    <t>Factory</t>
-  </si>
-  <si>
     <t>Présence récurrente du cercle de travail, au croisement du professionnel et du relationnel</t>
   </si>
   <si>
@@ -298,9 +288,6 @@
     <t>Hanna</t>
   </si>
   <si>
-    <t>Noyau théâtral / Factory</t>
-  </si>
-  <si>
     <t>Atrice, muse</t>
   </si>
   <si>
@@ -398,9 +385,6 @@
   </si>
   <si>
     <t>Juliane</t>
-  </si>
-  <si>
-    <t>Monteuse, assistante, actrice occasionnelle, productrice assistance à la mise en scène, présence au plateau,</t>
   </si>
   <si>
     <t>Assistance à la mise en scène, présence au plateau, postproduction</t>
@@ -459,9 +443,6 @@
   </si>
   <si>
     <t>Kurt</t>
-  </si>
-  <si>
-    <t>Ami proche, membre central du collectif, très intégré à la vie quotidienne du groupe Fassbinder</t>
   </si>
   <si>
     <t>L’Amour est plus froid que la mort; Le Bouc; Le Soldat américain; Pourquoi M. R. est-il atteint de folie meurtrière ?; Prenez garde à la sainte putain; Whity; Huit heures ne font pas un jour; Le Marchand des quatre saisons; Les Larmes amères de Petra von Kant; Effi Briest; Martha; Le Droit du plus fort; Maman Küsters s’en va au ciel; Peur de la peur; Le Rôti de Satan; Le Mariage de Maria Braun; Lili Marleen; Querelle</t>
@@ -1185,13 +1166,6 @@
     <t>Emma Patate, ma meilleure copine</t>
   </si>
   <si>
-    <t>Jeu, performance, chanson, scène
-seconde épouse de RWF</t>
-  </si>
-  <si>
-    <t>Hark Böhm</t>
-  </si>
-  <si>
     <t>"mon nègre Bavarois"</t>
   </si>
   <si>
@@ -1199,9 +1173,6 @@
   </si>
   <si>
     <t>Ilse Lo Zott</t>
-  </si>
-  <si>
-    <t>Factory/vie amoureuse</t>
   </si>
   <si>
     <t xml:space="preserve">Jeu, présence incarnée, dimension autobiographique
@@ -1216,60 +1187,106 @@
 Premier des trois grands amours de RWF. Ancien marin.</t>
   </si>
   <si>
+    <t>Rainer Werner Fasbbinder</t>
+  </si>
+  <si>
+    <t>Mary ou Bloody Mary</t>
+  </si>
+  <si>
+    <t>perso-Rainer-Werner-Fassbinder</t>
+  </si>
+  <si>
+    <t>Rainer Werner</t>
+  </si>
+  <si>
+    <t>Réalisateur</t>
+  </si>
+  <si>
+    <t>Période centrale/Collaborateurs réguliers</t>
+  </si>
+  <si>
+    <t>Période centrale/vie amoureuse</t>
+  </si>
+  <si>
+    <t>Collaborations ponctuelles.</t>
+  </si>
+  <si>
+    <t>Période tardive/Vie amoureuse</t>
+  </si>
+  <si>
+    <t>Collaborations régulières</t>
+  </si>
+  <si>
+    <t>Collaobrations ponctuelles</t>
+  </si>
+  <si>
+    <t>Collaboration ponctuelles</t>
+  </si>
+  <si>
+    <t>Ami proche, membre central du collectif, très intégré à la vie quotidienne du groupe Fassbinder
+En 1988 il fait de sa mort du sida un spectacle télévisuel</t>
+  </si>
+  <si>
+    <t>Bohm</t>
+  </si>
+  <si>
+    <t>Hark Bohm</t>
+  </si>
+  <si>
+    <t>Noyau théâtral/Stock company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stock company </t>
+  </si>
+  <si>
+    <t>Stock company</t>
+  </si>
+  <si>
+    <t>Stock company/ période centrale</t>
+  </si>
+  <si>
+    <t>Famille/Stock company</t>
+  </si>
+  <si>
+    <t>Noyau théâtral / Stock company</t>
+  </si>
+  <si>
+    <t>Stock company/vie amoureuse</t>
+  </si>
+  <si>
+    <t>Rôles ambigus : méchant absolu qui rejaillit dans sa cinématographie ( méchant dans James Bond)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jeu. Production. 
 Ancienne secrétaire. 
-Première épouse de RWF dont elle est éperdument amoureuse. Régulièrement humiliée par RWF, elle est une "victime née". </t>
-  </si>
-  <si>
-    <t>Rainer Werner Fasbbinder</t>
-  </si>
-  <si>
-    <t>Mary ou Bloody Mary</t>
-  </si>
-  <si>
-    <t>perso-Rainer-Werner-Fassbinder</t>
-  </si>
-  <si>
-    <t>Rainer Werner</t>
-  </si>
-  <si>
-    <t>Réalisateur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Factory </t>
-  </si>
-  <si>
-    <t>Famille/Factory</t>
-  </si>
-  <si>
-    <t>Noyau théâtral/Factory</t>
-  </si>
-  <si>
-    <t>Période centrale/Collaborateurs réguliers</t>
-  </si>
-  <si>
-    <t>Factory/ période centrale</t>
-  </si>
-  <si>
-    <t>Noyau théâtral/factory</t>
-  </si>
-  <si>
-    <t>Période centrale/vie amoureuse</t>
-  </si>
-  <si>
-    <t>Collaborations ponctuelles.</t>
-  </si>
-  <si>
-    <t>Période tardive/Vie amoureuse</t>
-  </si>
-  <si>
-    <t>Collaborations régulières</t>
-  </si>
-  <si>
-    <t>Collaobrations ponctuelles</t>
-  </si>
-  <si>
-    <t>Collaboration ponctuelles</t>
+Compagne de RWF dont elle est éperdument amoureuse. Régulièrement humiliée par RWF, elle est une "victime née". </t>
+  </si>
+  <si>
+    <t>Monteuse, assistante, actrice occasionnelle, productrice assistance à la mise en scène, présence au plateau
+Seconde épouse de RWF.
+Dirige la Rainer Werner fassbinder Foundation à la mort du cinéaste.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Producteur des premiers films - inspire Christoph de </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>L'année des treize lunes</t>
+    </r>
+  </si>
+  <si>
+    <t>Compagnon de Fassbinder, figure de la dimension autobiographique et affective la plus douloureuse : se suicide que RWF a rompu avec lui.</t>
+  </si>
+  <si>
+    <t>Jeu, performance, chanson, scène
+Première épouse de RWF</t>
   </si>
 </sst>
 </file>
@@ -1842,391 +1859,391 @@
     </row>
     <row r="2" spans="1:14" ht="72" customHeight="1">
       <c r="A2" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="H2" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="K2" s="8" t="s">
         <v>96</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>100</v>
       </c>
       <c r="L2" s="2"/>
       <c r="M2" s="18" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="72" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="L3" s="3"/>
       <c r="M3" s="18" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="72" customHeight="1">
       <c r="A4" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>77</v>
+        <v>343</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="9" t="s">
         <v>62</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>63</v>
       </c>
       <c r="L4" s="3"/>
       <c r="M4" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="N4" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="72" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>129</v>
+        <v>339</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="K5" s="9" t="s">
         <v>287</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>293</v>
       </c>
       <c r="L5" s="3"/>
       <c r="M5" s="18" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="72" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="L6" s="3"/>
       <c r="M6" s="18" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="72" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="L7" s="3"/>
       <c r="M7" s="18" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="72" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>326</v>
+        <v>353</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="L8" s="3"/>
       <c r="M8" s="18" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="72" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="L9" s="3"/>
       <c r="M9" s="18" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="72" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="M10" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="N10" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="M10" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="97" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="25"/>
@@ -2236,23 +2253,23 @@
     </row>
     <row r="12" spans="1:14" ht="97" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
@@ -2264,188 +2281,188 @@
     </row>
     <row r="13" spans="1:14" ht="72" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3" t="s">
-        <v>87</v>
+        <v>346</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="K13" s="27" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="L13" s="3"/>
       <c r="M13" s="18" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="72" customHeight="1">
       <c r="A14" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>69</v>
+        <v>348</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="L14" s="3"/>
       <c r="M14" s="18" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="72" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="L15" s="3"/>
       <c r="M15" s="18" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="72" customHeight="1">
       <c r="A16" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="E16" s="3" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L16" s="3"/>
       <c r="M16" s="18" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="72" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
@@ -2456,76 +2473,76 @@
     </row>
     <row r="18" spans="1:14" ht="72" customHeight="1">
       <c r="A18" s="6" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="K18" s="9" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="L18" s="3"/>
       <c r="M18" s="19" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="72" customHeight="1">
       <c r="A19" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>121</v>
+        <v>350</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="L19" s="3"/>
       <c r="M19" s="18" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="72" customHeight="1">
@@ -2543,171 +2560,173 @@
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="I20" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="K20" s="9" t="s">
         <v>21</v>
-      </c>
-      <c r="K20" s="9" t="s">
-        <v>22</v>
       </c>
       <c r="L20" s="3"/>
       <c r="M20" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="N20" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="72" customHeight="1">
       <c r="A21" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H21" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="K21" s="9" t="s">
         <v>41</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>42</v>
       </c>
       <c r="L21" s="3"/>
       <c r="M21" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="N21" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="72" customHeight="1">
       <c r="A22" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="K22" s="9" t="s">
         <v>137</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="K22" s="9" t="s">
-        <v>143</v>
       </c>
       <c r="L22" s="3"/>
       <c r="M22" s="18" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="72" customHeight="1">
       <c r="A23" s="6" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>87</v>
+        <v>346</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="J23" s="3"/>
       <c r="K23" s="9"/>
       <c r="L23" s="3"/>
       <c r="M23" s="18" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="72" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="G24" s="3"/>
+        <v>307</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>351</v>
+      </c>
       <c r="H24" s="3" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
@@ -2718,260 +2737,260 @@
     </row>
     <row r="25" spans="1:14" ht="72" customHeight="1">
       <c r="A25" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="E25" s="3" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="G25" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="I25" s="3" t="s">
+      <c r="J25" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="J25" s="3" t="s">
+      <c r="K25" s="9" t="s">
         <v>52</v>
-      </c>
-      <c r="K25" s="9" t="s">
-        <v>53</v>
       </c>
       <c r="L25" s="3"/>
       <c r="M25" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="N25" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="N25" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="72" customHeight="1">
       <c r="A26" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="K26" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M26" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="N26" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="K26" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="M26" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="72" customHeight="1">
       <c r="A27" s="6" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="K27" s="9" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="L27" s="3"/>
       <c r="M27" s="18" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="72" customHeight="1">
       <c r="A28" s="26" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="I28" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="J28" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="K28" s="9" t="s">
         <v>255</v>
-      </c>
-      <c r="J28" s="20" t="s">
-        <v>260</v>
-      </c>
-      <c r="K28" s="9" t="s">
-        <v>261</v>
       </c>
       <c r="L28" s="3"/>
       <c r="M28" s="18" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="72" customHeight="1">
       <c r="A29" s="6" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3" t="s">
-        <v>77</v>
+        <v>343</v>
       </c>
       <c r="G29" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H29" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="I29" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="K29" s="9" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="L29" s="3"/>
       <c r="M29" s="18" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="72" customHeight="1">
       <c r="A30" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="G30" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H30" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H30" s="3" t="s">
+      <c r="I30" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="I30" s="3" t="s">
+      <c r="J30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J30" s="3" t="s">
+      <c r="K30" s="9" t="s">
         <v>32</v>
-      </c>
-      <c r="K30" s="9" t="s">
-        <v>33</v>
       </c>
       <c r="L30" s="3"/>
       <c r="M30" s="19" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="72" customHeight="1">
       <c r="A31" s="7" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="E31" s="4"/>
       <c r="F31" s="4" t="s">
@@ -2981,59 +3000,59 @@
         <v>19</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I31" s="4"/>
       <c r="J31" s="4" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="L31" s="4"/>
       <c r="M31" s="18" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="N31" s="4" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="32" spans="1:14" s="21" customFormat="1" ht="108" customHeight="1">
       <c r="A32" s="21" t="s">
+        <v>257</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>258</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="D32" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="F32" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="G32" s="21" t="s">
+        <v>261</v>
+      </c>
+      <c r="H32" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="I32" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="J32" s="21" t="s">
         <v>263</v>
       </c>
-      <c r="B32" s="21" t="s">
+      <c r="K32" s="22" t="s">
         <v>264</v>
       </c>
-      <c r="C32" s="21" t="s">
-        <v>265</v>
-      </c>
-      <c r="D32" s="21" t="s">
-        <v>266</v>
-      </c>
-      <c r="F32" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="G32" s="21" t="s">
-        <v>267</v>
-      </c>
-      <c r="H32" s="21" t="s">
-        <v>282</v>
-      </c>
-      <c r="I32" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="J32" s="21" t="s">
-        <v>269</v>
-      </c>
-      <c r="K32" s="22" t="s">
-        <v>270</v>
-      </c>
       <c r="M32" s="22" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="N32" s="21" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -3056,7 +3075,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
       <c r="A1" s="28" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -3064,70 +3083,70 @@
     </row>
     <row r="3" spans="1:4" ht="34" customHeight="1">
       <c r="A3" s="11" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
     </row>
     <row r="4" spans="1:4" ht="34" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
     </row>
     <row r="5" spans="1:4" ht="34" customHeight="1">
       <c r="A5" s="13" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
     </row>
     <row r="6" spans="1:4" ht="34" customHeight="1">
       <c r="A6" s="13" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
     </row>
     <row r="7" spans="1:4" ht="34" customHeight="1">
       <c r="A7" s="13" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
     </row>
     <row r="8" spans="1:4" ht="34" customHeight="1">
       <c r="A8" s="13" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
     </row>
     <row r="9" spans="1:4" ht="34" customHeight="1">
       <c r="A9" s="15" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>

--- a/RWF_Entourage.xlsx
+++ b/RWF_Entourage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="301" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77283BBA-015D-BD45-ABAF-40D93DDE40A3}"/>
+  <xr:revisionPtr revIDLastSave="311" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{899D5EC0-1F9A-7345-A159-82140FE5E63F}"/>
   <bookViews>
     <workbookView xWindow="12620" yWindow="4000" windowWidth="29400" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="352">
   <si>
     <t>ID canonique</t>
   </si>
@@ -88,9 +88,6 @@
   </si>
   <si>
     <t>Armin</t>
-  </si>
-  <si>
-    <t>Période centrale</t>
   </si>
   <si>
     <t>Acteur</t>
@@ -1214,44 +1211,10 @@
     <t>Période tardive/Vie amoureuse</t>
   </si>
   <si>
-    <t>Collaborations régulières</t>
-  </si>
-  <si>
-    <t>Collaobrations ponctuelles</t>
-  </si>
-  <si>
-    <t>Collaboration ponctuelles</t>
-  </si>
-  <si>
-    <t>Ami proche, membre central du collectif, très intégré à la vie quotidienne du groupe Fassbinder
-En 1988 il fait de sa mort du sida un spectacle télévisuel</t>
-  </si>
-  <si>
     <t>Bohm</t>
   </si>
   <si>
     <t>Hark Bohm</t>
-  </si>
-  <si>
-    <t>Noyau théâtral/Stock company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stock company </t>
-  </si>
-  <si>
-    <t>Stock company</t>
-  </si>
-  <si>
-    <t>Stock company/ période centrale</t>
-  </si>
-  <si>
-    <t>Famille/Stock company</t>
-  </si>
-  <si>
-    <t>Noyau théâtral / Stock company</t>
-  </si>
-  <si>
-    <t>Stock company/vie amoureuse</t>
   </si>
   <si>
     <t>Rôles ambigus : méchant absolu qui rejaillit dans sa cinématographie ( méchant dans James Bond)</t>
@@ -1287,6 +1250,38 @@
   <si>
     <t>Jeu, performance, chanson, scène
 Première épouse de RWF</t>
+  </si>
+  <si>
+    <t>Noyau théâtral/Mini studio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mini studio </t>
+  </si>
+  <si>
+    <t>Mini studio</t>
+  </si>
+  <si>
+    <t>Mini studio/ période centrale</t>
+  </si>
+  <si>
+    <t>Famille/Mini studio</t>
+  </si>
+  <si>
+    <t>Noyau théâtral / Mini studio</t>
+  </si>
+  <si>
+    <t>Mini studio/vie amoureuse</t>
+  </si>
+  <si>
+    <t>Collaborations régulières/mini studio</t>
+  </si>
+  <si>
+    <t>Ami proche, membre central du collectif, très intégré à la vie quotidienne du groupe Fassbinder
+Rupture en 1977
+En 1988 il fait de sa mort du sida un spectacle télévisuel</t>
+  </si>
+  <si>
+    <t>Collaborations ponctuelles</t>
   </si>
 </sst>
 </file>
@@ -1859,391 +1854,391 @@
     </row>
     <row r="2" spans="1:14" ht="72" customHeight="1">
       <c r="A2" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="8" t="s">
         <v>95</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>96</v>
       </c>
       <c r="L2" s="2"/>
       <c r="M2" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="N2" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="72" customHeight="1">
       <c r="A3" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>171</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="9" t="s">
         <v>175</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>176</v>
       </c>
       <c r="L3" s="3"/>
       <c r="M3" s="18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="72" customHeight="1">
       <c r="A4" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="9" t="s">
         <v>61</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>62</v>
       </c>
       <c r="L4" s="3"/>
       <c r="M4" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="N4" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="72" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="K5" s="9" t="s">
         <v>286</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>287</v>
       </c>
       <c r="L5" s="3"/>
       <c r="M5" s="18" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="72" customHeight="1">
       <c r="A6" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="23" t="s">
         <v>124</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>125</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H6" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="K6" s="9" t="s">
         <v>128</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>129</v>
       </c>
       <c r="L6" s="3"/>
       <c r="M6" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="N6" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="72" customHeight="1">
       <c r="A7" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="K7" s="9" t="s">
         <v>165</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>166</v>
       </c>
       <c r="L7" s="3"/>
       <c r="M7" s="18" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="72" customHeight="1">
       <c r="A8" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="I8" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="J8" s="3" t="s">
+      <c r="K8" s="9" t="s">
         <v>104</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>105</v>
       </c>
       <c r="L8" s="3"/>
       <c r="M8" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="N8" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="72" customHeight="1">
       <c r="A9" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="K9" s="9" t="s">
         <v>191</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>192</v>
       </c>
       <c r="L9" s="3"/>
       <c r="M9" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="N9" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="72" customHeight="1">
       <c r="A10" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>151</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="K10" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="K10" s="9" t="s">
+      <c r="L10" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="L10" s="3" t="s">
+      <c r="M10" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="M10" s="18" t="s">
+      <c r="N10" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="97" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>290</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>291</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="25"/>
@@ -2253,23 +2248,23 @@
     </row>
     <row r="12" spans="1:14" ht="97" customHeight="1">
       <c r="A12" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>326</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>327</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
@@ -2281,188 +2276,188 @@
     </row>
     <row r="13" spans="1:14" ht="72" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G13" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="I13" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="J13" s="3" t="s">
+      <c r="K13" s="27" t="s">
         <v>272</v>
-      </c>
-      <c r="K13" s="27" t="s">
-        <v>273</v>
       </c>
       <c r="L13" s="3"/>
       <c r="M13" s="18" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="72" customHeight="1">
       <c r="A14" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K14" s="9" t="s">
         <v>68</v>
-      </c>
-      <c r="K14" s="9" t="s">
-        <v>69</v>
       </c>
       <c r="L14" s="3"/>
       <c r="M14" s="18" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="72" customHeight="1">
       <c r="A15" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="C15" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>240</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>241</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="I15" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="K15" s="9" t="s">
         <v>111</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>112</v>
       </c>
       <c r="L15" s="3"/>
       <c r="M15" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="72" customHeight="1">
       <c r="A16" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="K16" s="9" t="s">
         <v>76</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>77</v>
       </c>
       <c r="L16" s="3"/>
       <c r="M16" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="N16" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="72" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="E17" s="3" t="s">
+      <c r="F17" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>297</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>298</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
@@ -2473,76 +2468,78 @@
     </row>
     <row r="18" spans="1:14" ht="72" customHeight="1">
       <c r="A18" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3"/>
+      <c r="F18" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="K18" s="9" t="s">
         <v>200</v>
-      </c>
-      <c r="K18" s="9" t="s">
-        <v>201</v>
       </c>
       <c r="L18" s="3"/>
       <c r="M18" s="19" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="72" customHeight="1">
       <c r="A19" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="H19" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="J19" s="3" t="s">
+      <c r="K19" s="9" t="s">
         <v>119</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>120</v>
       </c>
       <c r="L19" s="3"/>
       <c r="M19" s="18" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="72" customHeight="1">
@@ -2560,173 +2557,173 @@
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="J20" s="3" t="s">
+      <c r="K20" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="K20" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="L20" s="3"/>
       <c r="M20" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="N20" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="72" customHeight="1">
       <c r="A21" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="K21" s="9" t="s">
         <v>40</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>41</v>
       </c>
       <c r="L21" s="3"/>
       <c r="M21" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="N21" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="72" customHeight="1">
+    </row>
+    <row r="22" spans="1:14" ht="132" customHeight="1">
       <c r="A22" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="J22" s="3" t="s">
+      <c r="K22" s="9" t="s">
         <v>136</v>
-      </c>
-      <c r="K22" s="9" t="s">
-        <v>137</v>
       </c>
       <c r="L22" s="3"/>
       <c r="M22" s="18" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="72" customHeight="1">
       <c r="A23" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="E23" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="H23" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="H23" s="3" t="s">
+      <c r="I23" s="3" t="s">
         <v>182</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>183</v>
       </c>
       <c r="J23" s="3"/>
       <c r="K23" s="9"/>
       <c r="L23" s="3"/>
       <c r="M23" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="N23" s="3" t="s">
         <v>184</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="72" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>304</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>305</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>307</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>308</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
@@ -2737,322 +2734,322 @@
     </row>
     <row r="25" spans="1:14" ht="72" customHeight="1">
       <c r="A25" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="E25" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H25" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="G25" s="3" t="s">
+      <c r="I25" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="I25" s="3" t="s">
+      <c r="J25" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="J25" s="3" t="s">
+      <c r="K25" s="9" t="s">
         <v>51</v>
-      </c>
-      <c r="K25" s="9" t="s">
-        <v>52</v>
       </c>
       <c r="L25" s="3"/>
       <c r="M25" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="N25" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="N25" s="3" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="72" customHeight="1">
       <c r="A26" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="C26" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G26" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H26" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="H26" s="3" t="s">
+      <c r="I26" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="K26" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="L26" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="K26" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="L26" s="3" t="s">
+      <c r="M26" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="M26" s="18" t="s">
+      <c r="N26" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="72" customHeight="1">
       <c r="A27" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>206</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H27" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H27" s="3" t="s">
+      <c r="I27" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="I27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="J27" s="3" t="s">
+      <c r="K27" s="9" t="s">
         <v>210</v>
-      </c>
-      <c r="K27" s="9" t="s">
-        <v>211</v>
       </c>
       <c r="L27" s="3"/>
       <c r="M27" s="18" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="72" customHeight="1">
       <c r="A28" s="26" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J28" s="20" t="s">
+        <v>253</v>
+      </c>
+      <c r="K28" s="9" t="s">
         <v>254</v>
-      </c>
-      <c r="K28" s="9" t="s">
-        <v>255</v>
       </c>
       <c r="L28" s="3"/>
       <c r="M28" s="18" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="72" customHeight="1">
       <c r="A29" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>142</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G29" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H29" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>29</v>
-      </c>
       <c r="I29" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J29" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="J29" s="3" t="s">
+      <c r="K29" s="9" t="s">
         <v>144</v>
-      </c>
-      <c r="K29" s="9" t="s">
-        <v>145</v>
       </c>
       <c r="L29" s="3"/>
       <c r="M29" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="N29" s="3" t="s">
         <v>146</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="72" customHeight="1">
       <c r="A30" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>27</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="G30" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H30" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H30" s="3" t="s">
+      <c r="I30" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="I30" s="3" t="s">
+      <c r="J30" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J30" s="3" t="s">
+      <c r="K30" s="9" t="s">
         <v>31</v>
-      </c>
-      <c r="K30" s="9" t="s">
-        <v>32</v>
       </c>
       <c r="L30" s="3"/>
       <c r="M30" s="19" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="72" customHeight="1">
       <c r="A31" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="B31" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="C31" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="D31" s="4" t="s">
         <v>215</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>216</v>
       </c>
       <c r="E31" s="4"/>
       <c r="F31" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="G31" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G31" s="4" t="s">
-        <v>19</v>
-      </c>
       <c r="H31" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I31" s="4"/>
       <c r="J31" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="K31" s="10" t="s">
         <v>217</v>
-      </c>
-      <c r="K31" s="10" t="s">
-        <v>218</v>
       </c>
       <c r="L31" s="4"/>
       <c r="M31" s="18" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="N31" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="32" spans="1:14" s="21" customFormat="1" ht="108" customHeight="1">
       <c r="A32" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="B32" s="21" t="s">
         <v>257</v>
       </c>
-      <c r="B32" s="21" t="s">
+      <c r="C32" s="21" t="s">
         <v>258</v>
       </c>
-      <c r="C32" s="21" t="s">
+      <c r="D32" s="21" t="s">
         <v>259</v>
       </c>
-      <c r="D32" s="21" t="s">
+      <c r="F32" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="G32" s="21" t="s">
         <v>260</v>
       </c>
-      <c r="F32" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="G32" s="21" t="s">
+      <c r="H32" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="I32" s="22" t="s">
+        <v>274</v>
+      </c>
+      <c r="J32" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="K32" s="22" t="s">
+        <v>263</v>
+      </c>
+      <c r="M32" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="N32" s="21" t="s">
         <v>261</v>
-      </c>
-      <c r="H32" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="I32" s="22" t="s">
-        <v>275</v>
-      </c>
-      <c r="J32" s="21" t="s">
-        <v>263</v>
-      </c>
-      <c r="K32" s="22" t="s">
-        <v>264</v>
-      </c>
-      <c r="M32" s="22" t="s">
-        <v>277</v>
-      </c>
-      <c r="N32" s="21" t="s">
-        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -3075,7 +3072,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
       <c r="A1" s="28" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -3083,70 +3080,70 @@
     </row>
     <row r="3" spans="1:4" ht="34" customHeight="1">
       <c r="A3" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>221</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>222</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
     </row>
     <row r="4" spans="1:4" ht="34" customHeight="1">
       <c r="A4" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>223</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>224</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
     </row>
     <row r="5" spans="1:4" ht="34" customHeight="1">
       <c r="A5" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>225</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>226</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
     </row>
     <row r="6" spans="1:4" ht="34" customHeight="1">
       <c r="A6" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="B6" s="14" t="s">
         <v>227</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>228</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
     </row>
     <row r="7" spans="1:4" ht="34" customHeight="1">
       <c r="A7" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>229</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>230</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
     </row>
     <row r="8" spans="1:4" ht="34" customHeight="1">
       <c r="A8" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>231</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>232</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
     </row>
     <row r="9" spans="1:4" ht="34" customHeight="1">
       <c r="A9" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>233</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>234</v>
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
